--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25403"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D43A09-080C-4044-B172-B56FBFE38440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FFD8AB-0A23-42BE-AAA9-84ADC396A7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1693,7 +1693,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2123,9 +2123,6 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2282,27 +2279,6 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2384,9 +2360,6 @@
     <xf numFmtId="165" fontId="9" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="25" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2394,6 +2367,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2468,29 +2466,46 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2770,35 +2785,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5546875" style="17" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5703125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.88671875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="40" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="49.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="16.2" thickBot="1">
+    <row r="1" spans="1:23" ht="16.5" thickBot="1">
       <c r="A1" s="244" t="s">
         <v>150</v>
       </c>
@@ -2825,7 +2840,7 @@
       <c r="V1" s="245"/>
       <c r="W1" s="246"/>
     </row>
-    <row r="2" spans="1:23" ht="16.2" thickBot="1">
+    <row r="2" spans="1:23" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2896,7 +2911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15" thickBot="1">
+    <row r="3" spans="1:23" ht="15.75" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -2965,7 +2980,7 @@
       <c r="V3" s="11"/>
       <c r="W3" s="12"/>
     </row>
-    <row r="4" spans="1:23" ht="15" thickBot="1">
+    <row r="4" spans="1:23" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -3022,17 +3037,17 @@
         <v>0.40599999999999997</v>
       </c>
       <c r="S4" s="91">
-        <v>2.0299999999999999E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="T4" s="91">
         <f t="shared" ref="T4:T47" si="3">S4*L4</f>
-        <v>0.81199999999999994</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="U4" s="13"/>
       <c r="V4" s="13"/>
       <c r="W4" s="14"/>
     </row>
-    <row r="5" spans="1:23" ht="42" thickBot="1">
+    <row r="5" spans="1:23" ht="39" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -3099,7 +3114,7 @@
       <c r="V5" s="13"/>
       <c r="W5" s="14"/>
     </row>
-    <row r="6" spans="1:23" ht="15" thickBot="1">
+    <row r="6" spans="1:23" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -3166,7 +3181,7 @@
       <c r="V6" s="13"/>
       <c r="W6" s="14"/>
     </row>
-    <row r="7" spans="1:23" ht="15" thickBot="1">
+    <row r="7" spans="1:23" ht="15.75" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -3233,7 +3248,7 @@
       <c r="V7" s="13"/>
       <c r="W7" s="14"/>
     </row>
-    <row r="8" spans="1:23" ht="55.8" thickBot="1">
+    <row r="8" spans="1:23" ht="51.75" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -3300,7 +3315,7 @@
       <c r="V8" s="23"/>
       <c r="W8" s="14"/>
     </row>
-    <row r="9" spans="1:23" ht="15" thickBot="1">
+    <row r="9" spans="1:23" ht="15.75" thickBot="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -3367,7 +3382,7 @@
       <c r="V9" s="13"/>
       <c r="W9" s="14"/>
     </row>
-    <row r="10" spans="1:23" ht="15" thickBot="1">
+    <row r="10" spans="1:23" ht="15.75" thickBot="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -3434,7 +3449,7 @@
       <c r="V10" s="13"/>
       <c r="W10" s="14"/>
     </row>
-    <row r="11" spans="1:23" ht="28.2" thickBot="1">
+    <row r="11" spans="1:23" ht="26.25" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -3501,7 +3516,7 @@
       <c r="V11" s="13"/>
       <c r="W11" s="14"/>
     </row>
-    <row r="12" spans="1:23" ht="15" thickBot="1">
+    <row r="12" spans="1:23" ht="15.75" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -3568,7 +3583,7 @@
       <c r="V12" s="13"/>
       <c r="W12" s="14"/>
     </row>
-    <row r="13" spans="1:23" ht="15" thickBot="1">
+    <row r="13" spans="1:23" ht="15.75" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -3635,7 +3650,7 @@
       <c r="V13" s="13"/>
       <c r="W13" s="14"/>
     </row>
-    <row r="14" spans="1:23" ht="15" thickBot="1">
+    <row r="14" spans="1:23" ht="15.75" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -3702,7 +3717,7 @@
       <c r="V14" s="13"/>
       <c r="W14" s="14"/>
     </row>
-    <row r="15" spans="1:23" ht="15" thickBot="1">
+    <row r="15" spans="1:23" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -3769,7 +3784,7 @@
       <c r="V15" s="13"/>
       <c r="W15" s="14"/>
     </row>
-    <row r="16" spans="1:23" ht="15" thickBot="1">
+    <row r="16" spans="1:23" ht="15.75" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -3836,7 +3851,7 @@
       <c r="V16" s="13"/>
       <c r="W16" s="14"/>
     </row>
-    <row r="17" spans="1:23" ht="15" thickBot="1">
+    <row r="17" spans="1:23" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -3903,41 +3918,41 @@
       <c r="V17" s="15"/>
       <c r="W17" s="16"/>
     </row>
-    <row r="18" spans="1:23" ht="28.2" thickBot="1">
+    <row r="18" spans="1:23" ht="26.25" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
       <c r="B18" s="254" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="218" t="s">
+      <c r="C18" s="210" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="172" t="s">
+      <c r="D18" s="171" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="173" t="s">
+      <c r="E18" s="172" t="s">
         <v>296</v>
       </c>
-      <c r="F18" s="174" t="s">
+      <c r="F18" s="173" t="s">
         <v>184</v>
       </c>
-      <c r="G18" s="175" t="s">
+      <c r="G18" s="174" t="s">
         <v>199</v>
       </c>
-      <c r="H18" s="176" t="s">
+      <c r="H18" s="175" t="s">
         <v>198</v>
       </c>
-      <c r="I18" s="177" t="s">
+      <c r="I18" s="176" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="174" t="s">
+      <c r="J18" s="173" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="175">
+      <c r="K18" s="174">
         <v>10</v>
       </c>
-      <c r="L18" s="175">
+      <c r="L18" s="174">
         <v>30</v>
       </c>
       <c r="M18" s="42">
@@ -3951,10 +3966,10 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="178" t="s">
+      <c r="P18" s="177" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="179">
+      <c r="Q18" s="178">
         <v>6.9699999999999998E-2</v>
       </c>
       <c r="R18" s="44">
@@ -3968,25 +3983,25 @@
         <f t="shared" si="3"/>
         <v>2.0909999999999997</v>
       </c>
-      <c r="U18" s="180"/>
-      <c r="V18" s="180"/>
-      <c r="W18" s="232"/>
-    </row>
-    <row r="19" spans="1:23" ht="16.2" thickBot="1">
+      <c r="U18" s="179"/>
+      <c r="V18" s="179"/>
+      <c r="W18" s="224"/>
+    </row>
+    <row r="19" spans="1:23" ht="16.5" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
       <c r="B19" s="255"/>
-      <c r="C19" s="262" t="s">
+      <c r="C19" s="229" t="s">
         <v>220</v>
       </c>
-      <c r="D19" s="263" t="s">
+      <c r="D19" s="230" t="s">
         <v>221</v>
       </c>
-      <c r="E19" s="263" t="s">
+      <c r="E19" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="263" t="s">
+      <c r="F19" s="230" t="s">
         <v>222</v>
       </c>
       <c r="G19" s="49" t="s">
@@ -3998,7 +4013,7 @@
       <c r="I19" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="263" t="s">
+      <c r="J19" s="230" t="s">
         <v>22</v>
       </c>
       <c r="K19" s="49">
@@ -4007,43 +4022,43 @@
       <c r="L19" s="49">
         <v>50</v>
       </c>
-      <c r="M19" s="264">
+      <c r="M19" s="231">
         <v>2</v>
       </c>
-      <c r="N19" s="264">
+      <c r="N19" s="231">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="264">
+      <c r="O19" s="231">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="265" t="s">
+      <c r="P19" s="232" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="266">
+      <c r="Q19" s="233">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="R19" s="267">
+      <c r="R19" s="234">
         <f t="shared" si="2"/>
         <v>0.39399999999999996</v>
       </c>
-      <c r="S19" s="267">
+      <c r="S19" s="234">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="T19" s="267">
+      <c r="T19" s="234">
         <f t="shared" si="3"/>
         <v>1.97</v>
       </c>
-      <c r="U19" s="268"/>
-      <c r="V19" s="269" t="s">
+      <c r="U19" s="235"/>
+      <c r="V19" s="236" t="s">
         <v>293</v>
       </c>
-      <c r="W19" s="270" t="s">
+      <c r="W19" s="237" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15" thickBot="1">
+    <row r="20" spans="1:23" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -4112,7 +4127,7 @@
       <c r="V20" s="11"/>
       <c r="W20" s="12"/>
     </row>
-    <row r="21" spans="1:23" ht="15" thickBot="1">
+    <row r="21" spans="1:23" ht="15.75" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -4158,7 +4173,7 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P21" s="195" t="s">
+      <c r="P21" s="194" t="s">
         <v>153</v>
       </c>
       <c r="Q21" s="43">
@@ -4181,7 +4196,7 @@
       </c>
       <c r="W21" s="14"/>
     </row>
-    <row r="22" spans="1:23" ht="15" thickBot="1">
+    <row r="22" spans="1:23" ht="15.75" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -4248,7 +4263,7 @@
       <c r="V22" s="13"/>
       <c r="W22" s="14"/>
     </row>
-    <row r="23" spans="1:23" ht="15" thickBot="1">
+    <row r="23" spans="1:23" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -4315,291 +4330,291 @@
       <c r="V23" s="15"/>
       <c r="W23" s="16"/>
     </row>
-    <row r="24" spans="1:23" ht="28.2" thickBot="1">
+    <row r="24" spans="1:23" ht="26.25" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="161" t="s">
+      <c r="B24" s="160" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="219" t="s">
+      <c r="C24" s="211" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="191" t="s">
+      <c r="D24" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="192" t="s">
+      <c r="E24" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="192" t="s">
+      <c r="F24" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="193" t="s">
+      <c r="G24" s="192" t="s">
         <v>146</v>
       </c>
-      <c r="H24" s="193" t="s">
+      <c r="H24" s="192" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="192" t="s">
+      <c r="I24" s="191" t="s">
         <v>145</v>
       </c>
-      <c r="J24" s="192" t="s">
+      <c r="J24" s="191" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="192">
+      <c r="K24" s="191">
         <v>42</v>
       </c>
-      <c r="L24" s="192">
+      <c r="L24" s="191">
         <v>162</v>
       </c>
-      <c r="M24" s="194">
+      <c r="M24" s="193">
         <v>8</v>
       </c>
-      <c r="N24" s="194">
+      <c r="N24" s="193">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="194">
+      <c r="O24" s="193">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="195" t="s">
+      <c r="P24" s="194" t="s">
         <v>153</v>
       </c>
-      <c r="Q24" s="196">
+      <c r="Q24" s="195">
         <v>3.68</v>
       </c>
-      <c r="R24" s="197">
+      <c r="R24" s="196">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="197">
+      <c r="S24" s="196">
         <v>3.68</v>
       </c>
-      <c r="T24" s="197">
+      <c r="T24" s="196">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="198" t="s">
+      <c r="U24" s="197" t="s">
         <v>247</v>
       </c>
-      <c r="V24" s="199" t="s">
+      <c r="V24" s="198" t="s">
         <v>293</v>
       </c>
-      <c r="W24" s="233">
+      <c r="W24" s="225">
         <v>3.68</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="28.2" thickBot="1">
+    <row r="25" spans="1:23" ht="26.25" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="222" t="s">
+      <c r="B25" s="214" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="220" t="s">
+      <c r="C25" s="212" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="207" t="s">
+      <c r="D25" s="199" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="208" t="s">
+      <c r="E25" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="208" t="s">
+      <c r="F25" s="200" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="209" t="s">
+      <c r="G25" s="201" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="210" t="s">
+      <c r="H25" s="202" t="s">
         <v>123</v>
       </c>
-      <c r="I25" s="211" t="s">
+      <c r="I25" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="208" t="s">
+      <c r="J25" s="200" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="208">
+      <c r="K25" s="200">
         <v>10</v>
       </c>
-      <c r="L25" s="208">
+      <c r="L25" s="200">
         <v>30</v>
       </c>
-      <c r="M25" s="212">
+      <c r="M25" s="204">
         <v>1</v>
       </c>
-      <c r="N25" s="212">
+      <c r="N25" s="204">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="212">
+      <c r="O25" s="204">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="213" t="s">
+      <c r="P25" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="214">
+      <c r="Q25" s="206">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="R25" s="215">
+      <c r="R25" s="207">
         <f t="shared" si="2"/>
         <v>0.59699999999999998</v>
       </c>
-      <c r="S25" s="215">
+      <c r="S25" s="207">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="T25" s="215">
+      <c r="T25" s="207">
         <f t="shared" si="3"/>
         <v>1.7910000000000001</v>
       </c>
-      <c r="U25" s="216"/>
-      <c r="V25" s="216"/>
-      <c r="W25" s="217"/>
-    </row>
-    <row r="26" spans="1:23" ht="28.2" thickBot="1">
+      <c r="U25" s="208"/>
+      <c r="V25" s="208"/>
+      <c r="W25" s="209"/>
+    </row>
+    <row r="26" spans="1:23" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
       <c r="B26" s="252" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="221" t="s">
+      <c r="C26" s="262" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="183" t="s">
+      <c r="D26" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="183" t="s">
+      <c r="E26" s="263" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="183" t="s">
+      <c r="F26" s="263" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="200" t="s">
+      <c r="G26" s="264" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="265" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="200" t="s">
+      <c r="I26" s="264" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="183" t="s">
+      <c r="J26" s="263" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="183">
+      <c r="K26" s="263">
         <v>7</v>
       </c>
-      <c r="L26" s="183">
+      <c r="L26" s="263">
         <v>22</v>
       </c>
-      <c r="M26" s="202">
+      <c r="M26" s="266">
         <v>1</v>
       </c>
-      <c r="N26" s="202">
+      <c r="N26" s="266">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O26" s="187">
+      <c r="O26" s="267">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P26" s="203" t="s">
+      <c r="P26" s="268" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="204">
+      <c r="Q26" s="269">
         <v>0.21840000000000001</v>
       </c>
-      <c r="R26" s="205">
+      <c r="R26" s="270">
         <f>Q26*K26</f>
         <v>1.5288000000000002</v>
       </c>
-      <c r="S26" s="205">
+      <c r="S26" s="270">
         <v>0.1774</v>
       </c>
-      <c r="T26" s="190">
+      <c r="T26" s="271">
         <f t="shared" si="3"/>
         <v>3.9028</v>
       </c>
-      <c r="U26" s="206"/>
-      <c r="V26" s="181" t="s">
+      <c r="U26" s="272"/>
+      <c r="V26" s="273" t="s">
         <v>293</v>
       </c>
-      <c r="W26" s="234"/>
-    </row>
-    <row r="27" spans="1:23" ht="28.2" thickBot="1">
+      <c r="W26" s="274"/>
+    </row>
+    <row r="27" spans="1:23" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
       <c r="B27" s="252"/>
-      <c r="C27" s="143" t="s">
+      <c r="C27" s="161" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="144" t="s">
+      <c r="D27" s="116" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="145" t="s">
+      <c r="E27" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="145" t="s">
+      <c r="F27" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="146" t="s">
+      <c r="G27" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="147" t="s">
+      <c r="H27" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="146" t="s">
+      <c r="I27" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="145" t="s">
+      <c r="J27" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="145">
+      <c r="K27" s="85">
         <v>15</v>
       </c>
-      <c r="L27" s="145">
+      <c r="L27" s="85">
         <v>45</v>
       </c>
-      <c r="M27" s="148">
+      <c r="M27" s="46">
         <v>2</v>
       </c>
-      <c r="N27" s="148">
+      <c r="N27" s="46">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O27" s="148">
+      <c r="O27" s="46">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P27" s="149" t="s">
+      <c r="P27" s="275" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="150">
+      <c r="Q27" s="163">
         <v>0.1085</v>
       </c>
-      <c r="R27" s="151">
+      <c r="R27" s="164">
         <f t="shared" si="2"/>
         <v>1.6274999999999999</v>
       </c>
-      <c r="S27" s="151">
+      <c r="S27" s="164">
         <v>0.1085</v>
       </c>
-      <c r="T27" s="151">
+      <c r="T27" s="164">
         <f t="shared" si="3"/>
         <v>4.8825000000000003</v>
       </c>
-      <c r="U27" s="152"/>
-      <c r="V27" s="152" t="s">
+      <c r="U27" s="169"/>
+      <c r="V27" s="169" t="s">
         <v>293</v>
       </c>
-      <c r="W27" s="153"/>
-    </row>
-    <row r="28" spans="1:23" ht="28.2" thickBot="1">
+      <c r="W27" s="166"/>
+    </row>
+    <row r="28" spans="1:23" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -4645,7 +4660,7 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="182" t="s">
+      <c r="P28" s="181" t="s">
         <v>16</v>
       </c>
       <c r="Q28" s="50">
@@ -4666,7 +4681,7 @@
       <c r="V28" s="26"/>
       <c r="W28" s="27"/>
     </row>
-    <row r="29" spans="1:23" ht="15" thickBot="1">
+    <row r="29" spans="1:23" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -4735,7 +4750,7 @@
       <c r="V29" s="11"/>
       <c r="W29" s="12"/>
     </row>
-    <row r="30" spans="1:23" ht="15" thickBot="1">
+    <row r="30" spans="1:23" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -4788,7 +4803,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="R30" s="91">
-        <f t="shared" si="2"/>
+        <f>Q30*K30</f>
         <v>0.16999999999999998</v>
       </c>
       <c r="S30" s="91">
@@ -4802,7 +4817,7 @@
       <c r="V30" s="13"/>
       <c r="W30" s="14"/>
     </row>
-    <row r="31" spans="1:23" ht="15" thickBot="1">
+    <row r="31" spans="1:23" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -4869,7 +4884,7 @@
       <c r="V31" s="13"/>
       <c r="W31" s="14"/>
     </row>
-    <row r="32" spans="1:23" ht="15" thickBot="1">
+    <row r="32" spans="1:23" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -4936,7 +4951,7 @@
       <c r="V32" s="13"/>
       <c r="W32" s="14"/>
     </row>
-    <row r="33" spans="1:23" ht="15" thickBot="1">
+    <row r="33" spans="1:23" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -5003,149 +5018,149 @@
       <c r="V33" s="15"/>
       <c r="W33" s="16"/>
     </row>
-    <row r="34" spans="1:23" ht="16.2" thickBot="1">
+    <row r="34" spans="1:23" ht="16.5" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
       <c r="B34" s="252" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="221" t="s">
+      <c r="C34" s="213" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="183" t="s">
+      <c r="D34" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="184" t="s">
+      <c r="E34" s="183" t="s">
         <v>91</v>
       </c>
-      <c r="F34" s="184" t="s">
+      <c r="F34" s="183" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="185" t="s">
+      <c r="G34" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="186" t="s">
+      <c r="H34" s="185" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="185" t="s">
+      <c r="I34" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="184" t="s">
+      <c r="J34" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="184">
+      <c r="K34" s="183">
         <v>11</v>
       </c>
-      <c r="L34" s="184">
+      <c r="L34" s="183">
         <v>42</v>
       </c>
-      <c r="M34" s="187">
+      <c r="M34" s="186">
         <v>2</v>
       </c>
-      <c r="N34" s="187">
+      <c r="N34" s="186">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="187">
+      <c r="O34" s="186">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="188" t="s">
+      <c r="P34" s="187" t="s">
         <v>135</v>
       </c>
-      <c r="Q34" s="189">
+      <c r="Q34" s="188">
         <v>0.318</v>
       </c>
-      <c r="R34" s="190">
+      <c r="R34" s="189">
         <f t="shared" si="2"/>
         <v>3.4980000000000002</v>
       </c>
-      <c r="S34" s="190">
+      <c r="S34" s="189">
         <v>0.4148</v>
       </c>
-      <c r="T34" s="190">
+      <c r="T34" s="189">
         <f t="shared" si="3"/>
         <v>17.421600000000002</v>
       </c>
-      <c r="U34" s="181"/>
-      <c r="V34" s="181" t="s">
+      <c r="U34" s="180"/>
+      <c r="V34" s="180" t="s">
         <v>293</v>
       </c>
-      <c r="W34" s="235" t="s">
+      <c r="W34" s="226" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="28.2" thickBot="1">
+    <row r="35" spans="1:23" ht="26.25" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
       <c r="B35" s="252"/>
-      <c r="C35" s="143" t="s">
+      <c r="C35" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="144" t="s">
+      <c r="D35" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="145" t="s">
+      <c r="E35" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="145" t="s">
+      <c r="F35" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="146" t="s">
+      <c r="G35" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="H35" s="146" t="s">
+      <c r="H35" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="I35" s="146" t="s">
+      <c r="I35" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="145" t="s">
+      <c r="J35" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="146">
+      <c r="K35" s="40">
         <v>6</v>
       </c>
-      <c r="L35" s="146">
+      <c r="L35" s="40">
         <v>21</v>
       </c>
-      <c r="M35" s="148">
+      <c r="M35" s="46">
         <v>1</v>
       </c>
-      <c r="N35" s="148">
+      <c r="N35" s="46">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="148">
+      <c r="O35" s="46">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="149" t="s">
+      <c r="P35" s="275" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="150">
+      <c r="Q35" s="163">
         <v>0.40610000000000002</v>
       </c>
-      <c r="R35" s="151">
+      <c r="R35" s="164">
         <f t="shared" si="2"/>
         <v>2.4366000000000003</v>
       </c>
-      <c r="S35" s="151">
+      <c r="S35" s="164">
         <v>0.3528</v>
       </c>
-      <c r="T35" s="151">
+      <c r="T35" s="164">
         <f t="shared" si="3"/>
         <v>7.4088000000000003</v>
       </c>
-      <c r="U35" s="152"/>
-      <c r="V35" s="152" t="s">
+      <c r="U35" s="169"/>
+      <c r="V35" s="169" t="s">
         <v>293</v>
       </c>
-      <c r="W35" s="153"/>
-    </row>
-    <row r="36" spans="1:23" ht="15" thickBot="1">
+      <c r="W35" s="166"/>
+    </row>
+    <row r="36" spans="1:23" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -5180,41 +5195,41 @@
       <c r="L36" s="146">
         <v>21</v>
       </c>
-      <c r="M36" s="148">
+      <c r="M36" s="147">
         <v>1</v>
       </c>
-      <c r="N36" s="148">
+      <c r="N36" s="147">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O36" s="148">
+      <c r="O36" s="147">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P36" s="149" t="s">
+      <c r="P36" s="148" t="s">
         <v>153</v>
       </c>
-      <c r="Q36" s="154">
+      <c r="Q36" s="153">
         <v>8</v>
       </c>
-      <c r="R36" s="151">
+      <c r="R36" s="150">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="S36" s="151">
+      <c r="S36" s="150">
         <v>8</v>
       </c>
-      <c r="T36" s="151">
+      <c r="T36" s="150">
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="U36" s="155"/>
-      <c r="V36" s="152" t="s">
+      <c r="U36" s="154"/>
+      <c r="V36" s="151" t="s">
         <v>293</v>
       </c>
-      <c r="W36" s="156"/>
-    </row>
-    <row r="37" spans="1:23" ht="15" thickBot="1">
+      <c r="W36" s="155"/>
+    </row>
+    <row r="37" spans="1:23" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -5263,7 +5278,7 @@
       <c r="P37" s="82" t="s">
         <v>153</v>
       </c>
-      <c r="Q37" s="159">
+      <c r="Q37" s="158">
         <v>4.76</v>
       </c>
       <c r="R37" s="94">
@@ -5273,21 +5288,21 @@
       <c r="S37" s="94">
         <v>4.76</v>
       </c>
-      <c r="T37" s="160">
+      <c r="T37" s="159">
         <f t="shared" si="3"/>
         <v>195.16</v>
       </c>
       <c r="U37" s="83" t="s">
         <v>295</v>
       </c>
-      <c r="V37" s="152" t="s">
+      <c r="V37" s="151" t="s">
         <v>293</v>
       </c>
-      <c r="W37" s="236">
+      <c r="W37" s="227">
         <v>4.76</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="15" thickBot="1">
+    <row r="38" spans="1:23" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -5354,7 +5369,7 @@
       <c r="V38" s="19"/>
       <c r="W38" s="14"/>
     </row>
-    <row r="39" spans="1:23" ht="15" thickBot="1">
+    <row r="39" spans="1:23" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -5421,7 +5436,7 @@
       <c r="V39" s="19"/>
       <c r="W39" s="14"/>
     </row>
-    <row r="40" spans="1:23" ht="15" thickBot="1">
+    <row r="40" spans="1:23" ht="15.75" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -5454,43 +5469,43 @@
       <c r="L40" s="146">
         <v>22</v>
       </c>
-      <c r="M40" s="148">
+      <c r="M40" s="147">
         <v>1</v>
       </c>
-      <c r="N40" s="148">
+      <c r="N40" s="147">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="148">
+      <c r="O40" s="147">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="158" t="s">
+      <c r="P40" s="157" t="s">
         <v>242</v>
       </c>
-      <c r="Q40" s="150">
+      <c r="Q40" s="149">
         <v>0.8</v>
       </c>
-      <c r="R40" s="151">
+      <c r="R40" s="150">
         <f t="shared" si="2"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="S40" s="151">
+      <c r="S40" s="150">
         <v>0.8</v>
       </c>
-      <c r="T40" s="151">
+      <c r="T40" s="150">
         <f t="shared" si="3"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="U40" s="157" t="s">
+      <c r="U40" s="156" t="s">
         <v>278</v>
       </c>
-      <c r="V40" s="152" t="s">
+      <c r="V40" s="151" t="s">
         <v>293</v>
       </c>
-      <c r="W40" s="153"/>
-    </row>
-    <row r="41" spans="1:23" ht="15" thickBot="1">
+      <c r="W40" s="152"/>
+    </row>
+    <row r="41" spans="1:23" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
@@ -5504,7 +5519,7 @@
       <c r="E41" s="145" t="s">
         <v>283</v>
       </c>
-      <c r="F41" s="168" t="s">
+      <c r="F41" s="167" t="s">
         <v>284</v>
       </c>
       <c r="G41" s="146" t="s">
@@ -5525,41 +5540,41 @@
       <c r="L41" s="146">
         <v>30</v>
       </c>
-      <c r="M41" s="148">
+      <c r="M41" s="147">
         <v>1</v>
       </c>
-      <c r="N41" s="148">
+      <c r="N41" s="147">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="148">
+      <c r="O41" s="147">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="149" t="s">
+      <c r="P41" s="148" t="s">
         <v>135</v>
       </c>
-      <c r="Q41" s="150">
+      <c r="Q41" s="149">
         <v>1</v>
       </c>
-      <c r="R41" s="151">
+      <c r="R41" s="150">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S41" s="151">
+      <c r="S41" s="150">
         <v>1</v>
       </c>
-      <c r="T41" s="151">
+      <c r="T41" s="150">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="U41" s="169"/>
-      <c r="V41" s="152" t="s">
+      <c r="U41" s="168"/>
+      <c r="V41" s="151" t="s">
         <v>293</v>
       </c>
-      <c r="W41" s="153"/>
-    </row>
-    <row r="42" spans="1:23" ht="28.2" thickBot="1">
+      <c r="W41" s="152"/>
+    </row>
+    <row r="42" spans="1:23" ht="26.25" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
@@ -5605,28 +5620,28 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P42" s="223" t="s">
+      <c r="P42" s="215" t="s">
         <v>16</v>
       </c>
       <c r="Q42" s="50">
-        <v>5.6099999999999997E-2</v>
+        <v>5.6399999999999999E-2</v>
       </c>
       <c r="R42" s="99">
         <f t="shared" si="2"/>
-        <v>0.56099999999999994</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="S42" s="99">
-        <v>5.6099999999999997E-2</v>
+        <v>5.6399999999999999E-2</v>
       </c>
       <c r="T42" s="99">
         <f t="shared" si="3"/>
-        <v>1.6829999999999998</v>
-      </c>
-      <c r="U42" s="224"/>
-      <c r="V42" s="224"/>
+        <v>1.6919999999999999</v>
+      </c>
+      <c r="U42" s="216"/>
+      <c r="V42" s="216"/>
       <c r="W42" s="27"/>
     </row>
-    <row r="43" spans="1:23" ht="15" thickBot="1">
+    <row r="43" spans="1:23" ht="15.75" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
@@ -5695,7 +5710,7 @@
       <c r="V43" s="20"/>
       <c r="W43" s="12"/>
     </row>
-    <row r="44" spans="1:23" ht="28.2" thickBot="1">
+    <row r="44" spans="1:23" ht="26.25" thickBot="1">
       <c r="A44" s="6">
         <v>42</v>
       </c>
@@ -5762,7 +5777,7 @@
       <c r="V44" s="24"/>
       <c r="W44" s="14"/>
     </row>
-    <row r="45" spans="1:23" ht="15" thickBot="1">
+    <row r="45" spans="1:23" ht="15.75" thickBot="1">
       <c r="A45" s="6">
         <v>43</v>
       </c>
@@ -5829,12 +5844,12 @@
       <c r="V45" s="25"/>
       <c r="W45" s="14"/>
     </row>
-    <row r="46" spans="1:23" ht="15" thickBot="1">
+    <row r="46" spans="1:23" ht="15.75" thickBot="1">
       <c r="A46" s="6">
         <v>44</v>
       </c>
       <c r="B46" s="252"/>
-      <c r="C46" s="162" t="s">
+      <c r="C46" s="161" t="s">
         <v>272</v>
       </c>
       <c r="D46" s="116" t="s">
@@ -5875,28 +5890,28 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P46" s="163" t="s">
+      <c r="P46" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="Q46" s="164">
-        <v>9.3600000000000003E-2</v>
-      </c>
-      <c r="R46" s="165">
+      <c r="Q46" s="163">
+        <v>8.8900000000000007E-2</v>
+      </c>
+      <c r="R46" s="164">
         <f t="shared" si="2"/>
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="S46" s="165">
-        <v>9.3600000000000003E-2</v>
-      </c>
-      <c r="T46" s="165">
+        <v>0.44450000000000001</v>
+      </c>
+      <c r="S46" s="164">
+        <v>8.8900000000000007E-2</v>
+      </c>
+      <c r="T46" s="164">
         <f t="shared" si="3"/>
-        <v>2.34</v>
-      </c>
-      <c r="U46" s="166"/>
-      <c r="V46" s="170"/>
-      <c r="W46" s="167"/>
-    </row>
-    <row r="47" spans="1:23" ht="15" thickBot="1">
+        <v>2.2225000000000001</v>
+      </c>
+      <c r="U46" s="165"/>
+      <c r="V46" s="169"/>
+      <c r="W46" s="166"/>
+    </row>
+    <row r="47" spans="1:23" ht="15.75" thickBot="1">
       <c r="A47" s="6">
         <v>45</v>
       </c>
@@ -5910,7 +5925,7 @@
       <c r="E47" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="171">
+      <c r="F47" s="170">
         <v>61300611121</v>
       </c>
       <c r="G47" s="41" t="s">
@@ -5963,7 +5978,7 @@
       <c r="V47" s="25"/>
       <c r="W47" s="14"/>
     </row>
-    <row r="48" spans="1:23" ht="124.8" thickBot="1">
+    <row r="48" spans="1:23" ht="115.5" thickBot="1">
       <c r="A48" s="6">
         <v>46</v>
       </c>
@@ -6026,41 +6041,41 @@
       <c r="V48" s="107"/>
       <c r="W48" s="108"/>
     </row>
-    <row r="49" spans="1:23" ht="28.2" thickBot="1">
+    <row r="49" spans="1:23" ht="26.25" thickBot="1">
       <c r="A49" s="6">
         <v>47</v>
       </c>
       <c r="B49" s="259" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="225" t="s">
+      <c r="C49" s="217" t="s">
         <v>249</v>
       </c>
-      <c r="D49" s="226" t="s">
+      <c r="D49" s="218" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="226" t="s">
+      <c r="E49" s="218" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="226" t="s">
+      <c r="F49" s="218" t="s">
         <v>248</v>
       </c>
-      <c r="G49" s="226" t="s">
+      <c r="G49" s="218" t="s">
         <v>144</v>
       </c>
-      <c r="H49" s="226" t="s">
+      <c r="H49" s="218" t="s">
         <v>144</v>
       </c>
-      <c r="I49" s="226" t="s">
+      <c r="I49" s="218" t="s">
         <v>144</v>
       </c>
-      <c r="J49" s="226" t="s">
+      <c r="J49" s="218" t="s">
         <v>144</v>
       </c>
-      <c r="K49" s="226" t="s">
+      <c r="K49" s="218" t="s">
         <v>144</v>
       </c>
-      <c r="L49" s="226" t="s">
+      <c r="L49" s="218" t="s">
         <v>144</v>
       </c>
       <c r="M49" s="58">
@@ -6074,29 +6089,29 @@
         <f>M49*20</f>
         <v>20</v>
       </c>
-      <c r="P49" s="227" t="s">
+      <c r="P49" s="219" t="s">
         <v>242</v>
       </c>
-      <c r="Q49" s="228">
+      <c r="Q49" s="220">
         <v>0.2</v>
       </c>
-      <c r="R49" s="229">
+      <c r="R49" s="221">
         <f>Q49*N49</f>
         <v>1</v>
       </c>
-      <c r="S49" s="228">
+      <c r="S49" s="220">
         <v>0.2</v>
       </c>
       <c r="T49" s="38">
         <f>S49*O49</f>
         <v>4</v>
       </c>
-      <c r="U49" s="230"/>
-      <c r="V49" s="230"/>
-      <c r="W49" s="231"/>
-    </row>
-    <row r="50" spans="1:23" ht="15" thickBot="1">
-      <c r="A50" s="237">
+      <c r="U49" s="222"/>
+      <c r="V49" s="222"/>
+      <c r="W49" s="223"/>
+    </row>
+    <row r="50" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A50" s="228">
         <v>48</v>
       </c>
       <c r="B50" s="260"/>
@@ -6164,7 +6179,7 @@
       <c r="V50" s="107"/>
       <c r="W50" s="121"/>
     </row>
-    <row r="51" spans="1:23" ht="15.6">
+    <row r="51" spans="1:23" ht="15.75">
       <c r="A51" s="1"/>
       <c r="C51" s="21"/>
       <c r="D51" s="8"/>
@@ -6184,18 +6199,18 @@
       <c r="Q51" s="18"/>
       <c r="R51" s="128">
         <f>SUM(R3:R50)</f>
-        <v>332.08725999999996</v>
+        <v>332.06675999999999</v>
       </c>
       <c r="S51" s="128"/>
       <c r="T51" s="90">
         <f>SUM(T3:T50)</f>
-        <v>1216.1183999999998</v>
+        <v>1216.0299</v>
       </c>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
       <c r="W51" s="7"/>
     </row>
-    <row r="52" spans="1:23" ht="16.2" thickBot="1">
+    <row r="52" spans="1:23" ht="16.5" thickBot="1">
       <c r="A52" s="1"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -6212,18 +6227,18 @@
       <c r="Q52" s="29"/>
       <c r="R52" s="131">
         <f>R51/5</f>
-        <v>66.417451999999997</v>
+        <v>66.413352000000003</v>
       </c>
       <c r="S52" s="131"/>
       <c r="T52" s="31">
         <f>T51/20</f>
-        <v>60.805919999999993</v>
+        <v>60.801495000000003</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7"/>
     </row>
-    <row r="53" spans="1:23" ht="15.6">
+    <row r="53" spans="1:23" ht="15.75">
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -6249,7 +6264,7 @@
       <c r="V53" s="7"/>
       <c r="W53" s="7"/>
     </row>
-    <row r="54" spans="1:23" ht="15.6">
+    <row r="54" spans="1:23" ht="15.75">
       <c r="A54" s="1"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -6275,7 +6290,7 @@
       <c r="V54" s="7"/>
       <c r="W54" s="7"/>
     </row>
-    <row r="55" spans="1:23" ht="16.2" thickBot="1">
+    <row r="55" spans="1:23" ht="16.5" thickBot="1">
       <c r="A55" s="1"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -6289,12 +6304,12 @@
       <c r="Q55" s="29"/>
       <c r="R55" s="133">
         <f>SUM(R52:R54)</f>
-        <v>92.197451999999998</v>
+        <v>92.193352000000004</v>
       </c>
       <c r="S55" s="133"/>
       <c r="T55" s="30">
         <f>SUM(T52:T54)</f>
-        <v>154.79592</v>
+        <v>154.791495</v>
       </c>
     </row>
     <row r="56" spans="1:23">
@@ -6578,10 +6593,9 @@
     <hyperlink ref="P40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
     <hyperlink ref="P23" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
     <hyperlink ref="P22" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="P21" r:id="rId44" display="Aliexpress" xr:uid="{5AFB32F5-5BD1-454E-973A-39F7F52EDCE6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId45"/>
+  <pageSetup orientation="portrait" r:id="rId44"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FFD8AB-0A23-42BE-AAA9-84ADC396A7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FE2C59-4A88-4875-A9AF-6DAEAF3A04F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="300">
   <si>
     <t>S. No.</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>J2</t>
-  </si>
-  <si>
-    <t>Total with Shipping</t>
   </si>
   <si>
     <t>Quantity 5</t>
@@ -429,9 +426,6 @@
     <t>C98220</t>
   </si>
   <si>
-    <t>C2869734</t>
-  </si>
-  <si>
     <t xml:space="preserve">Torex </t>
   </si>
   <si>
@@ -939,6 +933,9 @@
   </si>
   <si>
     <t>Out of stock. Will be arranged by custom supplier</t>
+  </si>
+  <si>
+    <t>Total with Shipping Single Board</t>
   </si>
 </sst>
 </file>
@@ -1693,7 +1690,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1776,9 +1773,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2087,12 +2081,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2237,9 +2225,6 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2394,6 +2379,48 @@
     <xf numFmtId="165" fontId="25" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2466,46 +2493,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2793,7 +2784,7 @@
     <col min="4" max="4" width="32.28515625" style="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -2814,31 +2805,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A1" s="244" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="245"/>
-      <c r="D1" s="245"/>
-      <c r="E1" s="245"/>
-      <c r="F1" s="245"/>
-      <c r="G1" s="245"/>
-      <c r="H1" s="245"/>
-      <c r="I1" s="245"/>
-      <c r="J1" s="245"/>
-      <c r="K1" s="245"/>
-      <c r="L1" s="245"/>
-      <c r="M1" s="245"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="245"/>
-      <c r="P1" s="245"/>
-      <c r="Q1" s="245"/>
-      <c r="R1" s="245"/>
-      <c r="S1" s="245"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="245"/>
-      <c r="V1" s="245"/>
-      <c r="W1" s="246"/>
+      <c r="A1" s="254" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="255"/>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
+      <c r="F1" s="255"/>
+      <c r="G1" s="255"/>
+      <c r="H1" s="255"/>
+      <c r="I1" s="255"/>
+      <c r="J1" s="255"/>
+      <c r="K1" s="255"/>
+      <c r="L1" s="255"/>
+      <c r="M1" s="255"/>
+      <c r="N1" s="255"/>
+      <c r="O1" s="255"/>
+      <c r="P1" s="255"/>
+      <c r="Q1" s="255"/>
+      <c r="R1" s="255"/>
+      <c r="S1" s="255"/>
+      <c r="T1" s="255"/>
+      <c r="U1" s="255"/>
+      <c r="V1" s="255"/>
+      <c r="W1" s="256"/>
     </row>
     <row r="2" spans="1:23" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2872,40 +2863,40 @@
         <v>9</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="123" t="s">
-        <v>246</v>
+        <v>46</v>
+      </c>
+      <c r="L2" s="122" t="s">
+        <v>244</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="Q2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="S2" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="T2" s="123" t="s">
-        <v>245</v>
+        <v>242</v>
+      </c>
+      <c r="T2" s="122" t="s">
+        <v>243</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="123" t="s">
-        <v>294</v>
+      <c r="V2" s="122" t="s">
+        <v>292</v>
       </c>
       <c r="W2" s="5" t="s">
         <v>13</v>
@@ -2915,64 +2906,64 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="251" t="s">
+      <c r="B3" s="261" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="116" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="117" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" s="61" t="s">
+      <c r="F3" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="34">
         <v>40</v>
       </c>
-      <c r="L3" s="35">
+      <c r="L3" s="34">
         <v>100</v>
       </c>
-      <c r="M3" s="36">
+      <c r="M3" s="35">
         <v>4</v>
       </c>
-      <c r="N3" s="36">
+      <c r="N3" s="35">
         <f>M3*5</f>
         <v>20</v>
       </c>
-      <c r="O3" s="36">
+      <c r="O3" s="35">
         <f>M3*20</f>
         <v>80</v>
       </c>
-      <c r="P3" s="62" t="s">
+      <c r="P3" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="37">
+      <c r="Q3" s="36">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="R3" s="38">
+      <c r="R3" s="37">
         <f>Q3*K3</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="S3" s="38">
+      <c r="S3" s="37">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="T3" s="38">
+      <c r="T3" s="37">
         <f>S3*L3</f>
         <v>1.3599999999999999</v>
       </c>
@@ -2984,62 +2975,62 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="252"/>
-      <c r="C4" s="63" t="s">
+      <c r="B4" s="262"/>
+      <c r="C4" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="85" t="s">
+      <c r="D4" s="84" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="I4" s="40" t="s">
+      <c r="G4" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="I4" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" s="41">
+      <c r="J4" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="40">
         <v>20</v>
       </c>
-      <c r="L4" s="41">
+      <c r="L4" s="40">
         <v>40</v>
       </c>
-      <c r="M4" s="65">
+      <c r="M4" s="64">
         <v>1</v>
       </c>
-      <c r="N4" s="65">
+      <c r="N4" s="64">
         <f t="shared" ref="N4:N48" si="0">M4*5</f>
         <v>5</v>
       </c>
-      <c r="O4" s="65">
+      <c r="O4" s="64">
         <f t="shared" ref="O4:O50" si="1">M4*20</f>
         <v>20</v>
       </c>
-      <c r="P4" s="66" t="s">
+      <c r="P4" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="43">
-        <v>2.0299999999999999E-2</v>
-      </c>
-      <c r="R4" s="91">
+      <c r="Q4" s="42">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="R4" s="90">
         <f t="shared" ref="R4:R47" si="2">Q4*K4</f>
-        <v>0.40599999999999997</v>
-      </c>
-      <c r="S4" s="91">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="S4" s="90">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="T4" s="91">
+      <c r="T4" s="90">
         <f t="shared" ref="T4:T47" si="3">S4*L4</f>
         <v>0.83199999999999996</v>
       </c>
@@ -3051,62 +3042,62 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="63" t="s">
+      <c r="B5" s="262"/>
+      <c r="C5" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="115" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="116" t="s">
-        <v>154</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="40">
         <v>100</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="40">
         <v>400</v>
       </c>
-      <c r="M5" s="65">
+      <c r="M5" s="64">
         <v>19</v>
       </c>
-      <c r="N5" s="65">
+      <c r="N5" s="64">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="O5" s="65">
+      <c r="O5" s="64">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="P5" s="66" t="s">
+      <c r="P5" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="42">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="R5" s="91">
+      <c r="R5" s="90">
         <f t="shared" si="2"/>
         <v>0.71000000000000008</v>
       </c>
-      <c r="S5" s="91">
+      <c r="S5" s="90">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="T5" s="91">
+      <c r="T5" s="90">
         <f t="shared" si="3"/>
         <v>2.8400000000000003</v>
       </c>
@@ -3118,62 +3109,62 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="252"/>
-      <c r="C6" s="63" t="s">
+      <c r="B6" s="262"/>
+      <c r="C6" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="E6" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="F6" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="I6" s="40" t="s">
+      <c r="G6" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="41">
+      <c r="J6" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="40">
         <v>100</v>
       </c>
-      <c r="L6" s="41">
+      <c r="L6" s="40">
         <v>200</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="64">
         <v>8</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="64">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="64">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P6" s="67" t="s">
+      <c r="P6" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="43">
+      <c r="Q6" s="42">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="R6" s="91">
+      <c r="R6" s="90">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="S6" s="91">
+      <c r="S6" s="90">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="T6" s="91">
+      <c r="T6" s="90">
         <f t="shared" si="3"/>
         <v>0.67999999999999994</v>
       </c>
@@ -3185,62 +3176,62 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="252"/>
-      <c r="C7" s="63" t="s">
+      <c r="B7" s="262"/>
+      <c r="C7" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="85" t="s">
+      <c r="F7" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="89" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="J7" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="H7" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="J7" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="K7" s="41">
+      <c r="K7" s="40">
         <v>100</v>
       </c>
-      <c r="L7" s="41">
+      <c r="L7" s="40">
         <v>100</v>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="64">
         <v>1</v>
       </c>
-      <c r="N7" s="65">
+      <c r="N7" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O7" s="65">
+      <c r="O7" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P7" s="88" t="s">
+      <c r="P7" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="43">
+      <c r="Q7" s="42">
         <v>1.4E-3</v>
       </c>
-      <c r="R7" s="91">
+      <c r="R7" s="90">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S7" s="91">
+      <c r="S7" s="90">
         <v>1.4E-3</v>
       </c>
-      <c r="T7" s="91">
+      <c r="T7" s="90">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
@@ -3252,62 +3243,62 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="252"/>
-      <c r="C8" s="63" t="s">
+      <c r="B8" s="262"/>
+      <c r="C8" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="116" t="s">
-        <v>213</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="41" t="s">
+      <c r="D8" s="115" t="s">
+        <v>211</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="I8" s="40" t="s">
+      <c r="G8" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="40">
         <v>150</v>
       </c>
-      <c r="L8" s="41">
+      <c r="L8" s="40">
         <v>600</v>
       </c>
-      <c r="M8" s="65">
+      <c r="M8" s="64">
         <v>29</v>
       </c>
-      <c r="N8" s="65">
+      <c r="N8" s="64">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="O8" s="65">
+      <c r="O8" s="64">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="P8" s="67" t="s">
+      <c r="P8" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="43">
+      <c r="Q8" s="42">
         <v>7.4000000000000003E-3</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="90">
         <f t="shared" si="2"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="90">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="T8" s="91">
+      <c r="T8" s="90">
         <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
@@ -3319,62 +3310,62 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="252"/>
-      <c r="C9" s="63" t="s">
+      <c r="B9" s="262"/>
+      <c r="C9" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="85" t="s">
+      <c r="E9" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="45">
+      <c r="J9" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="44">
         <v>10</v>
       </c>
-      <c r="L9" s="45">
+      <c r="L9" s="44">
         <v>30</v>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="64">
         <v>1</v>
       </c>
-      <c r="N9" s="65">
+      <c r="N9" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O9" s="65">
+      <c r="O9" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P9" s="67" t="s">
+      <c r="P9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="43">
+      <c r="Q9" s="42">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="R9" s="91">
+      <c r="R9" s="90">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
-      <c r="S9" s="91">
+      <c r="S9" s="90">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="T9" s="91">
+      <c r="T9" s="90">
         <f t="shared" si="3"/>
         <v>1.1099999999999999</v>
       </c>
@@ -3386,62 +3377,62 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="252"/>
-      <c r="C10" s="63" t="s">
+      <c r="B10" s="262"/>
+      <c r="C10" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="E10" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="64" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H10" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="I10" s="40" t="s">
+      <c r="G10" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" s="45">
+      <c r="J10" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="44">
         <v>100</v>
       </c>
-      <c r="L10" s="45">
+      <c r="L10" s="44">
         <v>200</v>
       </c>
-      <c r="M10" s="65">
+      <c r="M10" s="64">
         <v>6</v>
       </c>
-      <c r="N10" s="65">
+      <c r="N10" s="64">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="O10" s="65">
+      <c r="O10" s="64">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="P10" s="66" t="s">
+      <c r="P10" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="43">
+      <c r="Q10" s="42">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="R10" s="91">
+      <c r="R10" s="90">
         <f t="shared" si="2"/>
         <v>0.35000000000000003</v>
       </c>
-      <c r="S10" s="91">
+      <c r="S10" s="90">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="T10" s="91">
+      <c r="T10" s="90">
         <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
@@ -3453,62 +3444,62 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="252"/>
-      <c r="C11" s="63" t="s">
+      <c r="B11" s="262"/>
+      <c r="C11" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="116" t="s">
+      <c r="E11" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="40" t="s">
+      <c r="G11" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="I11" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" s="45">
+      <c r="J11" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="44">
         <v>100</v>
       </c>
-      <c r="L11" s="45">
+      <c r="L11" s="44">
         <v>350</v>
       </c>
-      <c r="M11" s="65">
+      <c r="M11" s="64">
         <v>16</v>
       </c>
-      <c r="N11" s="65">
+      <c r="N11" s="64">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="O11" s="65">
+      <c r="O11" s="64">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="P11" s="66" t="s">
+      <c r="P11" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="43">
+      <c r="Q11" s="42">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="R11" s="91">
+      <c r="R11" s="90">
         <f t="shared" si="2"/>
         <v>1.5599999999999998</v>
       </c>
-      <c r="S11" s="91">
+      <c r="S11" s="90">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="T11" s="91">
+      <c r="T11" s="90">
         <f t="shared" si="3"/>
         <v>5.46</v>
       </c>
@@ -3520,62 +3511,62 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="252"/>
-      <c r="C12" s="63" t="s">
+      <c r="B12" s="262"/>
+      <c r="C12" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="84" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="85" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>194</v>
-      </c>
-      <c r="I12" s="40" t="s">
+      <c r="G12" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="I12" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="K12" s="45">
+      <c r="J12" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="K12" s="44">
         <v>50</v>
       </c>
-      <c r="L12" s="45">
+      <c r="L12" s="44">
         <v>50</v>
       </c>
-      <c r="M12" s="65">
+      <c r="M12" s="64">
         <v>1</v>
       </c>
-      <c r="N12" s="65">
+      <c r="N12" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O12" s="65">
+      <c r="O12" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P12" s="92" t="s">
+      <c r="P12" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="43">
+      <c r="Q12" s="42">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="R12" s="91">
+      <c r="R12" s="90">
         <f t="shared" si="2"/>
         <v>0.245</v>
       </c>
-      <c r="S12" s="91">
+      <c r="S12" s="90">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="T12" s="91">
+      <c r="T12" s="90">
         <f t="shared" si="3"/>
         <v>0.245</v>
       </c>
@@ -3587,62 +3578,62 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="252"/>
-      <c r="C13" s="63" t="s">
+      <c r="B13" s="262"/>
+      <c r="C13" s="62" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="76" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="116" t="s">
-        <v>164</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="F13" s="77" t="s">
-        <v>165</v>
-      </c>
-      <c r="G13" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="J13" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="K13" s="45">
+      <c r="G13" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="J13" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="K13" s="44">
         <v>100</v>
       </c>
-      <c r="L13" s="45">
+      <c r="L13" s="44">
         <v>100</v>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="64">
         <v>1</v>
       </c>
-      <c r="N13" s="65">
+      <c r="N13" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O13" s="65">
+      <c r="O13" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P13" s="92" t="s">
+      <c r="P13" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q13" s="43">
+      <c r="Q13" s="42">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R13" s="91">
+      <c r="R13" s="90">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S13" s="91">
+      <c r="S13" s="90">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T13" s="91">
+      <c r="T13" s="90">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
@@ -3654,62 +3645,62 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="252"/>
-      <c r="C14" s="63" t="s">
+      <c r="B14" s="262"/>
+      <c r="C14" s="62" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="63" t="s">
         <v>214</v>
       </c>
-      <c r="D14" s="85" t="s">
-        <v>215</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="G14" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="I14" s="40" t="s">
+      <c r="G14" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="I14" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="41" t="s">
-        <v>224</v>
-      </c>
-      <c r="K14" s="45">
+      <c r="J14" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="K14" s="44">
         <v>100</v>
       </c>
-      <c r="L14" s="45">
+      <c r="L14" s="44">
         <v>100</v>
       </c>
-      <c r="M14" s="65">
+      <c r="M14" s="64">
         <v>1</v>
       </c>
-      <c r="N14" s="65">
+      <c r="N14" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O14" s="65">
+      <c r="O14" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P14" s="92" t="s">
+      <c r="P14" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="43">
+      <c r="Q14" s="42">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="R14" s="91">
+      <c r="R14" s="90">
         <f t="shared" si="2"/>
         <v>0.38999999999999996</v>
       </c>
-      <c r="S14" s="91">
+      <c r="S14" s="90">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="T14" s="91">
+      <c r="T14" s="90">
         <f t="shared" si="3"/>
         <v>0.38999999999999996</v>
       </c>
@@ -3721,62 +3712,62 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="252"/>
-      <c r="C15" s="63" t="s">
+      <c r="B15" s="262"/>
+      <c r="C15" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="84" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="63" t="s">
         <v>217</v>
       </c>
-      <c r="D15" s="85" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="64" t="s">
-        <v>219</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="I15" s="40" t="s">
+      <c r="G15" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="I15" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="K15" s="45">
+      <c r="J15" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="K15" s="44">
         <v>50</v>
       </c>
-      <c r="L15" s="45">
+      <c r="L15" s="44">
         <v>50</v>
       </c>
-      <c r="M15" s="65">
+      <c r="M15" s="64">
         <v>2</v>
       </c>
-      <c r="N15" s="65">
+      <c r="N15" s="64">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O15" s="65">
+      <c r="O15" s="64">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P15" s="92" t="s">
+      <c r="P15" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="43">
+      <c r="Q15" s="42">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="R15" s="91">
+      <c r="R15" s="90">
         <f t="shared" si="2"/>
         <v>0.27</v>
       </c>
-      <c r="S15" s="91">
+      <c r="S15" s="90">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="T15" s="91">
+      <c r="T15" s="90">
         <f t="shared" si="3"/>
         <v>0.27</v>
       </c>
@@ -3788,62 +3779,62 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="252"/>
-      <c r="C16" s="63" t="s">
+      <c r="B16" s="262"/>
+      <c r="C16" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" s="84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E16" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="63" t="s">
         <v>251</v>
       </c>
-      <c r="D16" s="135" t="s">
-        <v>252</v>
-      </c>
-      <c r="E16" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="64" t="s">
-        <v>253</v>
-      </c>
-      <c r="G16" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="I16" s="40" t="s">
+      <c r="G16" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="I16" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="K16" s="45">
+      <c r="J16" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="K16" s="44">
         <v>50</v>
       </c>
-      <c r="L16" s="45">
+      <c r="L16" s="44">
         <v>50</v>
       </c>
-      <c r="M16" s="65">
+      <c r="M16" s="64">
         <v>1</v>
       </c>
-      <c r="N16" s="65">
+      <c r="N16" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O16" s="65">
+      <c r="O16" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P16" s="92" t="s">
+      <c r="P16" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="43">
+      <c r="Q16" s="42">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="R16" s="91">
+      <c r="R16" s="90">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="S16" s="91">
+      <c r="S16" s="90">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="T16" s="91">
+      <c r="T16" s="90">
         <f>S16*L16</f>
         <v>0.32</v>
       </c>
@@ -3855,62 +3846,62 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="253"/>
-      <c r="C17" s="97" t="s">
+      <c r="B17" s="263"/>
+      <c r="C17" s="96" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="121" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="113" t="s">
         <v>254</v>
       </c>
-      <c r="D17" s="136" t="s">
-        <v>255</v>
-      </c>
-      <c r="E17" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="114" t="s">
-        <v>256</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="H17" s="52" t="s">
-        <v>259</v>
-      </c>
-      <c r="I17" s="53" t="s">
+      <c r="G17" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="72" t="s">
-        <v>260</v>
-      </c>
-      <c r="K17" s="51">
+      <c r="J17" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="K17" s="50">
         <v>50</v>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="50">
         <v>50</v>
       </c>
-      <c r="M17" s="54">
+      <c r="M17" s="53">
         <v>1</v>
       </c>
-      <c r="N17" s="54">
+      <c r="N17" s="53">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O17" s="54">
+      <c r="O17" s="53">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P17" s="95" t="s">
+      <c r="P17" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="Q17" s="55">
+      <c r="Q17" s="54">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="R17" s="96">
+      <c r="R17" s="95">
         <f t="shared" si="2"/>
         <v>0.39500000000000002</v>
       </c>
-      <c r="S17" s="96">
+      <c r="S17" s="95">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="T17" s="96">
+      <c r="T17" s="95">
         <f>S17*L17</f>
         <v>0.39500000000000002</v>
       </c>
@@ -3922,204 +3913,204 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="254" t="s">
-        <v>185</v>
-      </c>
-      <c r="C18" s="210" t="s">
+      <c r="B18" s="264" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="206" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="168" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="169" t="s">
+        <v>294</v>
+      </c>
+      <c r="F18" s="170" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="171" t="s">
-        <v>183</v>
-      </c>
-      <c r="E18" s="172" t="s">
-        <v>296</v>
-      </c>
-      <c r="F18" s="173" t="s">
-        <v>184</v>
-      </c>
-      <c r="G18" s="174" t="s">
-        <v>199</v>
-      </c>
-      <c r="H18" s="175" t="s">
-        <v>198</v>
-      </c>
-      <c r="I18" s="176" t="s">
+      <c r="G18" s="171" t="s">
+        <v>197</v>
+      </c>
+      <c r="H18" s="172" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" s="173" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="173" t="s">
+      <c r="J18" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="174">
+      <c r="K18" s="171">
         <v>10</v>
       </c>
-      <c r="L18" s="174">
+      <c r="L18" s="171">
         <v>30</v>
       </c>
-      <c r="M18" s="42">
+      <c r="M18" s="41">
         <v>1</v>
       </c>
-      <c r="N18" s="42">
+      <c r="N18" s="41">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O18" s="42">
+      <c r="O18" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="177" t="s">
+      <c r="P18" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="178">
+      <c r="Q18" s="175">
         <v>6.9699999999999998E-2</v>
       </c>
-      <c r="R18" s="44">
+      <c r="R18" s="43">
         <f t="shared" si="2"/>
         <v>0.69699999999999995</v>
       </c>
-      <c r="S18" s="44">
+      <c r="S18" s="43">
         <v>6.9699999999999998E-2</v>
       </c>
-      <c r="T18" s="44">
+      <c r="T18" s="43">
         <f t="shared" si="3"/>
         <v>2.0909999999999997</v>
       </c>
-      <c r="U18" s="179"/>
-      <c r="V18" s="179"/>
-      <c r="W18" s="224"/>
+      <c r="U18" s="176"/>
+      <c r="V18" s="176"/>
+      <c r="W18" s="220"/>
     </row>
     <row r="19" spans="1:23" ht="16.5" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="255"/>
-      <c r="C19" s="229" t="s">
+      <c r="B19" s="265"/>
+      <c r="C19" s="225" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="226" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="226" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="226" t="s">
         <v>220</v>
       </c>
-      <c r="D19" s="230" t="s">
-        <v>221</v>
-      </c>
-      <c r="E19" s="230" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="230" t="s">
-        <v>222</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>298</v>
-      </c>
-      <c r="H19" s="48" t="s">
-        <v>297</v>
-      </c>
-      <c r="I19" s="49" t="s">
+      <c r="G19" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="I19" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="230" t="s">
+      <c r="J19" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="49">
+      <c r="K19" s="48">
         <v>10</v>
       </c>
-      <c r="L19" s="49">
+      <c r="L19" s="48">
         <v>50</v>
       </c>
-      <c r="M19" s="231">
+      <c r="M19" s="227">
         <v>2</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="227">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="231">
+      <c r="O19" s="227">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="232" t="s">
+      <c r="P19" s="228" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="233">
+      <c r="Q19" s="229">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="230">
         <f t="shared" si="2"/>
         <v>0.39399999999999996</v>
       </c>
-      <c r="S19" s="234">
+      <c r="S19" s="230">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="T19" s="234">
+      <c r="T19" s="230">
         <f t="shared" si="3"/>
         <v>1.97</v>
       </c>
-      <c r="U19" s="235"/>
-      <c r="V19" s="236" t="s">
-        <v>293</v>
-      </c>
-      <c r="W19" s="237" t="s">
-        <v>299</v>
+      <c r="U19" s="231"/>
+      <c r="V19" s="232" t="s">
+        <v>291</v>
+      </c>
+      <c r="W19" s="233" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="259" t="s">
-        <v>190</v>
-      </c>
-      <c r="C20" s="60" t="s">
+      <c r="B20" s="269" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="116" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="D20" s="117" t="s">
+      <c r="F20" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="E20" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="F20" s="61" t="s">
-        <v>189</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="H20" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="I20" s="34" t="s">
+      <c r="G20" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="I20" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="32">
+      <c r="K20" s="31">
         <v>50</v>
       </c>
-      <c r="L20" s="32">
+      <c r="L20" s="31">
         <v>50</v>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="35">
         <v>1</v>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="35">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O20" s="36">
+      <c r="O20" s="35">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P20" s="115" t="s">
+      <c r="P20" s="114" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="37">
+      <c r="Q20" s="36">
         <v>2.12E-2</v>
       </c>
-      <c r="R20" s="38">
+      <c r="R20" s="37">
         <f t="shared" si="2"/>
         <v>1.06</v>
       </c>
-      <c r="S20" s="38">
+      <c r="S20" s="37">
         <v>2.12E-2</v>
       </c>
-      <c r="T20" s="38">
+      <c r="T20" s="37">
         <f t="shared" si="3"/>
         <v>1.06</v>
       </c>
@@ -4131,68 +4122,68 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="261"/>
-      <c r="C21" s="63" t="s">
+      <c r="B21" s="271"/>
+      <c r="C21" s="62" t="s">
+        <v>225</v>
+      </c>
+      <c r="D21" s="84" t="s">
+        <v>226</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="F21" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="D21" s="85" t="s">
-        <v>228</v>
-      </c>
-      <c r="E21" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" s="64" t="s">
-        <v>229</v>
-      </c>
-      <c r="G21" s="45" t="s">
-        <v>234</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="40" t="s">
+      <c r="G21" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="K21" s="45">
+      <c r="J21" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="K21" s="44">
         <v>12</v>
       </c>
-      <c r="L21" s="45">
+      <c r="L21" s="44">
         <v>45</v>
       </c>
-      <c r="M21" s="65">
+      <c r="M21" s="64">
         <v>2</v>
       </c>
-      <c r="N21" s="65">
+      <c r="N21" s="64">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O21" s="65">
+      <c r="O21" s="64">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P21" s="194" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q21" s="43">
+      <c r="P21" s="190" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q21" s="42">
         <v>0.11208</v>
       </c>
-      <c r="R21" s="91">
+      <c r="R21" s="90">
         <f t="shared" si="2"/>
         <v>1.3449599999999999</v>
       </c>
-      <c r="S21" s="91">
+      <c r="S21" s="90">
         <v>0.11208</v>
       </c>
-      <c r="T21" s="91">
+      <c r="T21" s="90">
         <f t="shared" si="3"/>
         <v>5.0435999999999996</v>
       </c>
       <c r="U21" s="19"/>
       <c r="V21" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="W21" s="14"/>
     </row>
@@ -4200,62 +4191,62 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="261"/>
-      <c r="C22" s="63" t="s">
+      <c r="B22" s="271"/>
+      <c r="C22" s="62" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" s="84" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="D22" s="85" t="s">
+      <c r="F22" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="G22" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="H22" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="G22" s="45" t="s">
-        <v>234</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="K22" s="45">
+      <c r="J22" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="K22" s="44">
         <v>50</v>
       </c>
-      <c r="L22" s="45">
+      <c r="L22" s="44">
         <v>50</v>
       </c>
-      <c r="M22" s="65">
+      <c r="M22" s="64">
         <v>2</v>
       </c>
-      <c r="N22" s="65">
+      <c r="N22" s="64">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O22" s="65">
+      <c r="O22" s="64">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P22" s="92" t="s">
+      <c r="P22" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="43">
+      <c r="Q22" s="42">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="R22" s="91">
+      <c r="R22" s="90">
         <f t="shared" si="2"/>
         <v>0.39500000000000002</v>
       </c>
-      <c r="S22" s="91">
+      <c r="S22" s="90">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="T22" s="91">
+      <c r="T22" s="90">
         <f t="shared" si="3"/>
         <v>0.39500000000000002</v>
       </c>
@@ -4267,62 +4258,62 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="260"/>
-      <c r="C23" s="97" t="s">
+      <c r="B23" s="270"/>
+      <c r="C23" s="96" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="121" t="s">
+        <v>260</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="113" t="s">
         <v>261</v>
       </c>
-      <c r="D23" s="136" t="s">
+      <c r="G23" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="E23" s="114" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="114" t="s">
-        <v>263</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>264</v>
-      </c>
-      <c r="I23" s="53" t="s">
+      <c r="I23" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="72" t="s">
-        <v>206</v>
-      </c>
-      <c r="K23" s="51">
+      <c r="J23" s="71" t="s">
+        <v>204</v>
+      </c>
+      <c r="K23" s="50">
         <v>10</v>
       </c>
-      <c r="L23" s="51">
+      <c r="L23" s="50">
         <v>30</v>
       </c>
-      <c r="M23" s="54">
+      <c r="M23" s="53">
         <v>1</v>
       </c>
-      <c r="N23" s="54">
+      <c r="N23" s="53">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O23" s="54">
+      <c r="O23" s="53">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P23" s="95" t="s">
+      <c r="P23" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="55">
+      <c r="Q23" s="54">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="R23" s="96">
+      <c r="R23" s="95">
         <f t="shared" si="2"/>
         <v>0.45100000000000001</v>
       </c>
-      <c r="S23" s="96">
+      <c r="S23" s="95">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="T23" s="96">
+      <c r="T23" s="95">
         <f t="shared" si="3"/>
         <v>1.353</v>
       </c>
@@ -4334,74 +4325,74 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="160" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="211" t="s">
+      <c r="B24" s="157" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="207" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="186" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="190" t="s">
+      <c r="E24" s="187" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="187" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="191" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="191" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="192" t="s">
-        <v>146</v>
-      </c>
-      <c r="H24" s="192" t="s">
+      <c r="G24" s="188" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="191" t="s">
-        <v>145</v>
-      </c>
-      <c r="J24" s="191" t="s">
+      <c r="H24" s="188" t="s">
+        <v>142</v>
+      </c>
+      <c r="I24" s="187" t="s">
+        <v>143</v>
+      </c>
+      <c r="J24" s="187" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="191">
+      <c r="K24" s="187">
         <v>42</v>
       </c>
-      <c r="L24" s="191">
+      <c r="L24" s="187">
         <v>162</v>
       </c>
-      <c r="M24" s="193">
+      <c r="M24" s="189">
         <v>8</v>
       </c>
-      <c r="N24" s="193">
+      <c r="N24" s="189">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="193">
+      <c r="O24" s="189">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="194" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q24" s="195">
+      <c r="P24" s="190" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q24" s="191">
         <v>3.68</v>
       </c>
-      <c r="R24" s="196">
+      <c r="R24" s="192">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="196">
+      <c r="S24" s="192">
         <v>3.68</v>
       </c>
-      <c r="T24" s="196">
+      <c r="T24" s="192">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="197" t="s">
-        <v>247</v>
-      </c>
-      <c r="V24" s="198" t="s">
-        <v>293</v>
-      </c>
-      <c r="W24" s="225">
+      <c r="U24" s="193" t="s">
+        <v>245</v>
+      </c>
+      <c r="V24" s="194" t="s">
+        <v>291</v>
+      </c>
+      <c r="W24" s="221">
         <v>3.68</v>
       </c>
     </row>
@@ -4409,271 +4400,271 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="214" t="s">
+      <c r="B25" s="210" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="212" t="s">
+      <c r="C25" s="208" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="195" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="196" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="199" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="200" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="200" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="201" t="s">
+      <c r="G25" s="197" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="198" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="202" t="s">
-        <v>123</v>
-      </c>
-      <c r="I25" s="203" t="s">
+      <c r="I25" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="200" t="s">
+      <c r="J25" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="200">
+      <c r="K25" s="196">
         <v>10</v>
       </c>
-      <c r="L25" s="200">
+      <c r="L25" s="196">
         <v>30</v>
       </c>
-      <c r="M25" s="204">
+      <c r="M25" s="200">
         <v>1</v>
       </c>
-      <c r="N25" s="204">
+      <c r="N25" s="200">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="204">
+      <c r="O25" s="200">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="205" t="s">
+      <c r="P25" s="201" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="206">
+      <c r="Q25" s="202">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="R25" s="207">
+      <c r="R25" s="203">
         <f t="shared" si="2"/>
         <v>0.59699999999999998</v>
       </c>
-      <c r="S25" s="207">
+      <c r="S25" s="203">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="T25" s="207">
+      <c r="T25" s="203">
         <f t="shared" si="3"/>
         <v>1.7910000000000001</v>
       </c>
-      <c r="U25" s="208"/>
-      <c r="V25" s="208"/>
-      <c r="W25" s="209"/>
+      <c r="U25" s="204"/>
+      <c r="V25" s="204"/>
+      <c r="W25" s="205"/>
     </row>
     <row r="26" spans="1:23" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="252" t="s">
+      <c r="B26" s="262" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="262" t="s">
+      <c r="C26" s="234" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="235" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="235" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="235" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="263" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="263" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="263" t="s">
-        <v>80</v>
-      </c>
-      <c r="G26" s="264" t="s">
+      <c r="G26" s="236" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="237" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="265" t="s">
-        <v>125</v>
-      </c>
-      <c r="I26" s="264" t="s">
+      <c r="I26" s="236" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="263" t="s">
+      <c r="J26" s="235" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="263">
+      <c r="K26" s="235">
         <v>7</v>
       </c>
-      <c r="L26" s="263">
+      <c r="L26" s="235">
         <v>22</v>
       </c>
-      <c r="M26" s="266">
+      <c r="M26" s="238">
         <v>1</v>
       </c>
-      <c r="N26" s="266">
+      <c r="N26" s="238">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O26" s="267">
+      <c r="O26" s="239">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P26" s="268" t="s">
+      <c r="P26" s="240" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="269">
+      <c r="Q26" s="241">
         <v>0.21840000000000001</v>
       </c>
-      <c r="R26" s="270">
+      <c r="R26" s="242">
         <f>Q26*K26</f>
         <v>1.5288000000000002</v>
       </c>
-      <c r="S26" s="270">
+      <c r="S26" s="242">
         <v>0.1774</v>
       </c>
-      <c r="T26" s="271">
+      <c r="T26" s="243">
         <f t="shared" si="3"/>
         <v>3.9028</v>
       </c>
-      <c r="U26" s="272"/>
-      <c r="V26" s="273" t="s">
-        <v>293</v>
-      </c>
-      <c r="W26" s="274"/>
+      <c r="U26" s="244"/>
+      <c r="V26" s="245" t="s">
+        <v>291</v>
+      </c>
+      <c r="W26" s="246"/>
     </row>
     <row r="27" spans="1:23" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="252"/>
-      <c r="C27" s="161" t="s">
+      <c r="B27" s="262"/>
+      <c r="C27" s="158" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="115" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="116" t="s">
+      <c r="E27" s="84" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="84" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="85" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="I27" s="40" t="s">
+      <c r="I27" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="85" t="s">
+      <c r="J27" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="85">
+      <c r="K27" s="84">
         <v>15</v>
       </c>
-      <c r="L27" s="85">
+      <c r="L27" s="84">
         <v>45</v>
       </c>
-      <c r="M27" s="46">
+      <c r="M27" s="45">
         <v>2</v>
       </c>
-      <c r="N27" s="46">
+      <c r="N27" s="45">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O27" s="46">
+      <c r="O27" s="45">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P27" s="275" t="s">
+      <c r="P27" s="247" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="163">
+      <c r="Q27" s="160">
         <v>0.1085</v>
       </c>
-      <c r="R27" s="164">
+      <c r="R27" s="161">
         <f t="shared" si="2"/>
         <v>1.6274999999999999</v>
       </c>
-      <c r="S27" s="164">
+      <c r="S27" s="161">
         <v>0.1085</v>
       </c>
-      <c r="T27" s="164">
+      <c r="T27" s="161">
         <f t="shared" si="3"/>
         <v>4.8825000000000003</v>
       </c>
-      <c r="U27" s="169"/>
-      <c r="V27" s="169" t="s">
-        <v>293</v>
-      </c>
-      <c r="W27" s="166"/>
+      <c r="U27" s="166"/>
+      <c r="V27" s="166" t="s">
+        <v>291</v>
+      </c>
+      <c r="W27" s="163"/>
     </row>
     <row r="28" spans="1:23" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="87" t="s">
+      <c r="B28" s="262"/>
+      <c r="C28" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="133" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="D28" s="134" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="47" t="s">
+      <c r="G28" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="I28" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="H28" s="48" t="s">
-        <v>205</v>
-      </c>
-      <c r="I28" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="68" t="s">
-        <v>206</v>
-      </c>
-      <c r="K28" s="68">
+      <c r="K28" s="67">
         <v>10</v>
       </c>
-      <c r="L28" s="68">
+      <c r="L28" s="67">
         <v>25</v>
       </c>
-      <c r="M28" s="98">
+      <c r="M28" s="97">
         <v>1</v>
       </c>
-      <c r="N28" s="98">
+      <c r="N28" s="97">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O28" s="98">
+      <c r="O28" s="97">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="181" t="s">
+      <c r="P28" s="178" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="50">
+      <c r="Q28" s="49">
         <v>9.6199999999999994E-2</v>
       </c>
-      <c r="R28" s="99">
+      <c r="R28" s="98">
         <f t="shared" si="2"/>
         <v>0.96199999999999997</v>
       </c>
-      <c r="S28" s="99">
+      <c r="S28" s="98">
         <v>9.6199999999999994E-2</v>
       </c>
-      <c r="T28" s="99">
+      <c r="T28" s="98">
         <f t="shared" si="3"/>
         <v>2.4049999999999998</v>
       </c>
@@ -4685,64 +4676,64 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="251" t="s">
+      <c r="B29" s="261" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="134" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="137" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29" s="33" t="s">
+      <c r="G29" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="117" t="s">
+      <c r="H29" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="K29" s="138">
+      <c r="I29" s="116" t="s">
+        <v>127</v>
+      </c>
+      <c r="J29" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="K29" s="135">
         <v>100</v>
       </c>
-      <c r="L29" s="138">
+      <c r="L29" s="135">
         <v>100</v>
       </c>
-      <c r="M29" s="138">
+      <c r="M29" s="135">
         <v>3</v>
       </c>
-      <c r="N29" s="36">
+      <c r="N29" s="35">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="O29" s="36">
+      <c r="O29" s="35">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="P29" s="139" t="s">
+      <c r="P29" s="136" t="s">
         <v>16</v>
       </c>
-      <c r="Q29" s="37">
+      <c r="Q29" s="36">
         <v>1E-3</v>
       </c>
-      <c r="R29" s="38">
+      <c r="R29" s="37">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="S29" s="38">
+      <c r="S29" s="37">
         <v>1E-3</v>
       </c>
-      <c r="T29" s="38">
+      <c r="T29" s="37">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
@@ -4754,62 +4745,62 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="252"/>
-      <c r="C30" s="74" t="s">
+      <c r="B30" s="262"/>
+      <c r="C30" s="73" t="s">
+        <v>264</v>
+      </c>
+      <c r="D30" s="108" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="38" t="s">
         <v>266</v>
       </c>
-      <c r="D30" s="109" t="s">
-        <v>170</v>
-      </c>
-      <c r="E30" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="G30" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H30" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="I30" s="85" t="s">
+      <c r="I30" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="K30" s="86">
+      <c r="J30" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="K30" s="85">
         <v>100</v>
       </c>
-      <c r="L30" s="86">
+      <c r="L30" s="85">
         <v>100</v>
       </c>
-      <c r="M30" s="86">
+      <c r="M30" s="85">
         <v>1</v>
       </c>
-      <c r="N30" s="65">
+      <c r="N30" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O30" s="65">
+      <c r="O30" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P30" s="93" t="s">
+      <c r="P30" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="Q30" s="43">
+      <c r="Q30" s="42">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="R30" s="91">
+      <c r="R30" s="90">
         <f>Q30*K30</f>
         <v>0.16999999999999998</v>
       </c>
-      <c r="S30" s="91">
+      <c r="S30" s="90">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="T30" s="91">
+      <c r="T30" s="90">
         <f t="shared" si="3"/>
         <v>0.16999999999999998</v>
       </c>
@@ -4821,62 +4812,62 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="252"/>
-      <c r="C31" s="74" t="s">
+      <c r="B31" s="262"/>
+      <c r="C31" s="73" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" s="115" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="116" t="s">
+      <c r="G31" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="I31" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="J31" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="G31" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="I31" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="J31" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="K31" s="86">
+      <c r="K31" s="85">
         <v>100</v>
       </c>
-      <c r="L31" s="86">
+      <c r="L31" s="85">
         <v>100</v>
       </c>
-      <c r="M31" s="86">
+      <c r="M31" s="85">
         <v>1</v>
       </c>
-      <c r="N31" s="65">
+      <c r="N31" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O31" s="65">
+      <c r="O31" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P31" s="93" t="s">
+      <c r="P31" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="Q31" s="43">
+      <c r="Q31" s="42">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="R31" s="91">
+      <c r="R31" s="90">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="S31" s="91">
+      <c r="S31" s="90">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="T31" s="91">
+      <c r="T31" s="90">
         <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
@@ -4888,62 +4879,62 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="252"/>
-      <c r="C32" s="74" t="s">
+      <c r="B32" s="262"/>
+      <c r="C32" s="73" t="s">
+        <v>234</v>
+      </c>
+      <c r="D32" s="115" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="116" t="s">
+      <c r="G32" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="41" t="s">
+      <c r="I32" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="G32" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H32" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="I32" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="K32" s="86">
+      <c r="K32" s="85">
         <v>100</v>
       </c>
-      <c r="L32" s="86">
+      <c r="L32" s="85">
         <v>100</v>
       </c>
-      <c r="M32" s="86">
+      <c r="M32" s="85">
         <v>4</v>
       </c>
-      <c r="N32" s="65">
+      <c r="N32" s="64">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="O32" s="65">
+      <c r="O32" s="64">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="P32" s="93" t="s">
+      <c r="P32" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="Q32" s="43">
+      <c r="Q32" s="42">
         <v>1.4E-3</v>
       </c>
-      <c r="R32" s="91">
+      <c r="R32" s="90">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S32" s="91">
+      <c r="S32" s="90">
         <v>1.4E-3</v>
       </c>
-      <c r="T32" s="91">
+      <c r="T32" s="90">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
@@ -4955,62 +4946,62 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="253"/>
-      <c r="C33" s="71" t="s">
+      <c r="B33" s="263"/>
+      <c r="C33" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="137" t="s">
+        <v>277</v>
+      </c>
+      <c r="E33" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="140" t="s">
-        <v>279</v>
-      </c>
-      <c r="E33" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="G33" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="H33" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="I33" s="122" t="s">
+      <c r="G33" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="72" t="s">
+      <c r="J33" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="141">
+      <c r="K33" s="138">
         <v>100</v>
       </c>
-      <c r="L33" s="141">
+      <c r="L33" s="138">
         <v>100</v>
       </c>
-      <c r="M33" s="141">
+      <c r="M33" s="138">
         <v>2</v>
       </c>
-      <c r="N33" s="54">
+      <c r="N33" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O33" s="54">
+      <c r="O33" s="53">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P33" s="142" t="s">
+      <c r="P33" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="55">
+      <c r="Q33" s="54">
         <v>1.4E-3</v>
       </c>
-      <c r="R33" s="96">
+      <c r="R33" s="95">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S33" s="96">
+      <c r="S33" s="95">
         <v>1.4E-3</v>
       </c>
-      <c r="T33" s="96">
+      <c r="T33" s="95">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
@@ -5022,283 +5013,283 @@
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="252" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="213" t="s">
+      <c r="B34" s="262" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="209" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="179" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="182" t="s">
+      <c r="E34" s="180" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="183" t="s">
+      <c r="F34" s="180" t="s">
         <v>91</v>
       </c>
-      <c r="F34" s="183" t="s">
-        <v>92</v>
-      </c>
-      <c r="G34" s="184" t="s">
+      <c r="G34" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="185" t="s">
-        <v>132</v>
-      </c>
-      <c r="I34" s="184" t="s">
+      <c r="H34" s="181" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="183" t="s">
+      <c r="I34" s="181" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="180" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="183">
+      <c r="K34" s="180">
         <v>11</v>
       </c>
-      <c r="L34" s="183">
+      <c r="L34" s="180">
         <v>42</v>
       </c>
-      <c r="M34" s="186">
+      <c r="M34" s="182">
         <v>2</v>
       </c>
-      <c r="N34" s="186">
+      <c r="N34" s="182">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="186">
+      <c r="O34" s="182">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="187" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q34" s="188">
+      <c r="P34" s="183" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q34" s="184">
         <v>0.318</v>
       </c>
-      <c r="R34" s="189">
+      <c r="R34" s="185">
         <f t="shared" si="2"/>
         <v>3.4980000000000002</v>
       </c>
-      <c r="S34" s="189">
+      <c r="S34" s="185">
         <v>0.4148</v>
       </c>
-      <c r="T34" s="189">
+      <c r="T34" s="185">
         <f t="shared" si="3"/>
         <v>17.421600000000002</v>
       </c>
-      <c r="U34" s="180"/>
-      <c r="V34" s="180" t="s">
-        <v>293</v>
-      </c>
-      <c r="W34" s="226" t="s">
-        <v>135</v>
+      <c r="U34" s="177"/>
+      <c r="V34" s="177" t="s">
+        <v>291</v>
+      </c>
+      <c r="W34" s="222" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:23" ht="26.25" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="252"/>
-      <c r="C35" s="161" t="s">
+      <c r="B35" s="262"/>
+      <c r="C35" s="158" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="116" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="85" t="s">
+      <c r="F35" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="85" t="s">
-        <v>95</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="H35" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="I35" s="40" t="s">
+      <c r="G35" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="H35" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="85" t="s">
+      <c r="J35" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="40">
+      <c r="K35" s="39">
         <v>6</v>
       </c>
-      <c r="L35" s="40">
+      <c r="L35" s="39">
         <v>21</v>
       </c>
-      <c r="M35" s="46">
+      <c r="M35" s="45">
         <v>1</v>
       </c>
-      <c r="N35" s="46">
+      <c r="N35" s="45">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="46">
+      <c r="O35" s="45">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="275" t="s">
+      <c r="P35" s="247" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="163">
+      <c r="Q35" s="160">
         <v>0.40610000000000002</v>
       </c>
-      <c r="R35" s="164">
+      <c r="R35" s="161">
         <f t="shared" si="2"/>
         <v>2.4366000000000003</v>
       </c>
-      <c r="S35" s="164">
+      <c r="S35" s="161">
         <v>0.3528</v>
       </c>
-      <c r="T35" s="164">
+      <c r="T35" s="161">
         <f t="shared" si="3"/>
         <v>7.4088000000000003</v>
       </c>
-      <c r="U35" s="169"/>
-      <c r="V35" s="169" t="s">
-        <v>293</v>
-      </c>
-      <c r="W35" s="166"/>
+      <c r="U35" s="166"/>
+      <c r="V35" s="166" t="s">
+        <v>291</v>
+      </c>
+      <c r="W35" s="163"/>
     </row>
     <row r="36" spans="1:23" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="252"/>
-      <c r="C36" s="143" t="s">
+      <c r="B36" s="262"/>
+      <c r="C36" s="140" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="141" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="142" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="144" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="145" t="s">
+      <c r="F36" s="142" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="145" t="s">
-        <v>98</v>
-      </c>
-      <c r="G36" s="146" t="s">
+      <c r="G36" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="146" t="s">
+      <c r="H36" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="145" t="s">
+      <c r="I36" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="145" t="s">
+      <c r="J36" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="146">
+      <c r="K36" s="143">
         <v>6</v>
       </c>
-      <c r="L36" s="146">
+      <c r="L36" s="143">
         <v>21</v>
       </c>
-      <c r="M36" s="147">
+      <c r="M36" s="144">
         <v>1</v>
       </c>
-      <c r="N36" s="147">
+      <c r="N36" s="144">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O36" s="147">
+      <c r="O36" s="144">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P36" s="148" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q36" s="153">
+      <c r="P36" s="145" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q36" s="150">
         <v>8</v>
       </c>
-      <c r="R36" s="150">
+      <c r="R36" s="147">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="S36" s="150">
+      <c r="S36" s="147">
         <v>8</v>
       </c>
-      <c r="T36" s="150">
+      <c r="T36" s="147">
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="U36" s="154"/>
-      <c r="V36" s="151" t="s">
-        <v>293</v>
-      </c>
-      <c r="W36" s="155"/>
+      <c r="U36" s="151"/>
+      <c r="V36" s="148" t="s">
+        <v>291</v>
+      </c>
+      <c r="W36" s="152"/>
     </row>
     <row r="37" spans="1:23" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="252"/>
-      <c r="C37" s="78" t="s">
+      <c r="B37" s="262"/>
+      <c r="C37" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="109" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="110" t="s">
+      <c r="E37" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="79" t="s">
-        <v>136</v>
-      </c>
-      <c r="F37" s="79" t="s">
-        <v>101</v>
-      </c>
-      <c r="G37" s="80" t="s">
+      <c r="G37" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="80" t="s">
+      <c r="H37" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="79" t="s">
+      <c r="I37" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="79" t="s">
+      <c r="J37" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="80">
+      <c r="K37" s="79">
         <v>11</v>
       </c>
-      <c r="L37" s="80">
+      <c r="L37" s="79">
         <v>41</v>
       </c>
-      <c r="M37" s="81">
+      <c r="M37" s="80">
         <v>2</v>
       </c>
-      <c r="N37" s="81">
+      <c r="N37" s="80">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O37" s="65">
+      <c r="O37" s="64">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P37" s="82" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q37" s="158">
+      <c r="P37" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q37" s="155">
         <v>4.76</v>
       </c>
-      <c r="R37" s="94">
+      <c r="R37" s="93">
         <f t="shared" si="2"/>
         <v>52.36</v>
       </c>
-      <c r="S37" s="94">
+      <c r="S37" s="93">
         <v>4.76</v>
       </c>
-      <c r="T37" s="159">
+      <c r="T37" s="156">
         <f t="shared" si="3"/>
         <v>195.16</v>
       </c>
-      <c r="U37" s="83" t="s">
-        <v>295</v>
-      </c>
-      <c r="V37" s="151" t="s">
+      <c r="U37" s="82" t="s">
         <v>293</v>
       </c>
-      <c r="W37" s="227">
+      <c r="V37" s="148" t="s">
+        <v>291</v>
+      </c>
+      <c r="W37" s="223">
         <v>4.76</v>
       </c>
     </row>
@@ -5306,62 +5297,62 @@
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="252"/>
-      <c r="C38" s="74" t="s">
+      <c r="B38" s="262"/>
+      <c r="C38" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="108" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F38" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="109" t="s">
-        <v>176</v>
-      </c>
-      <c r="E38" s="41" t="s">
+      <c r="G38" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="H38" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="F38" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="H38" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="I38" s="40" t="s">
+      <c r="I38" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="41" t="s">
+      <c r="J38" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="45">
+      <c r="K38" s="44">
         <v>6</v>
       </c>
-      <c r="L38" s="45">
+      <c r="L38" s="44">
         <v>21</v>
       </c>
-      <c r="M38" s="65">
+      <c r="M38" s="64">
         <v>1</v>
       </c>
-      <c r="N38" s="65">
+      <c r="N38" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O38" s="65">
+      <c r="O38" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P38" s="84" t="s">
+      <c r="P38" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="Q38" s="43">
+      <c r="Q38" s="42">
         <v>2.3496999999999999</v>
       </c>
-      <c r="R38" s="91">
+      <c r="R38" s="90">
         <f t="shared" si="2"/>
         <v>14.098199999999999</v>
       </c>
-      <c r="S38" s="91">
+      <c r="S38" s="90">
         <v>2.3496999999999999</v>
       </c>
-      <c r="T38" s="91">
+      <c r="T38" s="90">
         <f t="shared" si="3"/>
         <v>49.343699999999998</v>
       </c>
@@ -5373,62 +5364,62 @@
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="252"/>
-      <c r="C39" s="74" t="s">
+      <c r="B39" s="262"/>
+      <c r="C39" s="73" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" s="108" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="109" t="s">
+      <c r="F39" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="E39" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="G39" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="H39" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="I39" s="40" t="s">
+      <c r="G39" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="H39" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="I39" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="41" t="s">
+      <c r="J39" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="45">
+      <c r="K39" s="44">
         <v>6</v>
       </c>
-      <c r="L39" s="45">
+      <c r="L39" s="44">
         <v>21</v>
       </c>
-      <c r="M39" s="65">
+      <c r="M39" s="64">
         <v>1</v>
       </c>
-      <c r="N39" s="65">
+      <c r="N39" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O39" s="65">
+      <c r="O39" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P39" s="84" t="s">
+      <c r="P39" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="Q39" s="43">
+      <c r="Q39" s="42">
         <v>0.6492</v>
       </c>
-      <c r="R39" s="91">
+      <c r="R39" s="90">
         <f t="shared" si="2"/>
         <v>3.8952</v>
       </c>
-      <c r="S39" s="91">
+      <c r="S39" s="90">
         <v>0.5464</v>
       </c>
-      <c r="T39" s="91">
+      <c r="T39" s="90">
         <f t="shared" si="3"/>
         <v>11.474399999999999</v>
       </c>
@@ -5440,269 +5431,269 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="252"/>
-      <c r="C40" s="143" t="s">
+      <c r="B40" s="262"/>
+      <c r="C40" s="140" t="s">
+        <v>267</v>
+      </c>
+      <c r="D40" s="141" t="s">
+        <v>268</v>
+      </c>
+      <c r="E40" s="142" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="142" t="s">
         <v>269</v>
       </c>
-      <c r="D40" s="144" t="s">
-        <v>270</v>
-      </c>
-      <c r="E40" s="145" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="145" t="s">
-        <v>271</v>
-      </c>
-      <c r="G40" s="146" t="s">
-        <v>277</v>
-      </c>
-      <c r="H40" s="146"/>
-      <c r="I40" s="146" t="s">
+      <c r="G40" s="143" t="s">
+        <v>275</v>
+      </c>
+      <c r="H40" s="143"/>
+      <c r="I40" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="145" t="s">
+      <c r="J40" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="146">
+      <c r="K40" s="143">
         <v>6</v>
       </c>
-      <c r="L40" s="146">
+      <c r="L40" s="143">
         <v>22</v>
       </c>
-      <c r="M40" s="147">
+      <c r="M40" s="144">
         <v>1</v>
       </c>
-      <c r="N40" s="147">
+      <c r="N40" s="144">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="147">
+      <c r="O40" s="144">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="157" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q40" s="149">
+      <c r="P40" s="154" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q40" s="146">
         <v>0.8</v>
       </c>
-      <c r="R40" s="150">
+      <c r="R40" s="147">
         <f t="shared" si="2"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="S40" s="150">
+      <c r="S40" s="147">
         <v>0.8</v>
       </c>
-      <c r="T40" s="150">
+      <c r="T40" s="147">
         <f t="shared" si="3"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="U40" s="156" t="s">
-        <v>278</v>
-      </c>
-      <c r="V40" s="151" t="s">
-        <v>293</v>
-      </c>
-      <c r="W40" s="152"/>
+      <c r="U40" s="153" t="s">
+        <v>276</v>
+      </c>
+      <c r="V40" s="148" t="s">
+        <v>291</v>
+      </c>
+      <c r="W40" s="149"/>
     </row>
     <row r="41" spans="1:23" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="252"/>
-      <c r="C41" s="143" t="s">
+      <c r="B41" s="262"/>
+      <c r="C41" s="140" t="s">
+        <v>280</v>
+      </c>
+      <c r="D41" s="141" t="s">
+        <v>278</v>
+      </c>
+      <c r="E41" s="142" t="s">
+        <v>281</v>
+      </c>
+      <c r="F41" s="164" t="s">
         <v>282</v>
       </c>
-      <c r="D41" s="144" t="s">
-        <v>280</v>
-      </c>
-      <c r="E41" s="145" t="s">
+      <c r="G41" s="143" t="s">
         <v>283</v>
       </c>
-      <c r="F41" s="167" t="s">
-        <v>284</v>
-      </c>
-      <c r="G41" s="146" t="s">
-        <v>285</v>
-      </c>
-      <c r="H41" s="146" t="s">
+      <c r="H41" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="146" t="s">
+      <c r="I41" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="145" t="s">
+      <c r="J41" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="146">
+      <c r="K41" s="143">
         <v>10</v>
       </c>
-      <c r="L41" s="146">
+      <c r="L41" s="143">
         <v>30</v>
       </c>
-      <c r="M41" s="147">
+      <c r="M41" s="144">
         <v>1</v>
       </c>
-      <c r="N41" s="147">
+      <c r="N41" s="144">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="147">
+      <c r="O41" s="144">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="148" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q41" s="149">
+      <c r="P41" s="145" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q41" s="146">
         <v>1</v>
       </c>
-      <c r="R41" s="150">
+      <c r="R41" s="147">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S41" s="150">
+      <c r="S41" s="147">
         <v>1</v>
       </c>
-      <c r="T41" s="150">
+      <c r="T41" s="147">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="U41" s="168"/>
-      <c r="V41" s="151" t="s">
-        <v>293</v>
-      </c>
-      <c r="W41" s="152"/>
+      <c r="U41" s="165"/>
+      <c r="V41" s="148" t="s">
+        <v>291</v>
+      </c>
+      <c r="W41" s="149"/>
     </row>
     <row r="42" spans="1:23" ht="26.25" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="252"/>
-      <c r="C42" s="87" t="s">
+      <c r="B42" s="262"/>
+      <c r="C42" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" s="133" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="134" t="s">
+      <c r="E42" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="68" t="s">
+      <c r="G42" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="F42" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="G42" s="68" t="s">
-        <v>138</v>
-      </c>
-      <c r="H42" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="I42" s="68" t="s">
+      <c r="I42" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="68" t="s">
+      <c r="J42" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="47">
+      <c r="K42" s="46">
         <v>10</v>
       </c>
-      <c r="L42" s="47">
+      <c r="L42" s="46">
         <v>30</v>
       </c>
-      <c r="M42" s="98">
+      <c r="M42" s="97">
         <v>1</v>
       </c>
-      <c r="N42" s="98">
+      <c r="N42" s="97">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O42" s="98">
+      <c r="O42" s="97">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P42" s="215" t="s">
+      <c r="P42" s="211" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="50">
+      <c r="Q42" s="49">
         <v>5.6399999999999999E-2</v>
       </c>
-      <c r="R42" s="99">
+      <c r="R42" s="98">
         <f t="shared" si="2"/>
         <v>0.56399999999999995</v>
       </c>
-      <c r="S42" s="99">
+      <c r="S42" s="98">
         <v>5.6399999999999999E-2</v>
       </c>
-      <c r="T42" s="99">
+      <c r="T42" s="98">
         <f t="shared" si="3"/>
         <v>1.6919999999999999</v>
       </c>
-      <c r="U42" s="216"/>
-      <c r="V42" s="216"/>
+      <c r="U42" s="212"/>
+      <c r="V42" s="212"/>
       <c r="W42" s="27"/>
     </row>
     <row r="43" spans="1:23" ht="15.75" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="251" t="s">
-        <v>110</v>
-      </c>
-      <c r="C43" s="69" t="s">
+      <c r="B43" s="261" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="E43" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="F43" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="G43" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="H43" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="I43" s="35" t="s">
+      <c r="G43" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="I43" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="J43" s="35" t="s">
+      <c r="J43" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="K43" s="57">
+      <c r="K43" s="56">
         <v>50</v>
       </c>
-      <c r="L43" s="57">
+      <c r="L43" s="56">
         <v>50</v>
       </c>
-      <c r="M43" s="58">
+      <c r="M43" s="57">
         <v>1</v>
       </c>
-      <c r="N43" s="36">
+      <c r="N43" s="35">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O43" s="36">
+      <c r="O43" s="35">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P43" s="76" t="s">
+      <c r="P43" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="Q43" s="37">
+      <c r="Q43" s="36">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="R43" s="38">
+      <c r="R43" s="37">
         <f t="shared" si="2"/>
         <v>0.72500000000000009</v>
       </c>
-      <c r="S43" s="38">
+      <c r="S43" s="37">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="T43" s="38">
+      <c r="T43" s="37">
         <f t="shared" si="3"/>
         <v>0.72500000000000009</v>
       </c>
@@ -5714,62 +5705,62 @@
       <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B44" s="252"/>
-      <c r="C44" s="74" t="s">
+      <c r="B44" s="262"/>
+      <c r="C44" s="73" t="s">
+        <v>287</v>
+      </c>
+      <c r="D44" s="108" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="G44" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="D44" s="109" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F44" s="41" t="s">
+      <c r="H44" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="G44" s="41" t="s">
-        <v>291</v>
-      </c>
-      <c r="H44" s="41" t="s">
-        <v>292</v>
-      </c>
-      <c r="I44" s="41" t="s">
+      <c r="I44" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="J44" s="41" t="s">
+      <c r="J44" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="41">
+      <c r="K44" s="40">
         <v>10</v>
       </c>
-      <c r="L44" s="41">
+      <c r="L44" s="40">
         <v>30</v>
       </c>
-      <c r="M44" s="59">
+      <c r="M44" s="58">
         <v>1</v>
       </c>
-      <c r="N44" s="65">
+      <c r="N44" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O44" s="65">
+      <c r="O44" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P44" s="84" t="s">
+      <c r="P44" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="56">
+      <c r="Q44" s="55">
         <v>6.2E-2</v>
       </c>
-      <c r="R44" s="91">
+      <c r="R44" s="90">
         <f t="shared" si="2"/>
         <v>0.62</v>
       </c>
-      <c r="S44" s="91">
+      <c r="S44" s="90">
         <v>6.2E-2</v>
       </c>
-      <c r="T44" s="91">
+      <c r="T44" s="90">
         <f t="shared" si="3"/>
         <v>1.8599999999999999</v>
       </c>
@@ -5781,62 +5772,62 @@
       <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B45" s="252"/>
-      <c r="C45" s="74" t="s">
+      <c r="B45" s="262"/>
+      <c r="C45" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="108" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="109" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F45" s="77" t="s">
-        <v>109</v>
-      </c>
-      <c r="G45" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="H45" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="J45" s="41" t="s">
+      <c r="G45" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="H45" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="J45" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K45" s="41">
+      <c r="K45" s="40">
         <v>50</v>
       </c>
-      <c r="L45" s="41">
+      <c r="L45" s="40">
         <v>50</v>
       </c>
-      <c r="M45" s="59">
+      <c r="M45" s="58">
         <v>1</v>
       </c>
-      <c r="N45" s="65">
+      <c r="N45" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O45" s="65">
+      <c r="O45" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P45" s="75" t="s">
+      <c r="P45" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="43">
+      <c r="Q45" s="42">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="R45" s="91">
+      <c r="R45" s="90">
         <f t="shared" si="2"/>
         <v>0.65</v>
       </c>
-      <c r="S45" s="91">
+      <c r="S45" s="90">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="T45" s="91">
+      <c r="T45" s="90">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
@@ -5848,129 +5839,129 @@
       <c r="A46" s="6">
         <v>44</v>
       </c>
-      <c r="B46" s="252"/>
-      <c r="C46" s="161" t="s">
+      <c r="B46" s="262"/>
+      <c r="C46" s="158" t="s">
+        <v>270</v>
+      </c>
+      <c r="D46" s="115" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46" s="84" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="84" t="s">
         <v>272</v>
       </c>
-      <c r="D46" s="116" t="s">
+      <c r="G46" s="84" t="s">
         <v>273</v>
       </c>
-      <c r="E46" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="85" t="s">
+      <c r="H46" s="84" t="s">
         <v>274</v>
       </c>
-      <c r="G46" s="85" t="s">
-        <v>275</v>
-      </c>
-      <c r="H46" s="85" t="s">
-        <v>276</v>
-      </c>
-      <c r="I46" s="85" t="s">
+      <c r="I46" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="J46" s="85" t="s">
+      <c r="J46" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="85">
+      <c r="K46" s="84">
         <v>5</v>
       </c>
-      <c r="L46" s="85">
+      <c r="L46" s="84">
         <v>25</v>
       </c>
-      <c r="M46" s="46">
+      <c r="M46" s="45">
         <v>1</v>
       </c>
-      <c r="N46" s="46">
+      <c r="N46" s="45">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O46" s="46">
+      <c r="O46" s="45">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P46" s="162" t="s">
+      <c r="P46" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="Q46" s="163">
+      <c r="Q46" s="160">
         <v>8.8900000000000007E-2</v>
       </c>
-      <c r="R46" s="164">
+      <c r="R46" s="161">
         <f t="shared" si="2"/>
         <v>0.44450000000000001</v>
       </c>
-      <c r="S46" s="164">
+      <c r="S46" s="161">
         <v>8.8900000000000007E-2</v>
       </c>
-      <c r="T46" s="164">
+      <c r="T46" s="161">
         <f t="shared" si="3"/>
         <v>2.2225000000000001</v>
       </c>
-      <c r="U46" s="165"/>
-      <c r="V46" s="169"/>
-      <c r="W46" s="166"/>
+      <c r="U46" s="162"/>
+      <c r="V46" s="166"/>
+      <c r="W46" s="163"/>
     </row>
     <row r="47" spans="1:23" ht="15.75" thickBot="1">
       <c r="A47" s="6">
         <v>45</v>
       </c>
-      <c r="B47" s="252"/>
-      <c r="C47" s="74" t="s">
+      <c r="B47" s="262"/>
+      <c r="C47" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="167">
+        <v>61300611121</v>
+      </c>
+      <c r="G47" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="H47" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="D47" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="E47" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F47" s="170">
-        <v>61300611121</v>
-      </c>
-      <c r="G47" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="H47" s="41" t="s">
-        <v>288</v>
-      </c>
-      <c r="I47" s="41" t="s">
-        <v>288</v>
-      </c>
-      <c r="J47" s="41" t="s">
+      <c r="I47" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="J47" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K47" s="41">
+      <c r="K47" s="40">
         <v>20</v>
       </c>
-      <c r="L47" s="41">
+      <c r="L47" s="40">
         <v>40</v>
       </c>
-      <c r="M47" s="59">
+      <c r="M47" s="58">
         <v>1</v>
       </c>
-      <c r="N47" s="65">
+      <c r="N47" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O47" s="65">
+      <c r="O47" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P47" s="84" t="s">
+      <c r="P47" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="43">
+      <c r="Q47" s="42">
         <v>3.09E-2</v>
       </c>
-      <c r="R47" s="91">
+      <c r="R47" s="90">
         <f t="shared" si="2"/>
         <v>0.61799999999999999</v>
       </c>
-      <c r="S47" s="91">
+      <c r="S47" s="90">
         <v>3.09E-2</v>
       </c>
-      <c r="T47" s="91">
+      <c r="T47" s="90">
         <f t="shared" si="3"/>
         <v>1.236</v>
       </c>
@@ -5982,202 +5973,202 @@
       <c r="A48" s="6">
         <v>46</v>
       </c>
-      <c r="B48" s="253"/>
-      <c r="C48" s="100" t="s">
+      <c r="B48" s="263"/>
+      <c r="C48" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="101" t="s">
-        <v>241</v>
-      </c>
-      <c r="E48" s="102" t="s">
+      <c r="D48" s="100" t="s">
+        <v>239</v>
+      </c>
+      <c r="E48" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="102" t="s">
+      <c r="F48" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="G48" s="103" t="s">
-        <v>144</v>
-      </c>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="104" t="s">
+      <c r="G48" s="102" t="s">
+        <v>142</v>
+      </c>
+      <c r="H48" s="102"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="K48" s="104" t="s">
-        <v>144</v>
-      </c>
-      <c r="L48" s="104" t="s">
+      <c r="K48" s="103" t="s">
+        <v>142</v>
+      </c>
+      <c r="L48" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="105">
+      <c r="M48" s="104">
         <v>53</v>
       </c>
-      <c r="N48" s="106">
+      <c r="N48" s="105">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-      <c r="O48" s="54">
+      <c r="O48" s="53">
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
-      <c r="P48" s="103" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q48" s="104" t="s">
+      <c r="P48" s="102" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q48" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="104" t="s">
-        <v>144</v>
-      </c>
-      <c r="S48" s="104" t="s">
-        <v>144</v>
-      </c>
-      <c r="T48" s="104" t="s">
-        <v>144</v>
-      </c>
-      <c r="U48" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="V48" s="107"/>
-      <c r="W48" s="108"/>
+      <c r="R48" s="103" t="s">
+        <v>142</v>
+      </c>
+      <c r="S48" s="103" t="s">
+        <v>142</v>
+      </c>
+      <c r="T48" s="103" t="s">
+        <v>142</v>
+      </c>
+      <c r="U48" s="106" t="s">
+        <v>147</v>
+      </c>
+      <c r="V48" s="106"/>
+      <c r="W48" s="107"/>
     </row>
     <row r="49" spans="1:23" ht="26.25" thickBot="1">
       <c r="A49" s="6">
         <v>47</v>
       </c>
-      <c r="B49" s="259" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="217" t="s">
-        <v>249</v>
-      </c>
-      <c r="D49" s="218" t="s">
+      <c r="B49" s="269" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="213" t="s">
+        <v>247</v>
+      </c>
+      <c r="D49" s="214" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="218" t="s">
+      <c r="E49" s="214" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="218" t="s">
-        <v>248</v>
-      </c>
-      <c r="G49" s="218" t="s">
-        <v>144</v>
-      </c>
-      <c r="H49" s="218" t="s">
-        <v>144</v>
-      </c>
-      <c r="I49" s="218" t="s">
-        <v>144</v>
-      </c>
-      <c r="J49" s="218" t="s">
-        <v>144</v>
-      </c>
-      <c r="K49" s="218" t="s">
-        <v>144</v>
-      </c>
-      <c r="L49" s="218" t="s">
-        <v>144</v>
-      </c>
-      <c r="M49" s="58">
+      <c r="F49" s="214" t="s">
+        <v>246</v>
+      </c>
+      <c r="G49" s="214" t="s">
+        <v>142</v>
+      </c>
+      <c r="H49" s="214" t="s">
+        <v>142</v>
+      </c>
+      <c r="I49" s="214" t="s">
+        <v>142</v>
+      </c>
+      <c r="J49" s="214" t="s">
+        <v>142</v>
+      </c>
+      <c r="K49" s="214" t="s">
+        <v>142</v>
+      </c>
+      <c r="L49" s="214" t="s">
+        <v>142</v>
+      </c>
+      <c r="M49" s="57">
         <v>1</v>
       </c>
-      <c r="N49" s="36">
+      <c r="N49" s="35">
         <f>M49*5</f>
         <v>5</v>
       </c>
-      <c r="O49" s="36">
+      <c r="O49" s="35">
         <f>M49*20</f>
         <v>20</v>
       </c>
-      <c r="P49" s="219" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q49" s="220">
+      <c r="P49" s="215" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q49" s="216">
         <v>0.2</v>
       </c>
-      <c r="R49" s="221">
+      <c r="R49" s="217">
         <f>Q49*N49</f>
         <v>1</v>
       </c>
-      <c r="S49" s="220">
+      <c r="S49" s="216">
         <v>0.2</v>
       </c>
-      <c r="T49" s="38">
+      <c r="T49" s="37">
         <f>S49*O49</f>
         <v>4</v>
       </c>
-      <c r="U49" s="222"/>
-      <c r="V49" s="222"/>
-      <c r="W49" s="223"/>
+      <c r="U49" s="218"/>
+      <c r="V49" s="218"/>
+      <c r="W49" s="219"/>
     </row>
     <row r="50" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A50" s="228">
+      <c r="A50" s="224">
         <v>48</v>
       </c>
-      <c r="B50" s="260"/>
-      <c r="C50" s="118" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" s="119" t="s">
+      <c r="B50" s="270"/>
+      <c r="C50" s="117" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="119" t="s">
+      <c r="E50" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="120" t="s">
-        <v>152</v>
-      </c>
-      <c r="G50" s="119" t="s">
+      <c r="F50" s="119" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="H50" s="119" t="s">
+      <c r="H50" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="I50" s="119" t="s">
+      <c r="I50" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="J50" s="119" t="s">
+      <c r="J50" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="119" t="s">
+      <c r="K50" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="L50" s="119" t="s">
+      <c r="L50" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="111">
+      <c r="M50" s="110">
         <v>1</v>
       </c>
-      <c r="N50" s="111">
+      <c r="N50" s="110">
         <f t="shared" ref="N50" si="4">M50*5</f>
         <v>5</v>
       </c>
-      <c r="O50" s="54">
+      <c r="O50" s="53">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P50" s="126" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q50" s="112">
+      <c r="P50" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q50" s="111">
         <v>3.35</v>
       </c>
-      <c r="R50" s="113">
+      <c r="R50" s="112">
         <f>Q50*N50</f>
         <v>16.75</v>
       </c>
-      <c r="S50" s="113">
+      <c r="S50" s="112">
         <v>3.35</v>
       </c>
-      <c r="T50" s="96">
+      <c r="T50" s="95">
         <f>S50*O50</f>
         <v>67</v>
       </c>
-      <c r="U50" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="V50" s="107"/>
-      <c r="W50" s="121"/>
+      <c r="U50" s="106" t="s">
+        <v>147</v>
+      </c>
+      <c r="V50" s="106"/>
+      <c r="W50" s="120"/>
     </row>
     <row r="51" spans="1:23" ht="15.75">
       <c r="A51" s="1"/>
@@ -6190,19 +6181,19 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="247" t="s">
+      <c r="M51" s="257" t="s">
         <v>37</v>
       </c>
-      <c r="N51" s="248"/>
-      <c r="O51" s="248"/>
-      <c r="P51" s="248"/>
+      <c r="N51" s="258"/>
+      <c r="O51" s="258"/>
+      <c r="P51" s="258"/>
       <c r="Q51" s="18"/>
-      <c r="R51" s="128">
+      <c r="R51" s="127">
         <f>SUM(R3:R50)</f>
-        <v>332.06675999999999</v>
-      </c>
-      <c r="S51" s="128"/>
-      <c r="T51" s="90">
+        <v>332.07675999999998</v>
+      </c>
+      <c r="S51" s="127"/>
+      <c r="T51" s="89">
         <f>SUM(T3:T50)</f>
         <v>1216.0299</v>
       </c>
@@ -6218,19 +6209,19 @@
       <c r="I52" s="2"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="249" t="s">
+      <c r="M52" s="259" t="s">
         <v>38</v>
       </c>
-      <c r="N52" s="250"/>
-      <c r="O52" s="250"/>
-      <c r="P52" s="250"/>
+      <c r="N52" s="260"/>
+      <c r="O52" s="260"/>
+      <c r="P52" s="260"/>
       <c r="Q52" s="29"/>
-      <c r="R52" s="131">
+      <c r="R52" s="130">
         <f>R51/5</f>
-        <v>66.413352000000003</v>
-      </c>
-      <c r="S52" s="131"/>
-      <c r="T52" s="31">
+        <v>66.415351999999999</v>
+      </c>
+      <c r="S52" s="130"/>
+      <c r="T52" s="30">
         <f>T51/20</f>
         <v>60.801495000000003</v>
       </c>
@@ -6247,17 +6238,17 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="28"/>
-      <c r="N53" s="238" t="s">
-        <v>147</v>
-      </c>
-      <c r="O53" s="239"/>
-      <c r="P53" s="240"/>
-      <c r="Q53" s="127"/>
-      <c r="R53" s="129">
+      <c r="N53" s="248" t="s">
+        <v>145</v>
+      </c>
+      <c r="O53" s="249"/>
+      <c r="P53" s="250"/>
+      <c r="Q53" s="126"/>
+      <c r="R53" s="128">
         <v>3</v>
       </c>
-      <c r="S53" s="129"/>
-      <c r="T53" s="130">
+      <c r="S53" s="128"/>
+      <c r="T53" s="129">
         <v>3</v>
       </c>
       <c r="U53" s="7"/>
@@ -6273,17 +6264,17 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="256" t="s">
-        <v>250</v>
-      </c>
-      <c r="O54" s="257"/>
-      <c r="P54" s="258"/>
-      <c r="Q54" s="125"/>
-      <c r="R54" s="124">
+      <c r="N54" s="266" t="s">
+        <v>248</v>
+      </c>
+      <c r="O54" s="267"/>
+      <c r="P54" s="268"/>
+      <c r="Q54" s="124"/>
+      <c r="R54" s="123">
         <v>22.78</v>
       </c>
-      <c r="S54" s="124"/>
-      <c r="T54" s="132">
+      <c r="S54" s="123"/>
+      <c r="T54" s="131">
         <v>90.99</v>
       </c>
       <c r="U54" s="7"/>
@@ -6296,18 +6287,18 @@
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="N55" s="241" t="s">
-        <v>43</v>
-      </c>
-      <c r="O55" s="242"/>
-      <c r="P55" s="243"/>
+      <c r="N55" s="251" t="s">
+        <v>299</v>
+      </c>
+      <c r="O55" s="252"/>
+      <c r="P55" s="253"/>
       <c r="Q55" s="29"/>
-      <c r="R55" s="133">
+      <c r="R55" s="272">
         <f>SUM(R52:R54)</f>
-        <v>92.193352000000004</v>
-      </c>
-      <c r="S55" s="133"/>
-      <c r="T55" s="30">
+        <v>92.195352</v>
+      </c>
+      <c r="S55" s="132"/>
+      <c r="T55" s="273">
         <f>SUM(T52:T54)</f>
         <v>154.791495</v>
       </c>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FE2C59-4A88-4875-A9AF-6DAEAF3A04F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E4CAA0-8330-4AE9-90D8-95D5EB6C7219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6780" yWindow="3075" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="300">
   <si>
     <t>S. No.</t>
   </si>
@@ -2421,6 +2421,12 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2491,12 +2497,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2805,31 +2805,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="256" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="255"/>
-      <c r="J1" s="255"/>
-      <c r="K1" s="255"/>
-      <c r="L1" s="255"/>
-      <c r="M1" s="255"/>
-      <c r="N1" s="255"/>
-      <c r="O1" s="255"/>
-      <c r="P1" s="255"/>
-      <c r="Q1" s="255"/>
-      <c r="R1" s="255"/>
-      <c r="S1" s="255"/>
-      <c r="T1" s="255"/>
-      <c r="U1" s="255"/>
-      <c r="V1" s="255"/>
-      <c r="W1" s="256"/>
+      <c r="B1" s="257"/>
+      <c r="C1" s="257"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
+      <c r="G1" s="257"/>
+      <c r="H1" s="257"/>
+      <c r="I1" s="257"/>
+      <c r="J1" s="257"/>
+      <c r="K1" s="257"/>
+      <c r="L1" s="257"/>
+      <c r="M1" s="257"/>
+      <c r="N1" s="257"/>
+      <c r="O1" s="257"/>
+      <c r="P1" s="257"/>
+      <c r="Q1" s="257"/>
+      <c r="R1" s="257"/>
+      <c r="S1" s="257"/>
+      <c r="T1" s="257"/>
+      <c r="U1" s="257"/>
+      <c r="V1" s="257"/>
+      <c r="W1" s="258"/>
     </row>
     <row r="2" spans="1:23" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2906,7 +2906,7 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="261" t="s">
+      <c r="B3" s="263" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="59" t="s">
@@ -2975,7 +2975,7 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="262"/>
+      <c r="B4" s="264"/>
       <c r="C4" s="62" t="s">
         <v>21</v>
       </c>
@@ -3042,7 +3042,7 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="262"/>
+      <c r="B5" s="264"/>
       <c r="C5" s="62" t="s">
         <v>52</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="262"/>
+      <c r="B6" s="264"/>
       <c r="C6" s="62" t="s">
         <v>54</v>
       </c>
@@ -3176,7 +3176,7 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="262"/>
+      <c r="B7" s="264"/>
       <c r="C7" s="62" t="s">
         <v>153</v>
       </c>
@@ -3243,7 +3243,7 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="262"/>
+      <c r="B8" s="264"/>
       <c r="C8" s="62" t="s">
         <v>17</v>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="262"/>
+      <c r="B9" s="264"/>
       <c r="C9" s="62" t="s">
         <v>58</v>
       </c>
@@ -3377,7 +3377,7 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="262"/>
+      <c r="B10" s="264"/>
       <c r="C10" s="62" t="s">
         <v>61</v>
       </c>
@@ -3444,7 +3444,7 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="262"/>
+      <c r="B11" s="264"/>
       <c r="C11" s="62" t="s">
         <v>64</v>
       </c>
@@ -3511,7 +3511,7 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="262"/>
+      <c r="B12" s="264"/>
       <c r="C12" s="62" t="s">
         <v>158</v>
       </c>
@@ -3578,7 +3578,7 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="262"/>
+      <c r="B13" s="264"/>
       <c r="C13" s="62" t="s">
         <v>161</v>
       </c>
@@ -3645,7 +3645,7 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="262"/>
+      <c r="B14" s="264"/>
       <c r="C14" s="62" t="s">
         <v>212</v>
       </c>
@@ -3712,7 +3712,7 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="262"/>
+      <c r="B15" s="264"/>
       <c r="C15" s="62" t="s">
         <v>215</v>
       </c>
@@ -3779,7 +3779,7 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="262"/>
+      <c r="B16" s="264"/>
       <c r="C16" s="62" t="s">
         <v>249</v>
       </c>
@@ -3846,7 +3846,7 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="263"/>
+      <c r="B17" s="265"/>
       <c r="C17" s="96" t="s">
         <v>252</v>
       </c>
@@ -3913,7 +3913,7 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="264" t="s">
+      <c r="B18" s="266" t="s">
         <v>183</v>
       </c>
       <c r="C18" s="206" t="s">
@@ -3982,7 +3982,7 @@
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="265"/>
+      <c r="B19" s="267"/>
       <c r="C19" s="225" t="s">
         <v>218</v>
       </c>
@@ -4053,7 +4053,7 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="269" t="s">
+      <c r="B20" s="271" t="s">
         <v>188</v>
       </c>
       <c r="C20" s="59" t="s">
@@ -4122,7 +4122,7 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="271"/>
+      <c r="B21" s="273"/>
       <c r="C21" s="62" t="s">
         <v>225</v>
       </c>
@@ -4191,7 +4191,7 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="271"/>
+      <c r="B22" s="273"/>
       <c r="C22" s="62" t="s">
         <v>228</v>
       </c>
@@ -4258,7 +4258,7 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="270"/>
+      <c r="B23" s="272"/>
       <c r="C23" s="96" t="s">
         <v>259</v>
       </c>
@@ -4469,7 +4469,7 @@
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="262" t="s">
+      <c r="B26" s="264" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="234" t="s">
@@ -4540,7 +4540,7 @@
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="262"/>
+      <c r="B27" s="264"/>
       <c r="C27" s="158" t="s">
         <v>80</v>
       </c>
@@ -4609,7 +4609,7 @@
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="262"/>
+      <c r="B28" s="264"/>
       <c r="C28" s="86" t="s">
         <v>164</v>
       </c>
@@ -4676,7 +4676,7 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="261" t="s">
+      <c r="B29" s="263" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="68" t="s">
@@ -4745,7 +4745,7 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="262"/>
+      <c r="B30" s="264"/>
       <c r="C30" s="73" t="s">
         <v>264</v>
       </c>
@@ -4812,7 +4812,7 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="262"/>
+      <c r="B31" s="264"/>
       <c r="C31" s="73" t="s">
         <v>169</v>
       </c>
@@ -4879,7 +4879,7 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="262"/>
+      <c r="B32" s="264"/>
       <c r="C32" s="73" t="s">
         <v>234</v>
       </c>
@@ -4946,7 +4946,7 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="263"/>
+      <c r="B33" s="265"/>
       <c r="C33" s="70" t="s">
         <v>85</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="262" t="s">
+      <c r="B34" s="264" t="s">
         <v>104</v>
       </c>
       <c r="C34" s="209" t="s">
@@ -5086,7 +5086,7 @@
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="262"/>
+      <c r="B35" s="264"/>
       <c r="C35" s="158" t="s">
         <v>92</v>
       </c>
@@ -5155,7 +5155,7 @@
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="262"/>
+      <c r="B36" s="264"/>
       <c r="C36" s="140" t="s">
         <v>95</v>
       </c>
@@ -5224,7 +5224,7 @@
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="262"/>
+      <c r="B37" s="264"/>
       <c r="C37" s="77" t="s">
         <v>98</v>
       </c>
@@ -5297,7 +5297,7 @@
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="262"/>
+      <c r="B38" s="264"/>
       <c r="C38" s="73" t="s">
         <v>173</v>
       </c>
@@ -5364,7 +5364,7 @@
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="262"/>
+      <c r="B39" s="264"/>
       <c r="C39" s="73" t="s">
         <v>176</v>
       </c>
@@ -5431,7 +5431,7 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="262"/>
+      <c r="B40" s="264"/>
       <c r="C40" s="140" t="s">
         <v>267</v>
       </c>
@@ -5447,7 +5447,9 @@
       <c r="G40" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="H40" s="143"/>
+      <c r="H40" s="143" t="s">
+        <v>39</v>
+      </c>
       <c r="I40" s="143" t="s">
         <v>39</v>
       </c>
@@ -5500,7 +5502,7 @@
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="262"/>
+      <c r="B41" s="264"/>
       <c r="C41" s="140" t="s">
         <v>280</v>
       </c>
@@ -5569,7 +5571,7 @@
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="262"/>
+      <c r="B42" s="264"/>
       <c r="C42" s="86" t="s">
         <v>101</v>
       </c>
@@ -5636,7 +5638,7 @@
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="261" t="s">
+      <c r="B43" s="263" t="s">
         <v>109</v>
       </c>
       <c r="C43" s="68" t="s">
@@ -5705,7 +5707,7 @@
       <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B44" s="262"/>
+      <c r="B44" s="264"/>
       <c r="C44" s="73" t="s">
         <v>287</v>
       </c>
@@ -5772,7 +5774,7 @@
       <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B45" s="262"/>
+      <c r="B45" s="264"/>
       <c r="C45" s="73" t="s">
         <v>107</v>
       </c>
@@ -5839,7 +5841,7 @@
       <c r="A46" s="6">
         <v>44</v>
       </c>
-      <c r="B46" s="262"/>
+      <c r="B46" s="264"/>
       <c r="C46" s="158" t="s">
         <v>270</v>
       </c>
@@ -5906,7 +5908,7 @@
       <c r="A47" s="6">
         <v>45</v>
       </c>
-      <c r="B47" s="262"/>
+      <c r="B47" s="264"/>
       <c r="C47" s="73" t="s">
         <v>284</v>
       </c>
@@ -5973,7 +5975,7 @@
       <c r="A48" s="6">
         <v>46</v>
       </c>
-      <c r="B48" s="263"/>
+      <c r="B48" s="265"/>
       <c r="C48" s="99" t="s">
         <v>35</v>
       </c>
@@ -6036,7 +6038,7 @@
       <c r="A49" s="6">
         <v>47</v>
       </c>
-      <c r="B49" s="269" t="s">
+      <c r="B49" s="271" t="s">
         <v>149</v>
       </c>
       <c r="C49" s="213" t="s">
@@ -6105,7 +6107,7 @@
       <c r="A50" s="224">
         <v>48</v>
       </c>
-      <c r="B50" s="270"/>
+      <c r="B50" s="272"/>
       <c r="C50" s="117" t="s">
         <v>150</v>
       </c>
@@ -6181,12 +6183,12 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="257" t="s">
+      <c r="M51" s="259" t="s">
         <v>37</v>
       </c>
-      <c r="N51" s="258"/>
-      <c r="O51" s="258"/>
-      <c r="P51" s="258"/>
+      <c r="N51" s="260"/>
+      <c r="O51" s="260"/>
+      <c r="P51" s="260"/>
       <c r="Q51" s="18"/>
       <c r="R51" s="127">
         <f>SUM(R3:R50)</f>
@@ -6209,12 +6211,12 @@
       <c r="I52" s="2"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="259" t="s">
+      <c r="M52" s="261" t="s">
         <v>38</v>
       </c>
-      <c r="N52" s="260"/>
-      <c r="O52" s="260"/>
-      <c r="P52" s="260"/>
+      <c r="N52" s="262"/>
+      <c r="O52" s="262"/>
+      <c r="P52" s="262"/>
       <c r="Q52" s="29"/>
       <c r="R52" s="130">
         <f>R51/5</f>
@@ -6238,11 +6240,11 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="28"/>
-      <c r="N53" s="248" t="s">
+      <c r="N53" s="250" t="s">
         <v>145</v>
       </c>
-      <c r="O53" s="249"/>
-      <c r="P53" s="250"/>
+      <c r="O53" s="251"/>
+      <c r="P53" s="252"/>
       <c r="Q53" s="126"/>
       <c r="R53" s="128">
         <v>3</v>
@@ -6264,11 +6266,11 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="266" t="s">
+      <c r="N54" s="268" t="s">
         <v>248</v>
       </c>
-      <c r="O54" s="267"/>
-      <c r="P54" s="268"/>
+      <c r="O54" s="269"/>
+      <c r="P54" s="270"/>
       <c r="Q54" s="124"/>
       <c r="R54" s="123">
         <v>22.78</v>
@@ -6287,18 +6289,18 @@
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="N55" s="251" t="s">
+      <c r="N55" s="253" t="s">
         <v>299</v>
       </c>
-      <c r="O55" s="252"/>
-      <c r="P55" s="253"/>
+      <c r="O55" s="254"/>
+      <c r="P55" s="255"/>
       <c r="Q55" s="29"/>
-      <c r="R55" s="272">
+      <c r="R55" s="248">
         <f>SUM(R52:R54)</f>
         <v>92.195352</v>
       </c>
       <c r="S55" s="132"/>
-      <c r="T55" s="273">
+      <c r="T55" s="249">
         <f>SUM(T52:T54)</f>
         <v>154.791495</v>
       </c>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E4CAA0-8330-4AE9-90D8-95D5EB6C7219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6780" yWindow="3075" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6780" yWindow="3075" windowWidth="11790" windowHeight="15360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="301">
   <si>
     <t>S. No.</t>
   </si>
@@ -936,12 +935,15 @@
   </si>
   <si>
     <t>Total with Shipping Single Board</t>
+  </si>
+  <si>
+    <t>Alternate Supplier</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -1690,7 +1692,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="274">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2497,6 +2499,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2774,7 +2779,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -5562,8 +5567,8 @@
         <v>30</v>
       </c>
       <c r="U41" s="165"/>
-      <c r="V41" s="148" t="s">
-        <v>291</v>
+      <c r="V41" s="274" t="s">
+        <v>300</v>
       </c>
       <c r="W41" s="149"/>
     </row>
@@ -6543,52 +6548,53 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="P3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="P4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="P5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="P6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="P8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="P9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="P10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="P11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="P25" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="P26" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="P27" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="P29" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="P33" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="P35" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="P42" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="P43" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="P45" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="P24" r:id="rId18" display="Aliexpress" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="P44" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="P7" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="P12" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="P13" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="P18" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="P20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="P28" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="P31" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="P38" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="P39" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="P14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="P15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="P32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="P50" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="P49" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="P16" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="P17" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="P30" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="P46" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="P41" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="P47" r:id="rId39" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="P19" r:id="rId40" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="P40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="P23" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="P22" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="P3" r:id="rId1"/>
+    <hyperlink ref="P4" r:id="rId2"/>
+    <hyperlink ref="P5" r:id="rId3"/>
+    <hyperlink ref="P6" r:id="rId4"/>
+    <hyperlink ref="P8" r:id="rId5"/>
+    <hyperlink ref="P9" r:id="rId6"/>
+    <hyperlink ref="P10" r:id="rId7"/>
+    <hyperlink ref="P11" r:id="rId8"/>
+    <hyperlink ref="P25" r:id="rId9"/>
+    <hyperlink ref="P26" r:id="rId10"/>
+    <hyperlink ref="P27" r:id="rId11"/>
+    <hyperlink ref="P29" r:id="rId12"/>
+    <hyperlink ref="P33" r:id="rId13"/>
+    <hyperlink ref="P35" r:id="rId14"/>
+    <hyperlink ref="P42" r:id="rId15"/>
+    <hyperlink ref="P43" r:id="rId16"/>
+    <hyperlink ref="P45" r:id="rId17"/>
+    <hyperlink ref="P24" r:id="rId18" display="Aliexpress"/>
+    <hyperlink ref="P44" r:id="rId19"/>
+    <hyperlink ref="P7" r:id="rId20"/>
+    <hyperlink ref="P12" r:id="rId21"/>
+    <hyperlink ref="P13" r:id="rId22"/>
+    <hyperlink ref="P18" r:id="rId23"/>
+    <hyperlink ref="P20" r:id="rId24"/>
+    <hyperlink ref="P28" r:id="rId25"/>
+    <hyperlink ref="P31" r:id="rId26"/>
+    <hyperlink ref="P38" r:id="rId27"/>
+    <hyperlink ref="P39" r:id="rId28"/>
+    <hyperlink ref="P14" r:id="rId29"/>
+    <hyperlink ref="P15" r:id="rId30"/>
+    <hyperlink ref="P32" r:id="rId31"/>
+    <hyperlink ref="P50" r:id="rId32"/>
+    <hyperlink ref="P49" r:id="rId33"/>
+    <hyperlink ref="P16" r:id="rId34"/>
+    <hyperlink ref="P17" r:id="rId35"/>
+    <hyperlink ref="P30" r:id="rId36"/>
+    <hyperlink ref="P46" r:id="rId37"/>
+    <hyperlink ref="P41" r:id="rId38"/>
+    <hyperlink ref="P47" r:id="rId39"/>
+    <hyperlink ref="P19" r:id="rId40"/>
+    <hyperlink ref="P40" r:id="rId41"/>
+    <hyperlink ref="P23" r:id="rId42"/>
+    <hyperlink ref="P22" r:id="rId43"/>
+    <hyperlink ref="V41" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId44"/>
+  <pageSetup orientation="portrait" r:id="rId45"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC81F34F-75C6-4364-8E27-6C68E0DE9D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6780" yWindow="3075" windowWidth="11790" windowHeight="15360"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="306">
   <si>
     <t>S. No.</t>
   </si>
@@ -938,12 +939,27 @@
   </si>
   <si>
     <t>Alternate Supplier</t>
+  </si>
+  <si>
+    <t>R11, R12</t>
+  </si>
+  <si>
+    <t>RC0603JR-075K1L</t>
+  </si>
+  <si>
+    <t>RES SMD 5.1K OHM 5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>5.1K</t>
+  </si>
+  <si>
+    <t>C14677</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -1205,7 +1221,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1683,6 +1699,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1692,7 +1721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1895,613 +1924,619 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2779,8 +2814,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -2810,31 +2845,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="253" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="257"/>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
-      <c r="G1" s="257"/>
-      <c r="H1" s="257"/>
-      <c r="I1" s="257"/>
-      <c r="J1" s="257"/>
-      <c r="K1" s="257"/>
-      <c r="L1" s="257"/>
-      <c r="M1" s="257"/>
-      <c r="N1" s="257"/>
-      <c r="O1" s="257"/>
-      <c r="P1" s="257"/>
-      <c r="Q1" s="257"/>
-      <c r="R1" s="257"/>
-      <c r="S1" s="257"/>
-      <c r="T1" s="257"/>
-      <c r="U1" s="257"/>
-      <c r="V1" s="257"/>
-      <c r="W1" s="258"/>
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="254"/>
+      <c r="J1" s="254"/>
+      <c r="K1" s="254"/>
+      <c r="L1" s="254"/>
+      <c r="M1" s="254"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="254"/>
+      <c r="P1" s="254"/>
+      <c r="Q1" s="254"/>
+      <c r="R1" s="254"/>
+      <c r="S1" s="254"/>
+      <c r="T1" s="254"/>
+      <c r="U1" s="254"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2870,7 +2905,7 @@
       <c r="K2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="122" t="s">
+      <c r="L2" s="121" t="s">
         <v>244</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -2894,13 +2929,13 @@
       <c r="S2" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="T2" s="122" t="s">
+      <c r="T2" s="121" t="s">
         <v>243</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="122" t="s">
+      <c r="V2" s="121" t="s">
         <v>292</v>
       </c>
       <c r="W2" s="5" t="s">
@@ -2911,13 +2946,13 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="260" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="115" t="s">
         <v>157</v>
       </c>
       <c r="E3" s="60" t="s">
@@ -2980,11 +3015,11 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="264"/>
+      <c r="B4" s="261"/>
       <c r="C4" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="84" t="s">
+      <c r="D4" s="83" t="s">
         <v>50</v>
       </c>
       <c r="E4" s="63" t="s">
@@ -3015,11 +3050,11 @@
         <v>1</v>
       </c>
       <c r="N4" s="64">
-        <f t="shared" ref="N4:N48" si="0">M4*5</f>
+        <f t="shared" ref="N4:N49" si="0">M4*5</f>
         <v>5</v>
       </c>
       <c r="O4" s="64">
-        <f t="shared" ref="O4:O50" si="1">M4*20</f>
+        <f t="shared" ref="O4:O51" si="1">M4*20</f>
         <v>20</v>
       </c>
       <c r="P4" s="65" t="s">
@@ -3028,15 +3063,15 @@
       <c r="Q4" s="42">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="R4" s="90">
-        <f t="shared" ref="R4:R47" si="2">Q4*K4</f>
+      <c r="R4" s="89">
+        <f t="shared" ref="R4:R48" si="2">Q4*K4</f>
         <v>0.41599999999999998</v>
       </c>
-      <c r="S4" s="90">
+      <c r="S4" s="89">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="T4" s="90">
-        <f t="shared" ref="T4:T47" si="3">S4*L4</f>
+      <c r="T4" s="89">
+        <f t="shared" ref="T4:T48" si="3">S4*L4</f>
         <v>0.83199999999999996</v>
       </c>
       <c r="U4" s="13"/>
@@ -3047,11 +3082,11 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="264"/>
+      <c r="B5" s="261"/>
       <c r="C5" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="115" t="s">
+      <c r="D5" s="114" t="s">
         <v>152</v>
       </c>
       <c r="E5" s="40" t="s">
@@ -3095,14 +3130,14 @@
       <c r="Q5" s="42">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="R5" s="90">
+      <c r="R5" s="89">
         <f t="shared" si="2"/>
         <v>0.71000000000000008</v>
       </c>
-      <c r="S5" s="90">
+      <c r="S5" s="89">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="T5" s="90">
+      <c r="T5" s="89">
         <f t="shared" si="3"/>
         <v>2.8400000000000003</v>
       </c>
@@ -3114,11 +3149,11 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="264"/>
+      <c r="B6" s="261"/>
       <c r="C6" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="83" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="63" t="s">
@@ -3162,14 +3197,14 @@
       <c r="Q6" s="42">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="R6" s="90">
+      <c r="R6" s="89">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="S6" s="90">
+      <c r="S6" s="89">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="T6" s="90">
+      <c r="T6" s="89">
         <f t="shared" si="3"/>
         <v>0.67999999999999994</v>
       </c>
@@ -3181,17 +3216,17 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="264"/>
+      <c r="B7" s="261"/>
       <c r="C7" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="D7" s="84" t="s">
+      <c r="D7" s="83" t="s">
         <v>154</v>
       </c>
       <c r="E7" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="88" t="s">
+      <c r="F7" s="87" t="s">
         <v>156</v>
       </c>
       <c r="G7" s="44" t="s">
@@ -3223,20 +3258,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P7" s="87" t="s">
+      <c r="P7" s="86" t="s">
         <v>16</v>
       </c>
       <c r="Q7" s="42">
         <v>1.4E-3</v>
       </c>
-      <c r="R7" s="90">
+      <c r="R7" s="89">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S7" s="90">
+      <c r="S7" s="89">
         <v>1.4E-3</v>
       </c>
-      <c r="T7" s="90">
+      <c r="T7" s="89">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
@@ -3248,11 +3283,11 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="264"/>
+      <c r="B8" s="261"/>
       <c r="C8" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="115" t="s">
+      <c r="D8" s="114" t="s">
         <v>211</v>
       </c>
       <c r="E8" s="40" t="s">
@@ -3296,14 +3331,14 @@
       <c r="Q8" s="42">
         <v>7.4000000000000003E-3</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="89">
         <f t="shared" si="2"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="89">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="T8" s="90">
+      <c r="T8" s="89">
         <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
@@ -3315,11 +3350,11 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="264"/>
+      <c r="B9" s="261"/>
       <c r="C9" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="84" t="s">
+      <c r="D9" s="83" t="s">
         <v>59</v>
       </c>
       <c r="E9" s="63" t="s">
@@ -3363,14 +3398,14 @@
       <c r="Q9" s="42">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="R9" s="90">
+      <c r="R9" s="89">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
-      <c r="S9" s="90">
+      <c r="S9" s="89">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="T9" s="90">
+      <c r="T9" s="89">
         <f t="shared" si="3"/>
         <v>1.1099999999999999</v>
       </c>
@@ -3382,11 +3417,11 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="264"/>
+      <c r="B10" s="261"/>
       <c r="C10" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="84" t="s">
+      <c r="D10" s="83" t="s">
         <v>62</v>
       </c>
       <c r="E10" s="63" t="s">
@@ -3430,14 +3465,14 @@
       <c r="Q10" s="42">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="R10" s="90">
+      <c r="R10" s="89">
         <f t="shared" si="2"/>
         <v>0.35000000000000003</v>
       </c>
-      <c r="S10" s="90">
+      <c r="S10" s="89">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="T10" s="90">
+      <c r="T10" s="89">
         <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
@@ -3449,11 +3484,11 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="264"/>
+      <c r="B11" s="261"/>
       <c r="C11" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="115" t="s">
+      <c r="D11" s="114" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="40" t="s">
@@ -3497,14 +3532,14 @@
       <c r="Q11" s="42">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="R11" s="90">
+      <c r="R11" s="89">
         <f t="shared" si="2"/>
         <v>1.5599999999999998</v>
       </c>
-      <c r="S11" s="90">
+      <c r="S11" s="89">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="T11" s="90">
+      <c r="T11" s="89">
         <f t="shared" si="3"/>
         <v>5.46</v>
       </c>
@@ -3516,11 +3551,11 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="264"/>
+      <c r="B12" s="261"/>
       <c r="C12" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="84" t="s">
+      <c r="D12" s="83" t="s">
         <v>159</v>
       </c>
       <c r="E12" s="63" t="s">
@@ -3558,20 +3593,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P12" s="91" t="s">
+      <c r="P12" s="90" t="s">
         <v>16</v>
       </c>
       <c r="Q12" s="42">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="R12" s="90">
+      <c r="R12" s="89">
         <f t="shared" si="2"/>
         <v>0.245</v>
       </c>
-      <c r="S12" s="90">
+      <c r="S12" s="89">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="T12" s="90">
+      <c r="T12" s="89">
         <f t="shared" si="3"/>
         <v>0.245</v>
       </c>
@@ -3583,17 +3618,17 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="264"/>
+      <c r="B13" s="261"/>
       <c r="C13" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="D13" s="115" t="s">
+      <c r="D13" s="114" t="s">
         <v>162</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="F13" s="76" t="s">
+      <c r="F13" s="75" t="s">
         <v>163</v>
       </c>
       <c r="G13" s="44" t="s">
@@ -3625,20 +3660,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P13" s="91" t="s">
+      <c r="P13" s="90" t="s">
         <v>16</v>
       </c>
       <c r="Q13" s="42">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R13" s="90">
+      <c r="R13" s="89">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S13" s="90">
+      <c r="S13" s="89">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T13" s="90">
+      <c r="T13" s="89">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
@@ -3650,11 +3685,11 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="264"/>
+      <c r="B14" s="261"/>
       <c r="C14" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="D14" s="84" t="s">
+      <c r="D14" s="83" t="s">
         <v>213</v>
       </c>
       <c r="E14" s="63" t="s">
@@ -3692,20 +3727,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P14" s="91" t="s">
+      <c r="P14" s="90" t="s">
         <v>16</v>
       </c>
       <c r="Q14" s="42">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="R14" s="90">
+      <c r="R14" s="89">
         <f t="shared" si="2"/>
         <v>0.38999999999999996</v>
       </c>
-      <c r="S14" s="90">
+      <c r="S14" s="89">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="T14" s="90">
+      <c r="T14" s="89">
         <f t="shared" si="3"/>
         <v>0.38999999999999996</v>
       </c>
@@ -3717,11 +3752,11 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="264"/>
+      <c r="B15" s="261"/>
       <c r="C15" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="D15" s="84" t="s">
+      <c r="D15" s="83" t="s">
         <v>216</v>
       </c>
       <c r="E15" s="63" t="s">
@@ -3759,20 +3794,20 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P15" s="91" t="s">
+      <c r="P15" s="90" t="s">
         <v>16</v>
       </c>
       <c r="Q15" s="42">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="R15" s="90">
+      <c r="R15" s="89">
         <f t="shared" si="2"/>
         <v>0.27</v>
       </c>
-      <c r="S15" s="90">
+      <c r="S15" s="89">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="T15" s="90">
+      <c r="T15" s="89">
         <f t="shared" si="3"/>
         <v>0.27</v>
       </c>
@@ -3784,11 +3819,11 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="264"/>
+      <c r="B16" s="261"/>
       <c r="C16" s="62" t="s">
         <v>249</v>
       </c>
-      <c r="D16" s="84" t="s">
+      <c r="D16" s="83" t="s">
         <v>250</v>
       </c>
       <c r="E16" s="63" t="s">
@@ -3826,20 +3861,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P16" s="91" t="s">
+      <c r="P16" s="90" t="s">
         <v>16</v>
       </c>
       <c r="Q16" s="42">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="R16" s="90">
+      <c r="R16" s="89">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="S16" s="90">
+      <c r="S16" s="89">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="T16" s="90">
+      <c r="T16" s="89">
         <f>S16*L16</f>
         <v>0.32</v>
       </c>
@@ -3851,17 +3886,17 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="265"/>
-      <c r="C17" s="96" t="s">
+      <c r="B17" s="262"/>
+      <c r="C17" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="D17" s="121" t="s">
+      <c r="D17" s="120" t="s">
         <v>253</v>
       </c>
-      <c r="E17" s="113" t="s">
+      <c r="E17" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="113" t="s">
+      <c r="F17" s="112" t="s">
         <v>254</v>
       </c>
       <c r="G17" s="50" t="s">
@@ -3873,7 +3908,7 @@
       <c r="I17" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="71" t="s">
+      <c r="J17" s="70" t="s">
         <v>258</v>
       </c>
       <c r="K17" s="50">
@@ -3893,20 +3928,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P17" s="94" t="s">
+      <c r="P17" s="93" t="s">
         <v>16</v>
       </c>
       <c r="Q17" s="54">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="R17" s="95">
+      <c r="R17" s="94">
         <f t="shared" si="2"/>
         <v>0.39500000000000002</v>
       </c>
-      <c r="S17" s="95">
+      <c r="S17" s="94">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="T17" s="95">
+      <c r="T17" s="94">
         <f>S17*L17</f>
         <v>0.39500000000000002</v>
       </c>
@@ -3918,37 +3953,37 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="266" t="s">
+      <c r="B18" s="263" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="206" t="s">
+      <c r="C18" s="201" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="168" t="s">
+      <c r="D18" s="163" t="s">
         <v>181</v>
       </c>
-      <c r="E18" s="169" t="s">
+      <c r="E18" s="164" t="s">
         <v>294</v>
       </c>
-      <c r="F18" s="170" t="s">
+      <c r="F18" s="165" t="s">
         <v>182</v>
       </c>
-      <c r="G18" s="171" t="s">
+      <c r="G18" s="166" t="s">
         <v>197</v>
       </c>
-      <c r="H18" s="172" t="s">
+      <c r="H18" s="167" t="s">
         <v>196</v>
       </c>
-      <c r="I18" s="173" t="s">
+      <c r="I18" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="170" t="s">
+      <c r="J18" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="171">
+      <c r="K18" s="166">
         <v>10</v>
       </c>
-      <c r="L18" s="171">
+      <c r="L18" s="166">
         <v>30</v>
       </c>
       <c r="M18" s="41">
@@ -3962,10 +3997,10 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="174" t="s">
+      <c r="P18" s="169" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="175">
+      <c r="Q18" s="170">
         <v>6.9699999999999998E-2</v>
       </c>
       <c r="R18" s="43">
@@ -3979,25 +4014,25 @@
         <f t="shared" si="3"/>
         <v>2.0909999999999997</v>
       </c>
-      <c r="U18" s="176"/>
-      <c r="V18" s="176"/>
-      <c r="W18" s="220"/>
+      <c r="U18" s="171"/>
+      <c r="V18" s="171"/>
+      <c r="W18" s="215"/>
     </row>
     <row r="19" spans="1:23" ht="16.5" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="267"/>
-      <c r="C19" s="225" t="s">
+      <c r="B19" s="264"/>
+      <c r="C19" s="219" t="s">
         <v>218</v>
       </c>
-      <c r="D19" s="226" t="s">
+      <c r="D19" s="220" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="226" t="s">
+      <c r="E19" s="220" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="226" t="s">
+      <c r="F19" s="220" t="s">
         <v>220</v>
       </c>
       <c r="G19" s="48" t="s">
@@ -4009,7 +4044,7 @@
       <c r="I19" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="226" t="s">
+      <c r="J19" s="220" t="s">
         <v>22</v>
       </c>
       <c r="K19" s="48">
@@ -4018,39 +4053,39 @@
       <c r="L19" s="48">
         <v>50</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="221">
         <v>2</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="221">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="221">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="228" t="s">
+      <c r="P19" s="222" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="229">
+      <c r="Q19" s="223">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="R19" s="230">
+      <c r="R19" s="224">
         <f t="shared" si="2"/>
         <v>0.39399999999999996</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="224">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="T19" s="230">
+      <c r="T19" s="224">
         <f t="shared" si="3"/>
         <v>1.97</v>
       </c>
-      <c r="U19" s="231"/>
-      <c r="V19" s="232" t="s">
+      <c r="U19" s="225"/>
+      <c r="V19" s="226" t="s">
         <v>291</v>
       </c>
-      <c r="W19" s="233" t="s">
+      <c r="W19" s="227" t="s">
         <v>297</v>
       </c>
     </row>
@@ -4058,13 +4093,13 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="271" t="s">
+      <c r="B20" s="268" t="s">
         <v>188</v>
       </c>
       <c r="C20" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="116" t="s">
+      <c r="D20" s="115" t="s">
         <v>185</v>
       </c>
       <c r="E20" s="60" t="s">
@@ -4102,7 +4137,7 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P20" s="114" t="s">
+      <c r="P20" s="113" t="s">
         <v>16</v>
       </c>
       <c r="Q20" s="36">
@@ -4127,11 +4162,11 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="273"/>
+      <c r="B21" s="270"/>
       <c r="C21" s="62" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="84" t="s">
+      <c r="D21" s="83" t="s">
         <v>226</v>
       </c>
       <c r="E21" s="63" t="s">
@@ -4169,20 +4204,20 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P21" s="190" t="s">
+      <c r="P21" s="185" t="s">
         <v>151</v>
       </c>
       <c r="Q21" s="42">
         <v>0.11208</v>
       </c>
-      <c r="R21" s="90">
+      <c r="R21" s="89">
         <f t="shared" si="2"/>
         <v>1.3449599999999999</v>
       </c>
-      <c r="S21" s="90">
+      <c r="S21" s="89">
         <v>0.11208</v>
       </c>
-      <c r="T21" s="90">
+      <c r="T21" s="89">
         <f t="shared" si="3"/>
         <v>5.0435999999999996</v>
       </c>
@@ -4196,11 +4231,11 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="273"/>
+      <c r="B22" s="270"/>
       <c r="C22" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="D22" s="84" t="s">
+      <c r="D22" s="83" t="s">
         <v>229</v>
       </c>
       <c r="E22" s="63" t="s">
@@ -4238,20 +4273,20 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P22" s="91" t="s">
+      <c r="P22" s="90" t="s">
         <v>16</v>
       </c>
       <c r="Q22" s="42">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="R22" s="90">
+      <c r="R22" s="89">
         <f t="shared" si="2"/>
         <v>0.39500000000000002</v>
       </c>
-      <c r="S22" s="90">
+      <c r="S22" s="89">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="T22" s="90">
+      <c r="T22" s="89">
         <f t="shared" si="3"/>
         <v>0.39500000000000002</v>
       </c>
@@ -4263,17 +4298,17 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="272"/>
-      <c r="C23" s="96" t="s">
+      <c r="B23" s="269"/>
+      <c r="C23" s="95" t="s">
         <v>259</v>
       </c>
-      <c r="D23" s="121" t="s">
+      <c r="D23" s="120" t="s">
         <v>260</v>
       </c>
-      <c r="E23" s="113" t="s">
+      <c r="E23" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="113" t="s">
+      <c r="F23" s="112" t="s">
         <v>261</v>
       </c>
       <c r="G23" s="50" t="s">
@@ -4285,7 +4320,7 @@
       <c r="I23" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="71" t="s">
+      <c r="J23" s="70" t="s">
         <v>204</v>
       </c>
       <c r="K23" s="50">
@@ -4305,20 +4340,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P23" s="94" t="s">
+      <c r="P23" s="93" t="s">
         <v>16</v>
       </c>
       <c r="Q23" s="54">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="R23" s="95">
+      <c r="R23" s="94">
         <f t="shared" si="2"/>
         <v>0.45100000000000001</v>
       </c>
-      <c r="S23" s="95">
+      <c r="S23" s="94">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="T23" s="95">
+      <c r="T23" s="94">
         <f t="shared" si="3"/>
         <v>1.353</v>
       </c>
@@ -4330,74 +4365,74 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="157" t="s">
+      <c r="B24" s="245" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="207" t="s">
+      <c r="C24" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="186" t="s">
+      <c r="D24" s="181" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="187" t="s">
+      <c r="E24" s="182" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="187" t="s">
+      <c r="F24" s="182" t="s">
         <v>74</v>
       </c>
-      <c r="G24" s="188" t="s">
+      <c r="G24" s="183" t="s">
         <v>144</v>
       </c>
-      <c r="H24" s="188" t="s">
+      <c r="H24" s="183" t="s">
         <v>142</v>
       </c>
-      <c r="I24" s="187" t="s">
+      <c r="I24" s="182" t="s">
         <v>143</v>
       </c>
-      <c r="J24" s="187" t="s">
+      <c r="J24" s="182" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="187">
+      <c r="K24" s="182">
         <v>42</v>
       </c>
-      <c r="L24" s="187">
+      <c r="L24" s="182">
         <v>162</v>
       </c>
-      <c r="M24" s="189">
+      <c r="M24" s="184">
         <v>8</v>
       </c>
-      <c r="N24" s="189">
+      <c r="N24" s="184">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="189">
+      <c r="O24" s="184">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="190" t="s">
+      <c r="P24" s="185" t="s">
         <v>151</v>
       </c>
-      <c r="Q24" s="191">
+      <c r="Q24" s="186">
         <v>3.68</v>
       </c>
-      <c r="R24" s="192">
+      <c r="R24" s="187">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="192">
+      <c r="S24" s="187">
         <v>3.68</v>
       </c>
-      <c r="T24" s="192">
+      <c r="T24" s="187">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="193" t="s">
+      <c r="U24" s="188" t="s">
         <v>245</v>
       </c>
-      <c r="V24" s="194" t="s">
+      <c r="V24" s="189" t="s">
         <v>291</v>
       </c>
-      <c r="W24" s="221">
+      <c r="W24" s="216">
         <v>3.68</v>
       </c>
     </row>
@@ -4405,157 +4440,157 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="210" t="s">
+      <c r="B25" s="205" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="208" t="s">
+      <c r="C25" s="203" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="195" t="s">
+      <c r="D25" s="190" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="196" t="s">
+      <c r="E25" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="196" t="s">
+      <c r="F25" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="197" t="s">
+      <c r="G25" s="192" t="s">
         <v>121</v>
       </c>
-      <c r="H25" s="198" t="s">
+      <c r="H25" s="193" t="s">
         <v>122</v>
       </c>
-      <c r="I25" s="199" t="s">
+      <c r="I25" s="194" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="196" t="s">
+      <c r="J25" s="191" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="196">
+      <c r="K25" s="191">
         <v>10</v>
       </c>
-      <c r="L25" s="196">
+      <c r="L25" s="191">
         <v>30</v>
       </c>
-      <c r="M25" s="200">
+      <c r="M25" s="195">
         <v>1</v>
       </c>
-      <c r="N25" s="200">
+      <c r="N25" s="195">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="200">
+      <c r="O25" s="195">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="201" t="s">
+      <c r="P25" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="202">
+      <c r="Q25" s="197">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="R25" s="203">
+      <c r="R25" s="198">
         <f t="shared" si="2"/>
         <v>0.59699999999999998</v>
       </c>
-      <c r="S25" s="203">
+      <c r="S25" s="198">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="T25" s="203">
+      <c r="T25" s="198">
         <f t="shared" si="3"/>
         <v>1.7910000000000001</v>
       </c>
-      <c r="U25" s="204"/>
-      <c r="V25" s="204"/>
-      <c r="W25" s="205"/>
+      <c r="U25" s="199"/>
+      <c r="V25" s="199"/>
+      <c r="W25" s="200"/>
     </row>
     <row r="26" spans="1:23" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="264" t="s">
+      <c r="B26" s="261" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="234" t="s">
+      <c r="C26" s="228" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="235" t="s">
+      <c r="D26" s="229" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="235" t="s">
+      <c r="E26" s="229" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="235" t="s">
+      <c r="F26" s="229" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="236" t="s">
+      <c r="G26" s="230" t="s">
         <v>123</v>
       </c>
-      <c r="H26" s="237" t="s">
+      <c r="H26" s="231" t="s">
         <v>124</v>
       </c>
-      <c r="I26" s="236" t="s">
+      <c r="I26" s="230" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="235" t="s">
+      <c r="J26" s="229" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="235">
+      <c r="K26" s="229">
         <v>7</v>
       </c>
-      <c r="L26" s="235">
+      <c r="L26" s="229">
         <v>22</v>
       </c>
-      <c r="M26" s="238">
+      <c r="M26" s="232">
         <v>1</v>
       </c>
-      <c r="N26" s="238">
+      <c r="N26" s="232">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O26" s="239">
+      <c r="O26" s="233">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P26" s="240" t="s">
+      <c r="P26" s="234" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="241">
+      <c r="Q26" s="235">
         <v>0.21840000000000001</v>
       </c>
-      <c r="R26" s="242">
+      <c r="R26" s="236">
         <f>Q26*K26</f>
         <v>1.5288000000000002</v>
       </c>
-      <c r="S26" s="242">
+      <c r="S26" s="236">
         <v>0.1774</v>
       </c>
-      <c r="T26" s="243">
+      <c r="T26" s="237">
         <f t="shared" si="3"/>
         <v>3.9028</v>
       </c>
-      <c r="U26" s="244"/>
-      <c r="V26" s="245" t="s">
+      <c r="U26" s="238"/>
+      <c r="V26" s="239" t="s">
         <v>291</v>
       </c>
-      <c r="W26" s="246"/>
+      <c r="W26" s="240"/>
     </row>
     <row r="27" spans="1:23" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="264"/>
-      <c r="C27" s="158" t="s">
+      <c r="B27" s="261"/>
+      <c r="C27" s="153" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="115" t="s">
+      <c r="D27" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="84" t="s">
+      <c r="E27" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="84" t="s">
+      <c r="F27" s="83" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="39" t="s">
@@ -4567,13 +4602,13 @@
       <c r="I27" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="84" t="s">
+      <c r="J27" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="84">
+      <c r="K27" s="83">
         <v>15</v>
       </c>
-      <c r="L27" s="84">
+      <c r="L27" s="83">
         <v>45</v>
       </c>
       <c r="M27" s="45">
@@ -4587,38 +4622,38 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P27" s="247" t="s">
+      <c r="P27" s="241" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="160">
+      <c r="Q27" s="155">
         <v>0.1085</v>
       </c>
-      <c r="R27" s="161">
+      <c r="R27" s="156">
         <f t="shared" si="2"/>
         <v>1.6274999999999999</v>
       </c>
-      <c r="S27" s="161">
+      <c r="S27" s="156">
         <v>0.1085</v>
       </c>
-      <c r="T27" s="161">
+      <c r="T27" s="156">
         <f t="shared" si="3"/>
         <v>4.8825000000000003</v>
       </c>
-      <c r="U27" s="166"/>
-      <c r="V27" s="166" t="s">
+      <c r="U27" s="161"/>
+      <c r="V27" s="161" t="s">
         <v>291</v>
       </c>
-      <c r="W27" s="163"/>
+      <c r="W27" s="158"/>
     </row>
     <row r="28" spans="1:23" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="264"/>
-      <c r="C28" s="86" t="s">
+      <c r="B28" s="261"/>
+      <c r="C28" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D28" s="133" t="s">
+      <c r="D28" s="132" t="s">
         <v>165</v>
       </c>
       <c r="E28" s="67" t="s">
@@ -4645,31 +4680,31 @@
       <c r="L28" s="67">
         <v>25</v>
       </c>
-      <c r="M28" s="97">
+      <c r="M28" s="96">
         <v>1</v>
       </c>
-      <c r="N28" s="97">
+      <c r="N28" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O28" s="97">
+      <c r="O28" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="178" t="s">
+      <c r="P28" s="173" t="s">
         <v>16</v>
       </c>
       <c r="Q28" s="49">
         <v>9.6199999999999994E-2</v>
       </c>
-      <c r="R28" s="98">
+      <c r="R28" s="97">
         <f t="shared" si="2"/>
         <v>0.96199999999999997</v>
       </c>
-      <c r="S28" s="98">
+      <c r="S28" s="97">
         <v>9.6199999999999994E-2</v>
       </c>
-      <c r="T28" s="98">
+      <c r="T28" s="97">
         <f t="shared" si="3"/>
         <v>2.4049999999999998</v>
       </c>
@@ -4681,19 +4716,19 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="263" t="s">
+      <c r="B29" s="260" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="134" t="s">
+      <c r="D29" s="133" t="s">
         <v>167</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="72" t="s">
+      <c r="F29" s="71" t="s">
         <v>84</v>
       </c>
       <c r="G29" s="31" t="s">
@@ -4702,19 +4737,19 @@
       <c r="H29" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="I29" s="116" t="s">
+      <c r="I29" s="115" t="s">
         <v>127</v>
       </c>
       <c r="J29" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="K29" s="135">
+      <c r="K29" s="134">
         <v>100</v>
       </c>
-      <c r="L29" s="135">
+      <c r="L29" s="134">
         <v>100</v>
       </c>
-      <c r="M29" s="135">
+      <c r="M29" s="134">
         <v>3</v>
       </c>
       <c r="N29" s="35">
@@ -4725,7 +4760,7 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="P29" s="136" t="s">
+      <c r="P29" s="135" t="s">
         <v>16</v>
       </c>
       <c r="Q29" s="36">
@@ -4750,11 +4785,11 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="264"/>
-      <c r="C30" s="73" t="s">
+      <c r="B30" s="261"/>
+      <c r="C30" s="72" t="s">
         <v>264</v>
       </c>
-      <c r="D30" s="108" t="s">
+      <c r="D30" s="107" t="s">
         <v>168</v>
       </c>
       <c r="E30" s="40" t="s">
@@ -4769,19 +4804,19 @@
       <c r="H30" s="38" t="s">
         <v>266</v>
       </c>
-      <c r="I30" s="84" t="s">
+      <c r="I30" s="83" t="s">
         <v>40</v>
       </c>
       <c r="J30" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="K30" s="85">
+      <c r="K30" s="84">
         <v>100</v>
       </c>
-      <c r="L30" s="85">
+      <c r="L30" s="84">
         <v>100</v>
       </c>
-      <c r="M30" s="85">
+      <c r="M30" s="84">
         <v>1</v>
       </c>
       <c r="N30" s="64">
@@ -4792,20 +4827,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P30" s="92" t="s">
+      <c r="P30" s="91" t="s">
         <v>16</v>
       </c>
       <c r="Q30" s="42">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="R30" s="90">
+      <c r="R30" s="89">
         <f>Q30*K30</f>
         <v>0.16999999999999998</v>
       </c>
-      <c r="S30" s="90">
+      <c r="S30" s="89">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="T30" s="90">
+      <c r="T30" s="89">
         <f t="shared" si="3"/>
         <v>0.16999999999999998</v>
       </c>
@@ -4817,11 +4852,11 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="264"/>
-      <c r="C31" s="73" t="s">
+      <c r="B31" s="261"/>
+      <c r="C31" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="D31" s="115" t="s">
+      <c r="D31" s="114" t="s">
         <v>170</v>
       </c>
       <c r="E31" s="40" t="s">
@@ -4836,19 +4871,19 @@
       <c r="H31" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="I31" s="84" t="s">
+      <c r="I31" s="83" t="s">
         <v>40</v>
       </c>
       <c r="J31" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="K31" s="85">
+      <c r="K31" s="84">
         <v>100</v>
       </c>
-      <c r="L31" s="85">
+      <c r="L31" s="84">
         <v>100</v>
       </c>
-      <c r="M31" s="85">
+      <c r="M31" s="84">
         <v>1</v>
       </c>
       <c r="N31" s="64">
@@ -4859,20 +4894,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P31" s="92" t="s">
+      <c r="P31" s="91" t="s">
         <v>16</v>
       </c>
       <c r="Q31" s="42">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="R31" s="90">
+      <c r="R31" s="89">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="S31" s="90">
+      <c r="S31" s="89">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="T31" s="90">
+      <c r="T31" s="89">
         <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
@@ -4884,11 +4919,11 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="264"/>
-      <c r="C32" s="73" t="s">
+      <c r="B32" s="261"/>
+      <c r="C32" s="72" t="s">
         <v>234</v>
       </c>
-      <c r="D32" s="115" t="s">
+      <c r="D32" s="114" t="s">
         <v>235</v>
       </c>
       <c r="E32" s="40" t="s">
@@ -4903,19 +4938,19 @@
       <c r="H32" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="I32" s="84" t="s">
+      <c r="I32" s="83" t="s">
         <v>40</v>
       </c>
       <c r="J32" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="K32" s="85">
+      <c r="K32" s="84">
         <v>100</v>
       </c>
-      <c r="L32" s="85">
+      <c r="L32" s="84">
         <v>100</v>
       </c>
-      <c r="M32" s="85">
+      <c r="M32" s="84">
         <v>4</v>
       </c>
       <c r="N32" s="64">
@@ -4926,20 +4961,20 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="P32" s="92" t="s">
+      <c r="P32" s="91" t="s">
         <v>16</v>
       </c>
       <c r="Q32" s="42">
         <v>1.4E-3</v>
       </c>
-      <c r="R32" s="90">
+      <c r="R32" s="89">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S32" s="90">
+      <c r="S32" s="89">
         <v>1.4E-3</v>
       </c>
-      <c r="T32" s="90">
+      <c r="T32" s="89">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
@@ -4951,442 +4986,442 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="265"/>
-      <c r="C33" s="70" t="s">
+      <c r="B33" s="261"/>
+      <c r="C33" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="137" t="s">
+      <c r="D33" s="114" t="s">
         <v>277</v>
       </c>
-      <c r="E33" s="71" t="s">
+      <c r="E33" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="71" t="s">
+      <c r="F33" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="50" t="s">
+      <c r="G33" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="H33" s="51" t="s">
+      <c r="H33" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="I33" s="121" t="s">
+      <c r="I33" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="71" t="s">
+      <c r="J33" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="138">
+      <c r="K33" s="84">
         <v>100</v>
       </c>
-      <c r="L33" s="138">
+      <c r="L33" s="84">
         <v>100</v>
       </c>
-      <c r="M33" s="138">
+      <c r="M33" s="84">
         <v>2</v>
       </c>
-      <c r="N33" s="53">
+      <c r="N33" s="64">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O33" s="53">
+      <c r="O33" s="64">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P33" s="139" t="s">
+      <c r="P33" s="246" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="54">
+      <c r="Q33" s="42">
         <v>1.4E-3</v>
       </c>
-      <c r="R33" s="95">
+      <c r="R33" s="89">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S33" s="95">
+      <c r="S33" s="89">
         <v>1.4E-3</v>
       </c>
-      <c r="T33" s="95">
+      <c r="T33" s="89">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="U33" s="15"/>
-      <c r="V33" s="15"/>
-      <c r="W33" s="16"/>
-    </row>
-    <row r="34" spans="1:23" ht="16.5" thickBot="1">
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="14"/>
+    </row>
+    <row r="34" spans="1:23" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="264" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="209" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="179" t="s">
-        <v>89</v>
-      </c>
-      <c r="E34" s="180" t="s">
-        <v>90</v>
-      </c>
-      <c r="F34" s="180" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="181" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="181" t="s">
-        <v>39</v>
-      </c>
-      <c r="I34" s="181" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34" s="180" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="180">
-        <v>11</v>
-      </c>
-      <c r="L34" s="180">
-        <v>42</v>
-      </c>
-      <c r="M34" s="182">
+      <c r="B34" s="262"/>
+      <c r="C34" s="271" t="s">
+        <v>303</v>
+      </c>
+      <c r="D34" s="272" t="s">
+        <v>301</v>
+      </c>
+      <c r="E34" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="70" t="s">
+        <v>302</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="H34" s="273" t="s">
+        <v>305</v>
+      </c>
+      <c r="I34" s="120" t="s">
+        <v>40</v>
+      </c>
+      <c r="J34" s="70" t="s">
+        <v>304</v>
+      </c>
+      <c r="K34" s="274">
+        <v>100</v>
+      </c>
+      <c r="L34" s="274">
+        <v>100</v>
+      </c>
+      <c r="M34" s="274">
         <v>2</v>
       </c>
-      <c r="N34" s="182">
+      <c r="N34" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="182">
+      <c r="O34" s="53">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="183" t="s">
+      <c r="P34" s="275" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q34" s="54">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="R34" s="94">
+        <f>Q34*K34</f>
+        <v>0.12</v>
+      </c>
+      <c r="S34" s="94">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="T34" s="94">
+        <f t="shared" si="3"/>
+        <v>0.12</v>
+      </c>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="16"/>
+    </row>
+    <row r="35" spans="1:23" ht="16.5" thickBot="1">
+      <c r="A35" s="6">
+        <v>33</v>
+      </c>
+      <c r="B35" s="261" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="204" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="174" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="175" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="175" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" s="176" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="176" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="176" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" s="175" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="175">
+        <v>11</v>
+      </c>
+      <c r="L35" s="175">
+        <v>42</v>
+      </c>
+      <c r="M35" s="177">
+        <v>2</v>
+      </c>
+      <c r="N35" s="177">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="O35" s="177">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="P35" s="178" t="s">
         <v>133</v>
       </c>
-      <c r="Q34" s="184">
+      <c r="Q35" s="179">
         <v>0.318</v>
       </c>
-      <c r="R34" s="185">
+      <c r="R35" s="180">
         <f t="shared" si="2"/>
         <v>3.4980000000000002</v>
       </c>
-      <c r="S34" s="185">
+      <c r="S35" s="180">
         <v>0.4148</v>
       </c>
-      <c r="T34" s="185">
+      <c r="T35" s="180">
         <f t="shared" si="3"/>
         <v>17.421600000000002</v>
       </c>
-      <c r="U34" s="177"/>
-      <c r="V34" s="177" t="s">
+      <c r="U35" s="172"/>
+      <c r="V35" s="172" t="s">
         <v>291</v>
       </c>
-      <c r="W34" s="222" t="s">
+      <c r="W35" s="217" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A35" s="6">
-        <v>33</v>
-      </c>
-      <c r="B35" s="264"/>
-      <c r="C35" s="158" t="s">
+    <row r="36" spans="1:23" ht="26.25" thickBot="1">
+      <c r="A36" s="6">
+        <v>34</v>
+      </c>
+      <c r="B36" s="261"/>
+      <c r="C36" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="115" t="s">
+      <c r="D36" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="84" t="s">
+      <c r="E36" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="84" t="s">
+      <c r="F36" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="G35" s="39" t="s">
+      <c r="G36" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="H35" s="39" t="s">
+      <c r="H36" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="I35" s="39" t="s">
+      <c r="I36" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="84" t="s">
+      <c r="J36" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="39">
+      <c r="K36" s="39">
         <v>6</v>
       </c>
-      <c r="L35" s="39">
+      <c r="L36" s="39">
         <v>21</v>
       </c>
-      <c r="M35" s="45">
+      <c r="M36" s="45">
         <v>1</v>
       </c>
-      <c r="N35" s="45">
+      <c r="N36" s="45">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="45">
+      <c r="O36" s="45">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="247" t="s">
+      <c r="P36" s="241" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="160">
+      <c r="Q36" s="155">
         <v>0.40610000000000002</v>
       </c>
-      <c r="R35" s="161">
+      <c r="R36" s="156">
         <f t="shared" si="2"/>
         <v>2.4366000000000003</v>
       </c>
-      <c r="S35" s="161">
+      <c r="S36" s="156">
         <v>0.3528</v>
       </c>
-      <c r="T35" s="161">
+      <c r="T36" s="156">
         <f t="shared" si="3"/>
         <v>7.4088000000000003</v>
       </c>
-      <c r="U35" s="166"/>
-      <c r="V35" s="166" t="s">
+      <c r="U36" s="161"/>
+      <c r="V36" s="161" t="s">
         <v>291</v>
       </c>
-      <c r="W35" s="163"/>
-    </row>
-    <row r="36" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A36" s="6">
-        <v>34</v>
-      </c>
-      <c r="B36" s="264"/>
-      <c r="C36" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="141" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="142" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="142" t="s">
-        <v>97</v>
-      </c>
-      <c r="G36" s="143" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="143" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="142" t="s">
-        <v>39</v>
-      </c>
-      <c r="J36" s="142" t="s">
-        <v>22</v>
-      </c>
-      <c r="K36" s="143">
-        <v>6</v>
-      </c>
-      <c r="L36" s="143">
-        <v>21</v>
-      </c>
-      <c r="M36" s="144">
-        <v>1</v>
-      </c>
-      <c r="N36" s="144">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O36" s="144">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P36" s="145" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q36" s="150">
-        <v>8</v>
-      </c>
-      <c r="R36" s="147">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="S36" s="147">
-        <v>8</v>
-      </c>
-      <c r="T36" s="147">
-        <f t="shared" si="3"/>
-        <v>168</v>
-      </c>
-      <c r="U36" s="151"/>
-      <c r="V36" s="148" t="s">
-        <v>291</v>
-      </c>
-      <c r="W36" s="152"/>
+      <c r="W36" s="158"/>
     </row>
     <row r="37" spans="1:23" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="264"/>
-      <c r="C37" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="109" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="78" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="G37" s="79" t="s">
+      <c r="B37" s="261"/>
+      <c r="C37" s="136" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="137" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="138" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" s="138" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="139" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="79" t="s">
+      <c r="H37" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="78" t="s">
+      <c r="I37" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="78" t="s">
+      <c r="J37" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="79">
-        <v>11</v>
-      </c>
-      <c r="L37" s="79">
-        <v>41</v>
-      </c>
-      <c r="M37" s="80">
-        <v>2</v>
-      </c>
-      <c r="N37" s="80">
+      <c r="K37" s="139">
+        <v>6</v>
+      </c>
+      <c r="L37" s="139">
+        <v>21</v>
+      </c>
+      <c r="M37" s="140">
+        <v>1</v>
+      </c>
+      <c r="N37" s="140">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O37" s="64">
+        <v>5</v>
+      </c>
+      <c r="O37" s="140">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="P37" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="P37" s="141" t="s">
         <v>151</v>
       </c>
-      <c r="Q37" s="155">
-        <v>4.76</v>
-      </c>
-      <c r="R37" s="93">
+      <c r="Q37" s="146">
+        <v>8</v>
+      </c>
+      <c r="R37" s="143">
         <f t="shared" si="2"/>
-        <v>52.36</v>
-      </c>
-      <c r="S37" s="93">
-        <v>4.76</v>
-      </c>
-      <c r="T37" s="156">
+        <v>48</v>
+      </c>
+      <c r="S37" s="143">
+        <v>8</v>
+      </c>
+      <c r="T37" s="143">
         <f t="shared" si="3"/>
-        <v>195.16</v>
-      </c>
-      <c r="U37" s="82" t="s">
-        <v>293</v>
-      </c>
-      <c r="V37" s="148" t="s">
+        <v>168</v>
+      </c>
+      <c r="U37" s="147"/>
+      <c r="V37" s="144" t="s">
         <v>291</v>
       </c>
-      <c r="W37" s="223">
-        <v>4.76</v>
-      </c>
+      <c r="W37" s="148"/>
     </row>
     <row r="38" spans="1:23" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="264"/>
-      <c r="C38" s="73" t="s">
-        <v>173</v>
+      <c r="B38" s="261"/>
+      <c r="C38" s="76" t="s">
+        <v>98</v>
       </c>
       <c r="D38" s="108" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="F38" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="G38" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="H38" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="I38" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="F38" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="40" t="s">
+      <c r="J38" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="44">
-        <v>6</v>
-      </c>
-      <c r="L38" s="44">
-        <v>21</v>
-      </c>
-      <c r="M38" s="64">
-        <v>1</v>
-      </c>
-      <c r="N38" s="64">
+      <c r="K38" s="78">
+        <v>11</v>
+      </c>
+      <c r="L38" s="78">
+        <v>41</v>
+      </c>
+      <c r="M38" s="79">
+        <v>2</v>
+      </c>
+      <c r="N38" s="79">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O38" s="64">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P38" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q38" s="42">
-        <v>2.3496999999999999</v>
-      </c>
-      <c r="R38" s="90">
+        <v>40</v>
+      </c>
+      <c r="P38" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q38" s="151">
+        <v>4.76</v>
+      </c>
+      <c r="R38" s="92">
         <f t="shared" si="2"/>
-        <v>14.098199999999999</v>
-      </c>
-      <c r="S38" s="90">
-        <v>2.3496999999999999</v>
-      </c>
-      <c r="T38" s="90">
+        <v>52.36</v>
+      </c>
+      <c r="S38" s="92">
+        <v>4.76</v>
+      </c>
+      <c r="T38" s="152">
         <f t="shared" si="3"/>
-        <v>49.343699999999998</v>
-      </c>
-      <c r="U38" s="19"/>
-      <c r="V38" s="19"/>
-      <c r="W38" s="14"/>
+        <v>195.16</v>
+      </c>
+      <c r="U38" s="81" t="s">
+        <v>293</v>
+      </c>
+      <c r="V38" s="144" t="s">
+        <v>291</v>
+      </c>
+      <c r="W38" s="218">
+        <v>4.76</v>
+      </c>
     </row>
     <row r="39" spans="1:23" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="264"/>
-      <c r="C39" s="73" t="s">
-        <v>176</v>
-      </c>
-      <c r="D39" s="108" t="s">
-        <v>177</v>
+      <c r="B39" s="261"/>
+      <c r="C39" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" s="107" t="s">
+        <v>174</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H39" s="44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I39" s="39" t="s">
         <v>39</v>
@@ -5411,22 +5446,22 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P39" s="83" t="s">
+      <c r="P39" s="82" t="s">
         <v>16</v>
       </c>
       <c r="Q39" s="42">
-        <v>0.6492</v>
-      </c>
-      <c r="R39" s="90">
+        <v>2.3496999999999999</v>
+      </c>
+      <c r="R39" s="89">
         <f t="shared" si="2"/>
-        <v>3.8952</v>
-      </c>
-      <c r="S39" s="90">
-        <v>0.5464</v>
-      </c>
-      <c r="T39" s="90">
+        <v>14.098199999999999</v>
+      </c>
+      <c r="S39" s="89">
+        <v>2.3496999999999999</v>
+      </c>
+      <c r="T39" s="89">
         <f t="shared" si="3"/>
-        <v>11.474399999999999</v>
+        <v>49.343699999999998</v>
       </c>
       <c r="U39" s="19"/>
       <c r="V39" s="19"/>
@@ -5436,379 +5471,379 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="264"/>
-      <c r="C40" s="140" t="s">
-        <v>267</v>
-      </c>
-      <c r="D40" s="141" t="s">
-        <v>268</v>
-      </c>
-      <c r="E40" s="142" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="142" t="s">
-        <v>269</v>
-      </c>
-      <c r="G40" s="143" t="s">
-        <v>275</v>
-      </c>
-      <c r="H40" s="143" t="s">
+      <c r="B40" s="261"/>
+      <c r="C40" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="D40" s="107" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="H40" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="I40" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="I40" s="143" t="s">
-        <v>39</v>
-      </c>
-      <c r="J40" s="142" t="s">
+      <c r="J40" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="143">
+      <c r="K40" s="44">
         <v>6</v>
       </c>
-      <c r="L40" s="143">
-        <v>22</v>
-      </c>
-      <c r="M40" s="144">
+      <c r="L40" s="44">
+        <v>21</v>
+      </c>
+      <c r="M40" s="64">
         <v>1</v>
       </c>
-      <c r="N40" s="144">
+      <c r="N40" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="144">
+      <c r="O40" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="154" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q40" s="146">
-        <v>0.8</v>
-      </c>
-      <c r="R40" s="147">
+      <c r="P40" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q40" s="42">
+        <v>0.6492</v>
+      </c>
+      <c r="R40" s="89">
         <f t="shared" si="2"/>
-        <v>4.8000000000000007</v>
-      </c>
-      <c r="S40" s="147">
-        <v>0.8</v>
-      </c>
-      <c r="T40" s="147">
+        <v>3.8952</v>
+      </c>
+      <c r="S40" s="89">
+        <v>0.5464</v>
+      </c>
+      <c r="T40" s="89">
         <f t="shared" si="3"/>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="U40" s="153" t="s">
-        <v>276</v>
-      </c>
-      <c r="V40" s="148" t="s">
-        <v>291</v>
-      </c>
-      <c r="W40" s="149"/>
+        <v>11.474399999999999</v>
+      </c>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="14"/>
     </row>
     <row r="41" spans="1:23" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="264"/>
-      <c r="C41" s="140" t="s">
-        <v>280</v>
-      </c>
-      <c r="D41" s="141" t="s">
-        <v>278</v>
-      </c>
-      <c r="E41" s="142" t="s">
-        <v>281</v>
-      </c>
-      <c r="F41" s="164" t="s">
-        <v>282</v>
-      </c>
-      <c r="G41" s="143" t="s">
-        <v>283</v>
-      </c>
-      <c r="H41" s="143" t="s">
+      <c r="B41" s="261"/>
+      <c r="C41" s="136" t="s">
+        <v>267</v>
+      </c>
+      <c r="D41" s="137" t="s">
+        <v>268</v>
+      </c>
+      <c r="E41" s="138" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="138" t="s">
+        <v>269</v>
+      </c>
+      <c r="G41" s="139" t="s">
+        <v>275</v>
+      </c>
+      <c r="H41" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="143" t="s">
+      <c r="I41" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="142" t="s">
+      <c r="J41" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="143">
-        <v>10</v>
-      </c>
-      <c r="L41" s="143">
-        <v>30</v>
-      </c>
-      <c r="M41" s="144">
+      <c r="K41" s="139">
+        <v>6</v>
+      </c>
+      <c r="L41" s="139">
+        <v>22</v>
+      </c>
+      <c r="M41" s="140">
         <v>1</v>
       </c>
-      <c r="N41" s="144">
+      <c r="N41" s="140">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="144">
+      <c r="O41" s="140">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="145" t="s">
+      <c r="P41" s="150" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q41" s="142">
+        <v>0.8</v>
+      </c>
+      <c r="R41" s="143">
+        <f t="shared" si="2"/>
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="S41" s="143">
+        <v>0.8</v>
+      </c>
+      <c r="T41" s="143">
+        <f t="shared" si="3"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="U41" s="149" t="s">
+        <v>276</v>
+      </c>
+      <c r="V41" s="144" t="s">
+        <v>291</v>
+      </c>
+      <c r="W41" s="145"/>
+    </row>
+    <row r="42" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A42" s="6">
+        <v>40</v>
+      </c>
+      <c r="B42" s="261"/>
+      <c r="C42" s="136" t="s">
+        <v>280</v>
+      </c>
+      <c r="D42" s="137" t="s">
+        <v>278</v>
+      </c>
+      <c r="E42" s="138" t="s">
+        <v>281</v>
+      </c>
+      <c r="F42" s="159" t="s">
+        <v>282</v>
+      </c>
+      <c r="G42" s="139" t="s">
+        <v>283</v>
+      </c>
+      <c r="H42" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="J42" s="138" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="139">
+        <v>10</v>
+      </c>
+      <c r="L42" s="139">
+        <v>30</v>
+      </c>
+      <c r="M42" s="140">
+        <v>1</v>
+      </c>
+      <c r="N42" s="140">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O42" s="140">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P42" s="141" t="s">
         <v>133</v>
       </c>
-      <c r="Q41" s="146">
+      <c r="Q42" s="142">
         <v>1</v>
       </c>
-      <c r="R41" s="147">
+      <c r="R42" s="143">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S41" s="147">
+      <c r="S42" s="143">
         <v>1</v>
       </c>
-      <c r="T41" s="147">
+      <c r="T42" s="143">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="U41" s="165"/>
-      <c r="V41" s="274" t="s">
+      <c r="U42" s="160"/>
+      <c r="V42" s="244" t="s">
         <v>300</v>
       </c>
-      <c r="W41" s="149"/>
-    </row>
-    <row r="42" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A42" s="6">
-        <v>40</v>
-      </c>
-      <c r="B42" s="264"/>
-      <c r="C42" s="86" t="s">
+      <c r="W42" s="145"/>
+    </row>
+    <row r="43" spans="1:23" ht="26.25" thickBot="1">
+      <c r="A43" s="6">
+        <v>41</v>
+      </c>
+      <c r="B43" s="262"/>
+      <c r="C43" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="D42" s="133" t="s">
+      <c r="D43" s="132" t="s">
         <v>102</v>
       </c>
-      <c r="E42" s="67" t="s">
+      <c r="E43" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="F42" s="67" t="s">
+      <c r="F43" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="G42" s="67" t="s">
+      <c r="G43" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="H42" s="67" t="s">
+      <c r="H43" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="I42" s="67" t="s">
+      <c r="I43" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="67" t="s">
+      <c r="J43" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="46">
+      <c r="K43" s="46">
         <v>10</v>
       </c>
-      <c r="L42" s="46">
+      <c r="L43" s="46">
         <v>30</v>
       </c>
-      <c r="M42" s="97">
+      <c r="M43" s="96">
         <v>1</v>
       </c>
-      <c r="N42" s="97">
+      <c r="N43" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O42" s="97">
+      <c r="O43" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P42" s="211" t="s">
+      <c r="P43" s="206" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="49">
+      <c r="Q43" s="49">
         <v>5.6399999999999999E-2</v>
       </c>
-      <c r="R42" s="98">
+      <c r="R43" s="97">
         <f t="shared" si="2"/>
         <v>0.56399999999999995</v>
       </c>
-      <c r="S42" s="98">
+      <c r="S43" s="97">
         <v>5.6399999999999999E-2</v>
       </c>
-      <c r="T42" s="98">
+      <c r="T43" s="97">
         <f t="shared" si="3"/>
         <v>1.6919999999999999</v>
       </c>
-      <c r="U42" s="212"/>
-      <c r="V42" s="212"/>
-      <c r="W42" s="27"/>
-    </row>
-    <row r="43" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A43" s="6">
+      <c r="U43" s="207"/>
+      <c r="V43" s="207"/>
+      <c r="W43" s="27"/>
+    </row>
+    <row r="44" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A44" s="6">
+        <v>42</v>
+      </c>
+      <c r="B44" s="260" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="263" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" s="68" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" s="69" t="s">
-        <v>41</v>
-      </c>
-      <c r="E43" s="34" t="s">
+      <c r="E44" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="72" t="s">
+      <c r="F44" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="G43" s="35" t="s">
+      <c r="G44" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="H43" s="35" t="s">
+      <c r="H44" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="I43" s="34" t="s">
+      <c r="I44" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="J43" s="34" t="s">
+      <c r="J44" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="K43" s="56">
+      <c r="K44" s="56">
         <v>50</v>
       </c>
-      <c r="L43" s="56">
+      <c r="L44" s="56">
         <v>50</v>
       </c>
-      <c r="M43" s="57">
+      <c r="M44" s="57">
         <v>1</v>
       </c>
-      <c r="N43" s="35">
+      <c r="N44" s="35">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O43" s="35">
+      <c r="O44" s="35">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P43" s="75" t="s">
+      <c r="P44" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="Q43" s="36">
+      <c r="Q44" s="36">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="R43" s="37">
+      <c r="R44" s="37">
         <f t="shared" si="2"/>
         <v>0.72500000000000009</v>
       </c>
-      <c r="S43" s="37">
+      <c r="S44" s="37">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="T43" s="37">
+      <c r="T44" s="37">
         <f t="shared" si="3"/>
         <v>0.72500000000000009</v>
       </c>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="12"/>
-    </row>
-    <row r="44" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A44" s="6">
-        <v>42</v>
-      </c>
-      <c r="B44" s="264"/>
-      <c r="C44" s="73" t="s">
-        <v>287</v>
-      </c>
-      <c r="D44" s="108" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="F44" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="G44" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="H44" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="I44" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="J44" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="K44" s="40">
-        <v>10</v>
-      </c>
-      <c r="L44" s="40">
-        <v>30</v>
-      </c>
-      <c r="M44" s="58">
-        <v>1</v>
-      </c>
-      <c r="N44" s="64">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O44" s="64">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P44" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q44" s="55">
-        <v>6.2E-2</v>
-      </c>
-      <c r="R44" s="90">
-        <f t="shared" si="2"/>
-        <v>0.62</v>
-      </c>
-      <c r="S44" s="90">
-        <v>6.2E-2</v>
-      </c>
-      <c r="T44" s="90">
-        <f t="shared" si="3"/>
-        <v>1.8599999999999999</v>
-      </c>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="14"/>
-    </row>
-    <row r="45" spans="1:23" ht="15.75" thickBot="1">
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
+      <c r="W44" s="12"/>
+    </row>
+    <row r="45" spans="1:23" ht="26.25" thickBot="1">
       <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B45" s="264"/>
-      <c r="C45" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" s="108" t="s">
-        <v>34</v>
+      <c r="B45" s="261"/>
+      <c r="C45" s="72" t="s">
+        <v>287</v>
+      </c>
+      <c r="D45" s="107" t="s">
+        <v>42</v>
       </c>
       <c r="E45" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="76" t="s">
-        <v>108</v>
+      <c r="F45" s="40" t="s">
+        <v>288</v>
       </c>
       <c r="G45" s="40" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>141</v>
+        <v>290</v>
       </c>
       <c r="I45" s="40" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="J45" s="40" t="s">
         <v>22</v>
       </c>
       <c r="K45" s="40">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L45" s="40">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M45" s="58">
         <v>1</v>
@@ -5821,422 +5856,461 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P45" s="74" t="s">
+      <c r="P45" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="42">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="R45" s="90">
+      <c r="Q45" s="55">
+        <v>6.2E-2</v>
+      </c>
+      <c r="R45" s="89">
         <f t="shared" si="2"/>
-        <v>0.65</v>
-      </c>
-      <c r="S45" s="90">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="T45" s="90">
+        <v>0.62</v>
+      </c>
+      <c r="S45" s="89">
+        <v>6.2E-2</v>
+      </c>
+      <c r="T45" s="89">
         <f t="shared" si="3"/>
-        <v>0.65</v>
-      </c>
-      <c r="U45" s="25"/>
-      <c r="V45" s="25"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="U45" s="24"/>
+      <c r="V45" s="24"/>
       <c r="W45" s="14"/>
     </row>
     <row r="46" spans="1:23" ht="15.75" thickBot="1">
       <c r="A46" s="6">
         <v>44</v>
       </c>
-      <c r="B46" s="264"/>
-      <c r="C46" s="158" t="s">
-        <v>270</v>
-      </c>
-      <c r="D46" s="115" t="s">
-        <v>271</v>
-      </c>
-      <c r="E46" s="84" t="s">
+      <c r="B46" s="261"/>
+      <c r="C46" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="84" t="s">
-        <v>272</v>
-      </c>
-      <c r="G46" s="84" t="s">
-        <v>273</v>
-      </c>
-      <c r="H46" s="84" t="s">
-        <v>274</v>
-      </c>
-      <c r="I46" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="J46" s="84" t="s">
+      <c r="F46" s="75" t="s">
+        <v>108</v>
+      </c>
+      <c r="G46" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="I46" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="J46" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="84">
-        <v>5</v>
-      </c>
-      <c r="L46" s="84">
-        <v>25</v>
-      </c>
-      <c r="M46" s="45">
+      <c r="K46" s="40">
+        <v>50</v>
+      </c>
+      <c r="L46" s="40">
+        <v>50</v>
+      </c>
+      <c r="M46" s="58">
         <v>1</v>
       </c>
-      <c r="N46" s="45">
+      <c r="N46" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O46" s="45">
+      <c r="O46" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P46" s="159" t="s">
+      <c r="P46" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q46" s="160">
-        <v>8.8900000000000007E-2</v>
-      </c>
-      <c r="R46" s="161">
+      <c r="Q46" s="42">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="R46" s="89">
         <f t="shared" si="2"/>
-        <v>0.44450000000000001</v>
-      </c>
-      <c r="S46" s="161">
-        <v>8.8900000000000007E-2</v>
-      </c>
-      <c r="T46" s="161">
+        <v>0.65</v>
+      </c>
+      <c r="S46" s="89">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="T46" s="89">
         <f t="shared" si="3"/>
-        <v>2.2225000000000001</v>
-      </c>
-      <c r="U46" s="162"/>
-      <c r="V46" s="166"/>
-      <c r="W46" s="163"/>
+        <v>0.65</v>
+      </c>
+      <c r="U46" s="25"/>
+      <c r="V46" s="25"/>
+      <c r="W46" s="14"/>
     </row>
     <row r="47" spans="1:23" ht="15.75" thickBot="1">
       <c r="A47" s="6">
         <v>45</v>
       </c>
-      <c r="B47" s="264"/>
-      <c r="C47" s="73" t="s">
-        <v>284</v>
-      </c>
-      <c r="D47" s="40" t="s">
-        <v>279</v>
-      </c>
-      <c r="E47" s="40" t="s">
+      <c r="B47" s="261"/>
+      <c r="C47" s="153" t="s">
+        <v>270</v>
+      </c>
+      <c r="D47" s="114" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="167">
-        <v>61300611121</v>
-      </c>
-      <c r="G47" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="H47" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="I47" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="J47" s="40" t="s">
+      <c r="F47" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="G47" s="83" t="s">
+        <v>273</v>
+      </c>
+      <c r="H47" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="I47" s="83" t="s">
+        <v>40</v>
+      </c>
+      <c r="J47" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="K47" s="40">
-        <v>20</v>
-      </c>
-      <c r="L47" s="40">
-        <v>40</v>
-      </c>
-      <c r="M47" s="58">
+      <c r="K47" s="83">
+        <v>5</v>
+      </c>
+      <c r="L47" s="83">
+        <v>25</v>
+      </c>
+      <c r="M47" s="45">
         <v>1</v>
       </c>
-      <c r="N47" s="64">
+      <c r="N47" s="45">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O47" s="64">
+      <c r="O47" s="45">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P47" s="83" t="s">
+      <c r="P47" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="42">
+      <c r="Q47" s="155">
+        <v>8.8900000000000007E-2</v>
+      </c>
+      <c r="R47" s="156">
+        <f t="shared" si="2"/>
+        <v>0.44450000000000001</v>
+      </c>
+      <c r="S47" s="156">
+        <v>8.8900000000000007E-2</v>
+      </c>
+      <c r="T47" s="156">
+        <f t="shared" si="3"/>
+        <v>2.2225000000000001</v>
+      </c>
+      <c r="U47" s="157"/>
+      <c r="V47" s="161"/>
+      <c r="W47" s="158"/>
+    </row>
+    <row r="48" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A48" s="6">
+        <v>46</v>
+      </c>
+      <c r="B48" s="261"/>
+      <c r="C48" s="72" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="162">
+        <v>61300611121</v>
+      </c>
+      <c r="G48" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="H48" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="I48" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="J48" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" s="40">
+        <v>20</v>
+      </c>
+      <c r="L48" s="40">
+        <v>40</v>
+      </c>
+      <c r="M48" s="58">
+        <v>1</v>
+      </c>
+      <c r="N48" s="64">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O48" s="64">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P48" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q48" s="42">
         <v>3.09E-2</v>
       </c>
-      <c r="R47" s="90">
+      <c r="R48" s="89">
         <f t="shared" si="2"/>
         <v>0.61799999999999999</v>
       </c>
-      <c r="S47" s="90">
+      <c r="S48" s="89">
         <v>3.09E-2</v>
       </c>
-      <c r="T47" s="90">
+      <c r="T48" s="89">
         <f t="shared" si="3"/>
         <v>1.236</v>
       </c>
-      <c r="U47" s="25"/>
-      <c r="V47" s="25"/>
-      <c r="W47" s="14"/>
-    </row>
-    <row r="48" spans="1:23" ht="115.5" thickBot="1">
-      <c r="A48" s="6">
-        <v>46</v>
-      </c>
-      <c r="B48" s="265"/>
-      <c r="C48" s="99" t="s">
+      <c r="U48" s="25"/>
+      <c r="V48" s="25"/>
+      <c r="W48" s="14"/>
+    </row>
+    <row r="49" spans="1:23" ht="115.5" thickBot="1">
+      <c r="A49" s="6">
+        <v>47</v>
+      </c>
+      <c r="B49" s="262"/>
+      <c r="C49" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="100" t="s">
+      <c r="D49" s="99" t="s">
         <v>239</v>
       </c>
-      <c r="E48" s="101" t="s">
+      <c r="E49" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="101" t="s">
+      <c r="F49" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="G48" s="102" t="s">
+      <c r="G49" s="101" t="s">
         <v>142</v>
       </c>
-      <c r="H48" s="102"/>
-      <c r="I48" s="103"/>
-      <c r="J48" s="103" t="s">
+      <c r="H49" s="101"/>
+      <c r="I49" s="102"/>
+      <c r="J49" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="K48" s="103" t="s">
+      <c r="K49" s="102" t="s">
         <v>142</v>
       </c>
-      <c r="L48" s="103" t="s">
+      <c r="L49" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="104">
+      <c r="M49" s="103">
         <v>53</v>
       </c>
-      <c r="N48" s="105">
+      <c r="N49" s="104">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-      <c r="O48" s="53">
+      <c r="O49" s="53">
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
-      <c r="P48" s="102" t="s">
+      <c r="P49" s="101" t="s">
         <v>142</v>
       </c>
-      <c r="Q48" s="103" t="s">
+      <c r="Q49" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="103" t="s">
+      <c r="R49" s="102" t="s">
         <v>142</v>
       </c>
-      <c r="S48" s="103" t="s">
+      <c r="S49" s="102" t="s">
         <v>142</v>
       </c>
-      <c r="T48" s="103" t="s">
+      <c r="T49" s="102" t="s">
         <v>142</v>
       </c>
-      <c r="U48" s="106" t="s">
+      <c r="U49" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="V48" s="106"/>
-      <c r="W48" s="107"/>
-    </row>
-    <row r="49" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A49" s="6">
-        <v>47</v>
-      </c>
-      <c r="B49" s="271" t="s">
+      <c r="V49" s="105"/>
+      <c r="W49" s="106"/>
+    </row>
+    <row r="50" spans="1:23" ht="26.25" thickBot="1">
+      <c r="A50" s="6">
+        <v>48</v>
+      </c>
+      <c r="B50" s="268" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C50" s="208" t="s">
         <v>247</v>
       </c>
-      <c r="D49" s="214" t="s">
+      <c r="D50" s="209" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="214" t="s">
+      <c r="E50" s="209" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="214" t="s">
+      <c r="F50" s="209" t="s">
         <v>246</v>
       </c>
-      <c r="G49" s="214" t="s">
+      <c r="G50" s="209" t="s">
         <v>142</v>
       </c>
-      <c r="H49" s="214" t="s">
+      <c r="H50" s="209" t="s">
         <v>142</v>
       </c>
-      <c r="I49" s="214" t="s">
+      <c r="I50" s="209" t="s">
         <v>142</v>
       </c>
-      <c r="J49" s="214" t="s">
+      <c r="J50" s="209" t="s">
         <v>142</v>
       </c>
-      <c r="K49" s="214" t="s">
+      <c r="K50" s="209" t="s">
         <v>142</v>
       </c>
-      <c r="L49" s="214" t="s">
+      <c r="L50" s="209" t="s">
         <v>142</v>
       </c>
-      <c r="M49" s="57">
+      <c r="M50" s="57">
         <v>1</v>
       </c>
-      <c r="N49" s="35">
-        <f>M49*5</f>
+      <c r="N50" s="35">
+        <f>M50*5</f>
         <v>5</v>
       </c>
-      <c r="O49" s="35">
-        <f>M49*20</f>
+      <c r="O50" s="35">
+        <f>M50*20</f>
         <v>20</v>
       </c>
-      <c r="P49" s="215" t="s">
+      <c r="P50" s="210" t="s">
         <v>240</v>
       </c>
-      <c r="Q49" s="216">
+      <c r="Q50" s="211">
         <v>0.2</v>
       </c>
-      <c r="R49" s="217">
-        <f>Q49*N49</f>
+      <c r="R50" s="212">
+        <f>Q50*N50</f>
         <v>1</v>
       </c>
-      <c r="S49" s="216">
+      <c r="S50" s="211">
         <v>0.2</v>
       </c>
-      <c r="T49" s="37">
-        <f>S49*O49</f>
+      <c r="T50" s="37">
+        <f>S50*O50</f>
         <v>4</v>
       </c>
-      <c r="U49" s="218"/>
-      <c r="V49" s="218"/>
-      <c r="W49" s="219"/>
-    </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A50" s="224">
-        <v>48</v>
-      </c>
-      <c r="B50" s="272"/>
-      <c r="C50" s="117" t="s">
+      <c r="U50" s="213"/>
+      <c r="V50" s="213"/>
+      <c r="W50" s="214"/>
+    </row>
+    <row r="51" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A51" s="276">
+        <v>49</v>
+      </c>
+      <c r="B51" s="269"/>
+      <c r="C51" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="D50" s="118" t="s">
+      <c r="D51" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="118" t="s">
+      <c r="E51" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="119" t="s">
+      <c r="F51" s="118" t="s">
         <v>150</v>
       </c>
-      <c r="G50" s="118" t="s">
+      <c r="G51" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="H50" s="118" t="s">
+      <c r="H51" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="I50" s="118" t="s">
+      <c r="I51" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="J50" s="118" t="s">
+      <c r="J51" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="118" t="s">
+      <c r="K51" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="L50" s="118" t="s">
+      <c r="L51" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="110">
+      <c r="M51" s="109">
         <v>1</v>
       </c>
-      <c r="N50" s="110">
-        <f t="shared" ref="N50" si="4">M50*5</f>
+      <c r="N51" s="109">
+        <f t="shared" ref="N51" si="4">M51*5</f>
         <v>5</v>
       </c>
-      <c r="O50" s="53">
+      <c r="O51" s="53">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P50" s="125" t="s">
+      <c r="P51" s="124" t="s">
         <v>240</v>
       </c>
-      <c r="Q50" s="111">
+      <c r="Q51" s="110">
         <v>3.35</v>
       </c>
-      <c r="R50" s="112">
-        <f>Q50*N50</f>
+      <c r="R51" s="111">
+        <f>Q51*N51</f>
         <v>16.75</v>
       </c>
-      <c r="S50" s="112">
+      <c r="S51" s="111">
         <v>3.35</v>
       </c>
-      <c r="T50" s="95">
-        <f>S50*O50</f>
+      <c r="T51" s="94">
+        <f>S51*O51</f>
         <v>67</v>
       </c>
-      <c r="U50" s="106" t="s">
+      <c r="U51" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="V50" s="106"/>
-      <c r="W50" s="120"/>
-    </row>
-    <row r="51" spans="1:23" ht="15.75">
-      <c r="A51" s="1"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="259" t="s">
-        <v>37</v>
-      </c>
-      <c r="N51" s="260"/>
-      <c r="O51" s="260"/>
-      <c r="P51" s="260"/>
-      <c r="Q51" s="18"/>
-      <c r="R51" s="127">
-        <f>SUM(R3:R50)</f>
-        <v>332.07675999999998</v>
-      </c>
-      <c r="S51" s="127"/>
-      <c r="T51" s="89">
-        <f>SUM(T3:T50)</f>
-        <v>1216.0299</v>
-      </c>
-      <c r="U51" s="7"/>
-      <c r="V51" s="7"/>
-      <c r="W51" s="7"/>
-    </row>
-    <row r="52" spans="1:23" ht="16.5" thickBot="1">
+      <c r="V51" s="105"/>
+      <c r="W51" s="119"/>
+    </row>
+    <row r="52" spans="1:23" ht="15.75">
       <c r="A52" s="1"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="I52" s="2"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="261" t="s">
-        <v>38</v>
-      </c>
-      <c r="N52" s="262"/>
-      <c r="O52" s="262"/>
-      <c r="P52" s="262"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="130">
-        <f>R51/5</f>
-        <v>66.415351999999999</v>
-      </c>
-      <c r="S52" s="130"/>
-      <c r="T52" s="30">
-        <f>T51/20</f>
-        <v>60.801495000000003</v>
+      <c r="M52" s="256" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" s="257"/>
+      <c r="O52" s="257"/>
+      <c r="P52" s="257"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="126">
+        <f>SUM(R3:R51)</f>
+        <v>332.19675999999998</v>
+      </c>
+      <c r="S52" s="126"/>
+      <c r="T52" s="88">
+        <f>SUM(T3:T51)</f>
+        <v>1216.1499000000001</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7"/>
     </row>
-    <row r="53" spans="1:23" ht="15.75">
+    <row r="53" spans="1:23" ht="16.5" thickBot="1">
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -6244,19 +6318,21 @@
       <c r="I53" s="2"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="250" t="s">
-        <v>145</v>
-      </c>
-      <c r="O53" s="251"/>
-      <c r="P53" s="252"/>
-      <c r="Q53" s="126"/>
-      <c r="R53" s="128">
-        <v>3</v>
-      </c>
-      <c r="S53" s="128"/>
-      <c r="T53" s="129">
-        <v>3</v>
+      <c r="M53" s="258" t="s">
+        <v>38</v>
+      </c>
+      <c r="N53" s="259"/>
+      <c r="O53" s="259"/>
+      <c r="P53" s="259"/>
+      <c r="Q53" s="29"/>
+      <c r="R53" s="129">
+        <f>R52/5</f>
+        <v>66.439352</v>
+      </c>
+      <c r="S53" s="129"/>
+      <c r="T53" s="30">
+        <f>T52/20</f>
+        <v>60.807495000000003</v>
       </c>
       <c r="U53" s="7"/>
       <c r="V53" s="7"/>
@@ -6271,53 +6347,70 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="268" t="s">
-        <v>248</v>
-      </c>
-      <c r="O54" s="269"/>
-      <c r="P54" s="270"/>
-      <c r="Q54" s="124"/>
-      <c r="R54" s="123">
-        <v>22.78</v>
-      </c>
-      <c r="S54" s="123"/>
-      <c r="T54" s="131">
-        <v>90.99</v>
+      <c r="N54" s="247" t="s">
+        <v>145</v>
+      </c>
+      <c r="O54" s="248"/>
+      <c r="P54" s="249"/>
+      <c r="Q54" s="125"/>
+      <c r="R54" s="127">
+        <v>3</v>
+      </c>
+      <c r="S54" s="127"/>
+      <c r="T54" s="128">
+        <v>3</v>
       </c>
       <c r="U54" s="7"/>
       <c r="V54" s="7"/>
       <c r="W54" s="7"/>
     </row>
-    <row r="55" spans="1:23" ht="16.5" thickBot="1">
+    <row r="55" spans="1:23" ht="15.75">
       <c r="A55" s="1"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="N55" s="253" t="s">
-        <v>299</v>
-      </c>
-      <c r="O55" s="254"/>
-      <c r="P55" s="255"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="248">
-        <f>SUM(R52:R54)</f>
-        <v>92.195352</v>
-      </c>
-      <c r="S55" s="132"/>
-      <c r="T55" s="249">
-        <f>SUM(T52:T54)</f>
-        <v>154.791495</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23">
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="265" t="s">
+        <v>248</v>
+      </c>
+      <c r="O55" s="266"/>
+      <c r="P55" s="267"/>
+      <c r="Q55" s="123"/>
+      <c r="R55" s="122">
+        <v>22.78</v>
+      </c>
+      <c r="S55" s="122"/>
+      <c r="T55" s="130">
+        <v>90.99</v>
+      </c>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+    </row>
+    <row r="56" spans="1:23" ht="16.5" thickBot="1">
       <c r="A56" s="1"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="G56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
+      <c r="N56" s="250" t="s">
+        <v>299</v>
+      </c>
+      <c r="O56" s="251"/>
+      <c r="P56" s="252"/>
+      <c r="Q56" s="29"/>
+      <c r="R56" s="242">
+        <f>SUM(R53:R55)</f>
+        <v>92.219352000000001</v>
+      </c>
+      <c r="S56" s="131"/>
+      <c r="T56" s="243">
+        <f>SUM(T53:T55)</f>
+        <v>154.797495</v>
+      </c>
     </row>
     <row r="57" spans="1:23">
       <c r="A57" s="1"/>
@@ -6325,6 +6418,8 @@
       <c r="D57" s="2"/>
       <c r="G57" s="2"/>
       <c r="I57" s="2"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
     </row>
     <row r="58" spans="1:23">
       <c r="A58" s="1"/>
@@ -6342,11 +6437,15 @@
     </row>
     <row r="60" spans="1:23">
       <c r="A60" s="1"/>
-    </row>
-    <row r="61" spans="1:23" ht="15.75" customHeight="1">
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:23">
       <c r="A61" s="1"/>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:23" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
     </row>
     <row r="63" spans="1:23">
@@ -6362,34 +6461,37 @@
       <c r="A66" s="1"/>
     </row>
     <row r="67" spans="1:22">
-      <c r="H67" s="9"/>
-      <c r="U67" s="10"/>
-      <c r="V67" s="10"/>
+      <c r="A67" s="1"/>
     </row>
     <row r="68" spans="1:22">
       <c r="H68" s="9"/>
       <c r="U68" s="10"/>
       <c r="V68" s="10"/>
     </row>
+    <row r="69" spans="1:22">
+      <c r="H69" s="9"/>
+      <c r="U69" s="10"/>
+      <c r="V69" s="10"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N56:P56"/>
     <mergeCell ref="A1:W1"/>
-    <mergeCell ref="M51:P51"/>
     <mergeCell ref="M52:P52"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B42"/>
-    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="M53:P53"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="B44:B49"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="B50:B51"/>
     <mergeCell ref="B3:B17"/>
     <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B29:B34"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="U44:V44">
+  <conditionalFormatting sqref="U45:V45">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
@@ -6443,7 +6545,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R52:T54">
+  <conditionalFormatting sqref="R53:T55">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -6457,7 +6559,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34:N48 O50 M9:M28 N3:O48 M49:O49">
+  <conditionalFormatting sqref="M35:N49 O51 M9:M28 N3:O49 M50:O50">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -6469,7 +6571,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:O49 O50">
+  <conditionalFormatting sqref="M3:O50 O51">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -6481,7 +6583,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K48:L48">
+  <conditionalFormatting sqref="K49:L49">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -6495,7 +6597,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M50:N50">
+  <conditionalFormatting sqref="M51:N51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6507,7 +6609,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M50:N50">
+  <conditionalFormatting sqref="M51:N51">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6519,7 +6621,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R50:S50">
+  <conditionalFormatting sqref="R51:S51">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -6533,7 +6635,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T49:T50 R3:T48">
+  <conditionalFormatting sqref="T50:T51 R3:T49">
     <cfRule type="dataBar" priority="48">
       <dataBar>
         <cfvo type="min"/>
@@ -6548,53 +6650,54 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="P3" r:id="rId1"/>
-    <hyperlink ref="P4" r:id="rId2"/>
-    <hyperlink ref="P5" r:id="rId3"/>
-    <hyperlink ref="P6" r:id="rId4"/>
-    <hyperlink ref="P8" r:id="rId5"/>
-    <hyperlink ref="P9" r:id="rId6"/>
-    <hyperlink ref="P10" r:id="rId7"/>
-    <hyperlink ref="P11" r:id="rId8"/>
-    <hyperlink ref="P25" r:id="rId9"/>
-    <hyperlink ref="P26" r:id="rId10"/>
-    <hyperlink ref="P27" r:id="rId11"/>
-    <hyperlink ref="P29" r:id="rId12"/>
-    <hyperlink ref="P33" r:id="rId13"/>
-    <hyperlink ref="P35" r:id="rId14"/>
-    <hyperlink ref="P42" r:id="rId15"/>
-    <hyperlink ref="P43" r:id="rId16"/>
-    <hyperlink ref="P45" r:id="rId17"/>
-    <hyperlink ref="P24" r:id="rId18" display="Aliexpress"/>
-    <hyperlink ref="P44" r:id="rId19"/>
-    <hyperlink ref="P7" r:id="rId20"/>
-    <hyperlink ref="P12" r:id="rId21"/>
-    <hyperlink ref="P13" r:id="rId22"/>
-    <hyperlink ref="P18" r:id="rId23"/>
-    <hyperlink ref="P20" r:id="rId24"/>
-    <hyperlink ref="P28" r:id="rId25"/>
-    <hyperlink ref="P31" r:id="rId26"/>
-    <hyperlink ref="P38" r:id="rId27"/>
-    <hyperlink ref="P39" r:id="rId28"/>
-    <hyperlink ref="P14" r:id="rId29"/>
-    <hyperlink ref="P15" r:id="rId30"/>
-    <hyperlink ref="P32" r:id="rId31"/>
-    <hyperlink ref="P50" r:id="rId32"/>
-    <hyperlink ref="P49" r:id="rId33"/>
-    <hyperlink ref="P16" r:id="rId34"/>
-    <hyperlink ref="P17" r:id="rId35"/>
-    <hyperlink ref="P30" r:id="rId36"/>
-    <hyperlink ref="P46" r:id="rId37"/>
-    <hyperlink ref="P41" r:id="rId38"/>
-    <hyperlink ref="P47" r:id="rId39"/>
-    <hyperlink ref="P19" r:id="rId40"/>
-    <hyperlink ref="P40" r:id="rId41"/>
-    <hyperlink ref="P23" r:id="rId42"/>
-    <hyperlink ref="P22" r:id="rId43"/>
-    <hyperlink ref="V41" r:id="rId44"/>
+    <hyperlink ref="P3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="P4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="P5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="P6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="P8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="P9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="P10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="P11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="P25" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="P26" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="P27" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="P29" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="P33" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="P36" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="P43" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="P44" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="P46" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="P24" r:id="rId18" display="Aliexpress" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="P45" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="P7" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="P12" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="P13" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="P18" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="P20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="P28" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="P31" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="P39" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="P40" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="P14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="P15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="P32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="P51" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="P50" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="P16" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="P17" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="P30" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="P47" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="P42" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="P48" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="P19" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="P41" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="P23" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="P22" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="V42" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="P34" r:id="rId45" xr:uid="{68CEE5F5-2B0A-4F4B-8D34-E9663AFF095E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId45"/>
+  <pageSetup orientation="portrait" r:id="rId46"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6609,7 +6712,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>U44:V44</xm:sqref>
+          <xm:sqref>U45:V45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{73D72061-44BE-43BF-B86A-016273A3FADD}">
@@ -6648,7 +6751,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R52:T54</xm:sqref>
+          <xm:sqref>R53:T55</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{193AFC57-9059-4DAB-9E2A-67F7DD9723ED}">
@@ -6661,7 +6764,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>K48:L48</xm:sqref>
+          <xm:sqref>K49:L49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{19A41A86-C9BB-4A96-AA11-2BBEAF826782}">
@@ -6674,7 +6777,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R50:S50</xm:sqref>
+          <xm:sqref>R51:S51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}">
@@ -6687,7 +6790,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>T49:T50 R3:T48</xm:sqref>
+          <xm:sqref>T50:T51 R3:T49</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
